--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,26 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F62B96C-A2AD-4B94-847D-E70BACC7291B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F669A1-B00C-4525-A5BC-7FB32CEFE979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sport-artwork review" sheetId="1" r:id="rId1"/>
     <sheet name="BilledeListe" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Forsvundne (havde valg)" sheetId="3" r:id="rId3"/>
-    <sheet name="Vejledning" sheetId="4" r:id="rId4"/>
+    <sheet name="Vejledning" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sport-artwork review'!$A$1:$H$1</definedName>
-    <definedName name="BilledeValgListe">BilledeListe!$A$1:$A$152</definedName>
+    <definedName name="BilledeValgListe">BilledeListe!$A$1:$A$154</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="594">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -269,6 +268,9 @@
     <t>League Cup: Ipswich - Arsenal</t>
   </si>
   <si>
+    <t>EFL Championship.jpg</t>
+  </si>
+  <si>
     <t>League Cup: Liverpool - Tottenham</t>
   </si>
   <si>
@@ -695,978 +697,981 @@
     <t>Serie A: Inter-Udinese</t>
   </si>
   <si>
+    <t>Serie A: Napoli-Bologna</t>
+  </si>
+  <si>
+    <t>Sæt pris på Danmark</t>
+  </si>
+  <si>
+    <t>Til salg i 100 år</t>
+  </si>
+  <si>
+    <t>Vuelta a España: 20. etape</t>
+  </si>
+  <si>
+    <t>Vuelta a España: 21. etape</t>
+  </si>
+  <si>
+    <t>Vuelta a España: Studiet</t>
+  </si>
+  <si>
+    <t>Vuelta a España -  Studiet.jpg</t>
+  </si>
+  <si>
+    <t>C - DR1/DR2</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk</t>
+  </si>
+  <si>
+    <t>24 timer vi aldrig glemmer</t>
+  </si>
+  <si>
+    <t>DR2.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>24 timer vi aldrig glemmer - 11. september 2001</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk; dr1.dk</t>
+  </si>
+  <si>
+    <t>Aftenshowet</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken Australien</t>
+  </si>
+  <si>
+    <t>DR1.dk; dr1.dk</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken Australien II (3:11)</t>
+  </si>
+  <si>
+    <t>DR1.dk</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken Australien II (4:11)</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken USA</t>
+  </si>
+  <si>
+    <t>DR2.dk</t>
+  </si>
+  <si>
+    <t>Alt forladt</t>
+  </si>
+  <si>
+    <t>Alt forladt - Elhøj og Kirckhoff i det glemte Danmark</t>
+  </si>
+  <si>
+    <t>Alt forladt - Mønsted Kalkgruber</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser (225)</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser (226)</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser (229)</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser (230)</t>
+  </si>
+  <si>
+    <t>Arrene fra apartheid (3:3)</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1.dk</t>
+  </si>
+  <si>
+    <t>Beck</t>
+  </si>
+  <si>
+    <t>Beck: Djævelens advokat</t>
+  </si>
+  <si>
+    <t>Bjerget</t>
+  </si>
+  <si>
+    <t>Blue Bayou</t>
+  </si>
+  <si>
+    <t>Danmarkshistorien fortalt af Erik Kjersgaard</t>
+  </si>
+  <si>
+    <t>Danmarkshistorien fortalt af Erik Kjersgaard (2:12)</t>
+  </si>
+  <si>
+    <t>Dansk teater 300 år</t>
+  </si>
+  <si>
+    <t>Dansk teater 300 år: Teatergalskaben</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk</t>
+  </si>
+  <si>
+    <t>Danske spioner i den kolde krig</t>
+  </si>
+  <si>
+    <t>Danske spioner i den kolde krig (2:4) Bag fjendens linjer</t>
+  </si>
+  <si>
+    <t>Danske spioner i den kolde krig Bag fjendens linjer</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk; DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk; dr1.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>Deadline: Hvorfor bliver børnene dummere?</t>
+  </si>
+  <si>
+    <t>Deadline: Kan man slutte fred med Putin?</t>
+  </si>
+  <si>
+    <t>Den klassiske musikquiz</t>
+  </si>
+  <si>
+    <t>Den klassiske musikquiz (7:8)</t>
+  </si>
+  <si>
+    <t>Den sidste fest</t>
+  </si>
+  <si>
+    <t>Den sidste fest (3:4) - 0,03 sekunder</t>
+  </si>
+  <si>
+    <t>Den sidste sommer med fred</t>
+  </si>
+  <si>
+    <t>Den store bagedyst</t>
+  </si>
+  <si>
+    <t>Dengang vi var bønder</t>
+  </si>
+  <si>
+    <t>Dengang vi var bønder (1:6)</t>
+  </si>
+  <si>
+    <t>Dengang vi var bønder (2:6)</t>
+  </si>
+  <si>
+    <t>Det danske madmirakel</t>
+  </si>
+  <si>
+    <t>Det danske madmirakel (3:4) Verdens bedste kokke</t>
+  </si>
+  <si>
+    <t>Det danske madmirakel Verdens bedste kokke</t>
+  </si>
+  <si>
+    <t>Dokument indefra: Stikkeren</t>
+  </si>
+  <si>
+    <t>Drømmen om et liv på landet</t>
+  </si>
+  <si>
+    <t>Dyrenes Danmark</t>
+  </si>
+  <si>
+    <t>En bedrager uden nåde</t>
+  </si>
+  <si>
+    <t>En bedrager uden nåde (3:4)</t>
+  </si>
+  <si>
+    <t>En hemmelighed under jorden</t>
+  </si>
+  <si>
+    <t>En hemmelighed under jorden (3:5) Hvis krigen kommer</t>
+  </si>
+  <si>
+    <t>En hemmelighed under jorden Hvis krigen kommer</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2.dk</t>
+  </si>
+  <si>
+    <t>Endelig fri – apartheidens mange hemmeligheder</t>
+  </si>
+  <si>
+    <t>Europas vidundere</t>
+  </si>
+  <si>
+    <t>Europas vidundere III (3:4) Tower of London</t>
+  </si>
+  <si>
+    <t>Europas vidundere III (4:4) Wawelhøjen</t>
+  </si>
+  <si>
+    <t>Europas vidundere III Tower of London</t>
+  </si>
+  <si>
+    <t>Europas vidundere III Wawelhøjen</t>
+  </si>
+  <si>
+    <t>Eventyr i blinde</t>
+  </si>
+  <si>
+    <t>Eventyr i blinde (3:5) Musik i Cinque Terre</t>
+  </si>
+  <si>
+    <t>Eventyr i blinde Musik i Cinque Terre</t>
+  </si>
+  <si>
+    <t>Filmperler: Blue Bayou</t>
+  </si>
+  <si>
+    <t>Fjeldrytteren</t>
+  </si>
+  <si>
+    <t>Flugtrute</t>
+  </si>
+  <si>
+    <t>Flugtrute: DDR-Danmark</t>
+  </si>
+  <si>
+    <t>Flugtrute: DDR-Danmark (2:2)</t>
+  </si>
+  <si>
+    <t>Folk og fæ</t>
+  </si>
+  <si>
+    <t>Fortidens fantastiske ingeniørkunst</t>
+  </si>
+  <si>
+    <t>Fortidens fantastiske ingeniørkunst II (8:10) Skjulte vidundere</t>
+  </si>
+  <si>
+    <t>Fortidens fantastiske ingeniørkunst II (9:10) Oldtidens vandveje</t>
+  </si>
+  <si>
+    <t>Fortidens fantastiske ingeniørkunst II Oldtidens vandveje</t>
+  </si>
+  <si>
+    <t>Frank &amp; Kastaniegaarden</t>
+  </si>
+  <si>
+    <t>Frank &amp; Kastaniegaarden - Bønner og seerbesøg</t>
+  </si>
+  <si>
+    <t>Frank &amp; Kastaniegaarden - Korea (1:2)</t>
+  </si>
+  <si>
+    <t>dr1.dk</t>
+  </si>
+  <si>
+    <t>Frank And Kastaniegaarden - Bønner og seerbesøg</t>
+  </si>
+  <si>
+    <t>Frontlinje Grønland</t>
+  </si>
+  <si>
+    <t>Frontlinje Grønland - Minus 27 grader</t>
+  </si>
+  <si>
+    <t>DR1.dk; DR2.dk</t>
+  </si>
+  <si>
+    <t>Gudstjenesten</t>
+  </si>
+  <si>
+    <t>Hammerslag</t>
+  </si>
+  <si>
+    <t>Hammerslag 2021</t>
+  </si>
+  <si>
+    <t>Hammerslag 2021 - Til tops i København</t>
+  </si>
+  <si>
+    <t>Horisont</t>
+  </si>
+  <si>
+    <t>Husker du ... årtierne</t>
+  </si>
+  <si>
+    <t>Husker du...</t>
+  </si>
+  <si>
+    <t>Husker du... 1989</t>
+  </si>
+  <si>
+    <t>I haven med Søren Ryge</t>
+  </si>
+  <si>
+    <t>I haven med Søren Ryge: Havens træer</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk</t>
+  </si>
+  <si>
+    <t>Jagten på Danmarkshistorien</t>
+  </si>
+  <si>
+    <t>Jagten på Danmarkshistorien (1:7) Struensees sidste dans</t>
+  </si>
+  <si>
+    <t>Jagten på Danmarkshistorien Struensees sidste dans</t>
+  </si>
+  <si>
+    <t>Jordemoderen</t>
+  </si>
+  <si>
+    <t>Jordemoderen XII (7:8)</t>
+  </si>
+  <si>
+    <t>Jordemoderen XII (8:8)</t>
+  </si>
+  <si>
+    <t>Jorden Kalder</t>
+  </si>
+  <si>
+    <t>Jorden kalder</t>
+  </si>
+  <si>
+    <t>Jorden kalder: Er der håb for havet?</t>
+  </si>
+  <si>
+    <t>Kellys helte</t>
+  </si>
+  <si>
+    <t>Kender du typen?</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2018</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2018 - Med far til fire og Tintin</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2018 - Med mannequin og enarmet tyveknægt</t>
+  </si>
+  <si>
+    <t>Klostrets mørke hemmeligheder</t>
+  </si>
+  <si>
+    <t>Klostrets mørke hemmeligheder (3:4)</t>
+  </si>
+  <si>
+    <t>Knoglerne fra KZ-lejren</t>
+  </si>
+  <si>
+    <t>Knoglerne fra kz-lejren</t>
+  </si>
+  <si>
+    <t>Knoglerne fra kz-lejren: Den forsvundne modstandsmand</t>
+  </si>
+  <si>
+    <t>Knoglerne fra kz-lejren: Die Schlimmsten</t>
+  </si>
+  <si>
+    <t>Knoglerne fra kz-lejren: Svaret i brevet</t>
+  </si>
+  <si>
+    <t>Kodeknækkerne</t>
+  </si>
+  <si>
+    <t>Kodeknækkerne (5:8) Bandekoden</t>
+  </si>
+  <si>
+    <t>Kodeknækkerne Bandekoden</t>
+  </si>
+  <si>
+    <t>Kong Haakon: Norges nye konge</t>
+  </si>
+  <si>
+    <t>Kontinenterne</t>
+  </si>
+  <si>
+    <t>Kontinenterne (2:6) Asien</t>
+  </si>
+  <si>
+    <t>Kontinenterne (4:6) Europa</t>
+  </si>
+  <si>
+    <t>Kontinenterne Europa</t>
+  </si>
+  <si>
+    <t>Krigsmaskinen</t>
+  </si>
+  <si>
+    <t>Krigsmaskinen (2:4)</t>
+  </si>
+  <si>
+    <t>Kriminalinspektør Banks</t>
+  </si>
+  <si>
+    <t>Kriminalinspektør Banks: Understrøm</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby X (1)</t>
+  </si>
+  <si>
+    <t>Kunstnerkolonien</t>
+  </si>
+  <si>
+    <t>Kunstnerkolonien på Sydfyn</t>
+  </si>
+  <si>
+    <t>Kunstnerkolonien på Sydfyn (2:8)</t>
+  </si>
+  <si>
+    <t>Maria Wern</t>
+  </si>
+  <si>
+    <t>Maria Wern: Et tidligere liv</t>
+  </si>
+  <si>
+    <t>Maria Wern: Plads 89</t>
+  </si>
+  <si>
+    <t>Mennesket</t>
+  </si>
+  <si>
+    <t>Mens vi venter på at dø</t>
+  </si>
+  <si>
+    <t>dr2.dk</t>
+  </si>
+  <si>
+    <t>Mens vi venter på at dø - Pelser vi haven</t>
+  </si>
+  <si>
+    <t>Mig og 60'erne</t>
+  </si>
+  <si>
+    <t>Min fars krig</t>
+  </si>
+  <si>
+    <t>Min fars krig (1:3) Besættelsen</t>
+  </si>
+  <si>
+    <t>Min fars krig Besættelsen</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Mississippi i fortidens skygge</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Morgenandagten</t>
+  </si>
+  <si>
+    <t>Nak &amp; Æd</t>
+  </si>
+  <si>
+    <t>Nak &amp; Æd - en kanin på Endelave (1:8)</t>
+  </si>
+  <si>
+    <t>Nak &amp; Æd - en krokodille i Zambia</t>
+  </si>
+  <si>
+    <t>Nak And Æd - en krokodille i Zambia</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>Otte dage for Rom</t>
+  </si>
+  <si>
+    <t>Otte dage, der skabte Rom (5:8) Boudiccas hævn</t>
+  </si>
+  <si>
+    <t>Otte dage, der skabte Rom Boudiccas hævn</t>
+  </si>
+  <si>
+    <t>P2 Radioavisen</t>
+  </si>
+  <si>
+    <t>P3 Essensen</t>
+  </si>
+  <si>
+    <t>P3 Essensen - 3 attentater der ændrede verden</t>
+  </si>
+  <si>
+    <t>Parterapi</t>
+  </si>
+  <si>
+    <t>På roadtrip i Indokina</t>
+  </si>
+  <si>
+    <t>På roadtrip i Indokina (3:7)</t>
+  </si>
+  <si>
+    <t>På roadtrip i Indokina (4:7)</t>
+  </si>
+  <si>
+    <t>På skuldrene af H. C. Ørsted</t>
+  </si>
+  <si>
+    <t>På skuldrene af H. C. Ørsted - Kan mennesket skabe som en Gud?</t>
+  </si>
+  <si>
+    <t>Radioavisen</t>
+  </si>
+  <si>
+    <t>Rick Stein elsker mad</t>
+  </si>
+  <si>
+    <t>Rick Stein elsker mad (14:15)</t>
+  </si>
+  <si>
+    <t>RO PÅ i naturen</t>
+  </si>
+  <si>
+    <t>RO PÅ med DR Symfoniorkestret</t>
+  </si>
+  <si>
+    <t>RO PÅ med DR Symfoniorkestret: Lys over havet</t>
+  </si>
+  <si>
+    <t>Scavenius og Kær på tur i kunsthistorien</t>
+  </si>
+  <si>
+    <t>Scavenius og Kær på tur i kunsthistorien (3:4)</t>
+  </si>
+  <si>
+    <t>DR1.dk; DR2.dk; dr1.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Seneste nyt fra TVA</t>
+  </si>
+  <si>
+    <t>Skattejægerne</t>
+  </si>
+  <si>
+    <t>Skattejægerne (6:10)</t>
+  </si>
+  <si>
+    <t>Smagen af Italien</t>
+  </si>
+  <si>
+    <t>Smagen af Italien (4:6)</t>
+  </si>
+  <si>
+    <t>Sommeren 1985</t>
+  </si>
+  <si>
+    <t>Sommeren 1985 (6:6)</t>
+  </si>
+  <si>
+    <t>Spise med Price</t>
+  </si>
+  <si>
+    <t>Sportsmagasinet</t>
+  </si>
+  <si>
+    <t>Stikkeren</t>
+  </si>
+  <si>
+    <t>Stikkeren (1:3)</t>
+  </si>
+  <si>
+    <t>Stjerner og Striber</t>
+  </si>
+  <si>
+    <t>Storbritanniens smukke floder</t>
+  </si>
+  <si>
+    <t>Storbritanniens smukke floder (2:4)</t>
+  </si>
+  <si>
+    <t>Storbritanniens smukkeste floder</t>
+  </si>
+  <si>
+    <t>Store danskere</t>
+  </si>
+  <si>
+    <t>Store danskere - Tine Bryld</t>
+  </si>
+  <si>
+    <t>Så er der mad</t>
+  </si>
+  <si>
+    <t>Så er der mad - I den gode smags tjeneste (4:5)</t>
+  </si>
+  <si>
+    <t>Så er der mad - Verdens bedste (5:5)</t>
+  </si>
+  <si>
+    <t>Søren Ryge</t>
+  </si>
+  <si>
+    <t>Team Bachstad</t>
+  </si>
+  <si>
+    <t>Team Bachstad i Caribien</t>
+  </si>
+  <si>
+    <t>Team Bachstad i Caribien (5:7)</t>
+  </si>
+  <si>
+    <t>Team Bachstad i Caribien (6:7)</t>
+  </si>
+  <si>
+    <t>The Burial</t>
+  </si>
+  <si>
+    <t>The Capture</t>
+  </si>
+  <si>
+    <t>The Capture III (1:6)</t>
+  </si>
+  <si>
+    <t>The Dark</t>
+  </si>
+  <si>
+    <t>The Dark (2:6)</t>
+  </si>
+  <si>
+    <t>To hjerner, et lærred</t>
+  </si>
+  <si>
+    <t>Troldspejlet</t>
+  </si>
+  <si>
+    <t>Tuva &amp; Ronny - et lille hotel i Grækenland</t>
+  </si>
+  <si>
+    <t>Tuva og Ronnys græske hotel</t>
+  </si>
+  <si>
+    <t>Tuva og Ronnys græske hotel (10:12)</t>
+  </si>
+  <si>
+    <t>Tuva og Ronnys græske hotel (6:12)</t>
+  </si>
+  <si>
+    <t>Tuva og Ronnys græske hotel (9:12)</t>
+  </si>
+  <si>
+    <t>TVA</t>
+  </si>
+  <si>
+    <t>Udsendelsesophør</t>
+  </si>
+  <si>
+    <t>Uforglemt</t>
+  </si>
+  <si>
+    <t>Uforglemt: Mordet på Hayley Reid (3:3)</t>
+  </si>
+  <si>
+    <t>Undergrundsbanken</t>
+  </si>
+  <si>
+    <t>Verdenssituationen med Clement</t>
+  </si>
+  <si>
+    <t>Verdenssituationen med Clement: Er Sverige blevet dansk?</t>
+  </si>
+  <si>
+    <t>Vilde haver - gør det selv</t>
+  </si>
+  <si>
+    <t>Vilde haver - gør det selv: Sådan laver du vandhuller</t>
+  </si>
+  <si>
+    <t>DR1 HD (T).dk; DR1.dk</t>
+  </si>
+  <si>
+    <t>Vores planet</t>
+  </si>
+  <si>
+    <t>Vores planet III</t>
+  </si>
+  <si>
+    <t>Vores planet III (5:8)</t>
+  </si>
+  <si>
+    <t>Vores vejr</t>
+  </si>
+  <si>
+    <t>Vores Vejr</t>
+  </si>
+  <si>
+    <t>Vores år</t>
+  </si>
+  <si>
+    <t>Værtshushistorier</t>
+  </si>
+  <si>
+    <t>Værtshushistorier: Café Viking</t>
+  </si>
+  <si>
+    <t>ATP Tour Highlights.jpg</t>
+  </si>
+  <si>
+    <t>ATP-1000.jpg</t>
+  </si>
+  <si>
+    <t>Aften Paris Nice.jpg</t>
+  </si>
+  <si>
+    <t>Aften Roubaix.jpg</t>
+  </si>
+  <si>
+    <t>Aftentour.jpg</t>
+  </si>
+  <si>
+    <t>Atletik Diamond League.jpg</t>
+  </si>
+  <si>
+    <t>Badminton.jpg</t>
+  </si>
+  <si>
+    <t>Betinia Liga.jpg</t>
+  </si>
+  <si>
+    <t>BetiniaStudio.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga Review of the Midseason.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga Special.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga_2.jpg</t>
+  </si>
+  <si>
+    <t>Champions League Weekly.jpg</t>
+  </si>
+  <si>
+    <t>Champions League Weekly2.jpg</t>
+  </si>
+  <si>
+    <t>Champions League.jpg</t>
+  </si>
+  <si>
+    <t>Coupe-Davis.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Clásica San Sebastián.jpg</t>
+  </si>
+  <si>
+    <t>Cykling La Vuelta Femenina.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Paris Nice.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Polen Rundt.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Postnord Danmark Rundt.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour Auvergne Rhone-Alpes.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de France Femmes.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de France.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de France2.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de Romandie.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Volta.jpg</t>
+  </si>
+  <si>
+    <t>Cykling-generic.jpg</t>
+  </si>
+  <si>
+    <t>Cykling-generic2.jpg</t>
+  </si>
+  <si>
+    <t>Cykling.jpg</t>
+  </si>
+  <si>
+    <t>DP World Tour Danish Golf Championship.jpg</t>
+  </si>
+  <si>
+    <t>Danskerklubben.jpg</t>
+  </si>
+  <si>
+    <t>Danskerklubben2.jpg</t>
+  </si>
+  <si>
+    <t>Davis Cup.jpg</t>
+  </si>
+  <si>
+    <t>EFL Championship Highligts.jpg</t>
+  </si>
+  <si>
+    <t>EM i atletik.jpg</t>
+  </si>
+  <si>
+    <t>Endurance Car Racing.jpg</t>
+  </si>
+  <si>
+    <t>F1Q.JPG</t>
+  </si>
+  <si>
+    <t>F1T.JPG</t>
+  </si>
+  <si>
+    <t>FIA World Endurance Championship.jpg</t>
+  </si>
+  <si>
+    <t>Fodbold Friuli Venezia Giulia Cup - Kampe.jpg</t>
+  </si>
+  <si>
+    <t>Fodbold Serie A.jpg</t>
+  </si>
+  <si>
+    <t>Formel 1 Belgien Grand Prix.jpg</t>
+  </si>
+  <si>
+    <t>Formel 1.jpg</t>
+  </si>
+  <si>
+    <t>Formel E VM.jpg</t>
+  </si>
+  <si>
+    <t>Golf LPGA Tour.jpg</t>
+  </si>
+  <si>
+    <t>Golf PGA Champions Tour.jpg</t>
+  </si>
+  <si>
+    <t>Golf PGA Tour.jpg</t>
+  </si>
+  <si>
+    <t>Håndbold  Golden League.jpg</t>
+  </si>
+  <si>
+    <t>Håndbold Kvindeligaen.jpg</t>
+  </si>
+  <si>
+    <t>Højdepunkter fra Dansk Motorsport1.jpg</t>
+  </si>
+  <si>
+    <t>IndyCar1.jpg</t>
+  </si>
+  <si>
+    <t>Le Mans.jpg</t>
+  </si>
+  <si>
+    <t>League Cup.jpg</t>
+  </si>
+  <si>
+    <t>Ligue 1 The Season Review Show.jpg</t>
+  </si>
+  <si>
+    <t>Ligue1.jpg</t>
+  </si>
+  <si>
+    <t>MotoGP.jpg</t>
+  </si>
+  <si>
+    <t>MotoGp Season Review.jpg</t>
+  </si>
+  <si>
+    <t>Motocross.jpg</t>
+  </si>
+  <si>
+    <t>Motorsport-generic.jpg</t>
+  </si>
+  <si>
+    <t>Målfesten.jpg</t>
+  </si>
+  <si>
+    <t>NFL Gameday.jpg</t>
+  </si>
+  <si>
+    <t>NFL2.jpg</t>
+  </si>
+  <si>
+    <t>PDC European Tour.jpg</t>
+  </si>
+  <si>
+    <t>PDC World Series of Darts.jpg</t>
+  </si>
+  <si>
+    <t>Pokal-highligts.jpg</t>
+  </si>
+  <si>
+    <t>Pokalkampe.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Goals of the Season.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Netbusters.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Preview.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Review of the Season.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Review.jpg</t>
+  </si>
+  <si>
+    <t>Premier League-studiet.jpg</t>
+  </si>
+  <si>
+    <t>RaceTV_DK.jpg</t>
+  </si>
+  <si>
+    <t>Skisport.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports Deadline Day.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports Fan Club.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports Soccer Saturday.jpg</t>
+  </si>
+  <si>
+    <t>Snooker.jpg</t>
+  </si>
+  <si>
+    <t>Speedway FIM Speedway Grand Prix.jpg</t>
+  </si>
+  <si>
+    <t>Sporten.jpg</t>
+  </si>
+  <si>
+    <t>Spot på Betinia Liga.jpg</t>
+  </si>
+  <si>
+    <t>Superligaens Topchefer.jpg</t>
+  </si>
+  <si>
     <t>TV_2_Sport_X.jpg</t>
   </si>
   <si>
-    <t>Serie A: Napoli-Bologna</t>
-  </si>
-  <si>
-    <t>Sæt pris på Danmark</t>
-  </si>
-  <si>
-    <t>Til salg i 100 år</t>
-  </si>
-  <si>
-    <t>Vuelta a España: 20. etape</t>
-  </si>
-  <si>
-    <t>Vuelta a España: 21. etape</t>
-  </si>
-  <si>
-    <t>Vuelta a España: Studiet</t>
-  </si>
-  <si>
-    <t>Vuelta a España -  Studiet.jpg</t>
-  </si>
-  <si>
-    <t>C - DR1/DR2</t>
-  </si>
-  <si>
-    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk</t>
-  </si>
-  <si>
-    <t>24 timer vi aldrig glemmer</t>
-  </si>
-  <si>
-    <t>DR2.dk; dr2.dk</t>
-  </si>
-  <si>
-    <t>24 timer vi aldrig glemmer - 11. september 2001</t>
-  </si>
-  <si>
-    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk; dr1.dk</t>
-  </si>
-  <si>
-    <t>Aftenshowet</t>
-  </si>
-  <si>
-    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk</t>
-  </si>
-  <si>
-    <t>Alene i vildmarken Australien</t>
-  </si>
-  <si>
-    <t>DR1.dk; dr1.dk</t>
-  </si>
-  <si>
-    <t>Alene i vildmarken Australien II (3:11)</t>
-  </si>
-  <si>
-    <t>DR1.dk</t>
-  </si>
-  <si>
-    <t>Alene i vildmarken Australien II (4:11)</t>
-  </si>
-  <si>
-    <t>Alene i vildmarken USA</t>
-  </si>
-  <si>
-    <t>DR2.dk</t>
-  </si>
-  <si>
-    <t>Alt forladt</t>
-  </si>
-  <si>
-    <t>Alt forladt - Elhøj og Kirckhoff i det glemte Danmark</t>
-  </si>
-  <si>
-    <t>Alt forladt - Mønsted Kalkgruber</t>
-  </si>
-  <si>
-    <t>Antikkrejlerne med kendisser</t>
-  </si>
-  <si>
-    <t>Antikkrejlerne med kendisser (225)</t>
-  </si>
-  <si>
-    <t>Antikkrejlerne med kendisser (226)</t>
-  </si>
-  <si>
-    <t>Antikkrejlerne med kendisser (229)</t>
-  </si>
-  <si>
-    <t>Antikkrejlerne med kendisser (230)</t>
-  </si>
-  <si>
-    <t>Arrene fra apartheid (3:3)</t>
-  </si>
-  <si>
-    <t>DR1 Denmark (DK,DA).dk; DR1.dk</t>
-  </si>
-  <si>
-    <t>Beck</t>
-  </si>
-  <si>
-    <t>Beck: Djævelens advokat</t>
-  </si>
-  <si>
-    <t>Bjerget</t>
-  </si>
-  <si>
-    <t>Blue Bayou</t>
-  </si>
-  <si>
-    <t>Danmarkshistorien fortalt af Erik Kjersgaard</t>
-  </si>
-  <si>
-    <t>Danmarkshistorien fortalt af Erik Kjersgaard (2:12)</t>
-  </si>
-  <si>
-    <t>Dansk teater 300 år</t>
-  </si>
-  <si>
-    <t>Dansk teater 300 år: Teatergalskaben</t>
-  </si>
-  <si>
-    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk</t>
-  </si>
-  <si>
-    <t>Danske spioner i den kolde krig</t>
-  </si>
-  <si>
-    <t>Danske spioner i den kolde krig (2:4) Bag fjendens linjer</t>
-  </si>
-  <si>
-    <t>Danske spioner i den kolde krig Bag fjendens linjer</t>
-  </si>
-  <si>
-    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk; DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk; dr1.dk; dr2.dk</t>
-  </si>
-  <si>
-    <t>Deadline</t>
-  </si>
-  <si>
-    <t>Deadline: Hvorfor bliver børnene dummere?</t>
-  </si>
-  <si>
-    <t>Deadline: Kan man slutte fred med Putin?</t>
-  </si>
-  <si>
-    <t>Den klassiske musikquiz</t>
-  </si>
-  <si>
-    <t>Den klassiske musikquiz (7:8)</t>
-  </si>
-  <si>
-    <t>Den sidste fest</t>
-  </si>
-  <si>
-    <t>Den sidste fest (3:4) - 0,03 sekunder</t>
-  </si>
-  <si>
-    <t>Den sidste sommer med fred</t>
-  </si>
-  <si>
-    <t>Den store bagedyst</t>
-  </si>
-  <si>
-    <t>Dengang vi var bønder</t>
-  </si>
-  <si>
-    <t>Dengang vi var bønder (1:6)</t>
-  </si>
-  <si>
-    <t>Dengang vi var bønder (2:6)</t>
-  </si>
-  <si>
-    <t>Det danske madmirakel</t>
-  </si>
-  <si>
-    <t>Det danske madmirakel (3:4) Verdens bedste kokke</t>
-  </si>
-  <si>
-    <t>Det danske madmirakel Verdens bedste kokke</t>
-  </si>
-  <si>
-    <t>Dokument indefra: Stikkeren</t>
-  </si>
-  <si>
-    <t>Drømmen om et liv på landet</t>
-  </si>
-  <si>
-    <t>Dyrenes Danmark</t>
-  </si>
-  <si>
-    <t>En bedrager uden nåde</t>
-  </si>
-  <si>
-    <t>En bedrager uden nåde (3:4)</t>
-  </si>
-  <si>
-    <t>En hemmelighed under jorden</t>
-  </si>
-  <si>
-    <t>En hemmelighed under jorden (3:5) Hvis krigen kommer</t>
-  </si>
-  <si>
-    <t>En hemmelighed under jorden Hvis krigen kommer</t>
-  </si>
-  <si>
-    <t>DR2 Denmark (DK,DA).dk; DR2.dk</t>
-  </si>
-  <si>
-    <t>Endelig fri – apartheidens mange hemmeligheder</t>
-  </si>
-  <si>
-    <t>Europas vidundere</t>
-  </si>
-  <si>
-    <t>Europas vidundere III (3:4) Tower of London</t>
-  </si>
-  <si>
-    <t>Europas vidundere III (4:4) Wawelhøjen</t>
-  </si>
-  <si>
-    <t>Europas vidundere III Tower of London</t>
-  </si>
-  <si>
-    <t>Europas vidundere III Wawelhøjen</t>
-  </si>
-  <si>
-    <t>Eventyr i blinde</t>
-  </si>
-  <si>
-    <t>Eventyr i blinde (3:5) Musik i Cinque Terre</t>
-  </si>
-  <si>
-    <t>Eventyr i blinde Musik i Cinque Terre</t>
-  </si>
-  <si>
-    <t>Filmperler: Blue Bayou</t>
-  </si>
-  <si>
-    <t>Fjeldrytteren</t>
-  </si>
-  <si>
-    <t>Flugtrute</t>
-  </si>
-  <si>
-    <t>Flugtrute: DDR-Danmark</t>
-  </si>
-  <si>
-    <t>Flugtrute: DDR-Danmark (2:2)</t>
-  </si>
-  <si>
-    <t>Folk og fæ</t>
-  </si>
-  <si>
-    <t>Fortidens fantastiske ingeniørkunst</t>
-  </si>
-  <si>
-    <t>Fortidens fantastiske ingeniørkunst II (8:10) Skjulte vidundere</t>
-  </si>
-  <si>
-    <t>Fortidens fantastiske ingeniørkunst II (9:10) Oldtidens vandveje</t>
-  </si>
-  <si>
-    <t>Fortidens fantastiske ingeniørkunst II Oldtidens vandveje</t>
-  </si>
-  <si>
-    <t>Frank &amp; Kastaniegaarden</t>
-  </si>
-  <si>
-    <t>Frank &amp; Kastaniegaarden - Bønner og seerbesøg</t>
-  </si>
-  <si>
-    <t>Frank &amp; Kastaniegaarden - Korea (1:2)</t>
-  </si>
-  <si>
-    <t>dr1.dk</t>
-  </si>
-  <si>
-    <t>Frank And Kastaniegaarden - Bønner og seerbesøg</t>
-  </si>
-  <si>
-    <t>Frontlinje Grønland</t>
-  </si>
-  <si>
-    <t>Frontlinje Grønland - Minus 27 grader</t>
-  </si>
-  <si>
-    <t>DR1.dk; DR2.dk</t>
-  </si>
-  <si>
-    <t>Gudstjenesten</t>
-  </si>
-  <si>
-    <t>Hammerslag</t>
-  </si>
-  <si>
-    <t>Hammerslag 2021</t>
-  </si>
-  <si>
-    <t>Hammerslag 2021 - Til tops i København</t>
-  </si>
-  <si>
-    <t>Horisont</t>
-  </si>
-  <si>
-    <t>Husker du ... årtierne</t>
-  </si>
-  <si>
-    <t>Husker du...</t>
-  </si>
-  <si>
-    <t>Husker du... 1989</t>
-  </si>
-  <si>
-    <t>I haven med Søren Ryge</t>
-  </si>
-  <si>
-    <t>I haven med Søren Ryge: Havens træer</t>
-  </si>
-  <si>
-    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk</t>
-  </si>
-  <si>
-    <t>Jagten på Danmarkshistorien</t>
-  </si>
-  <si>
-    <t>Jagten på Danmarkshistorien (1:7) Struensees sidste dans</t>
-  </si>
-  <si>
-    <t>Jagten på Danmarkshistorien Struensees sidste dans</t>
-  </si>
-  <si>
-    <t>Jordemoderen</t>
-  </si>
-  <si>
-    <t>Jordemoderen XII (7:8)</t>
-  </si>
-  <si>
-    <t>Jordemoderen XII (8:8)</t>
-  </si>
-  <si>
-    <t>Jorden Kalder</t>
-  </si>
-  <si>
-    <t>Jorden kalder</t>
-  </si>
-  <si>
-    <t>Jorden kalder: Er der håb for havet?</t>
-  </si>
-  <si>
-    <t>Kellys helte</t>
-  </si>
-  <si>
-    <t>Kender du typen?</t>
-  </si>
-  <si>
-    <t>Kender Du Typen? 2018</t>
-  </si>
-  <si>
-    <t>Kender Du Typen? 2018 - Med far til fire og Tintin</t>
-  </si>
-  <si>
-    <t>Kender Du Typen? 2018 - Med mannequin og enarmet tyveknægt</t>
-  </si>
-  <si>
-    <t>Klostrets mørke hemmeligheder</t>
-  </si>
-  <si>
-    <t>Klostrets mørke hemmeligheder (3:4)</t>
-  </si>
-  <si>
-    <t>Knoglerne fra KZ-lejren</t>
-  </si>
-  <si>
-    <t>Knoglerne fra kz-lejren</t>
-  </si>
-  <si>
-    <t>Knoglerne fra kz-lejren: Den forsvundne modstandsmand</t>
-  </si>
-  <si>
-    <t>Knoglerne fra kz-lejren: Die Schlimmsten</t>
-  </si>
-  <si>
-    <t>Knoglerne fra kz-lejren: Svaret i brevet</t>
-  </si>
-  <si>
-    <t>Kodeknækkerne</t>
-  </si>
-  <si>
-    <t>Kodeknækkerne (5:8) Bandekoden</t>
-  </si>
-  <si>
-    <t>Kodeknækkerne Bandekoden</t>
-  </si>
-  <si>
-    <t>Kong Haakon: Norges nye konge</t>
-  </si>
-  <si>
-    <t>Kontinenterne</t>
-  </si>
-  <si>
-    <t>Kontinenterne (2:6) Asien</t>
-  </si>
-  <si>
-    <t>Kontinenterne (4:6) Europa</t>
-  </si>
-  <si>
-    <t>Kontinenterne Europa</t>
-  </si>
-  <si>
-    <t>Krigsmaskinen</t>
-  </si>
-  <si>
-    <t>Krigsmaskinen (2:4)</t>
-  </si>
-  <si>
-    <t>Kriminalinspektør Banks</t>
-  </si>
-  <si>
-    <t>Kriminalinspektør Banks: Understrøm</t>
-  </si>
-  <si>
-    <t>Kriminalkommissær Barnaby</t>
-  </si>
-  <si>
-    <t>Kriminalkommissær Barnaby X (1)</t>
-  </si>
-  <si>
-    <t>Kunstnerkolonien</t>
-  </si>
-  <si>
-    <t>Kunstnerkolonien på Sydfyn</t>
-  </si>
-  <si>
-    <t>Kunstnerkolonien på Sydfyn (2:8)</t>
-  </si>
-  <si>
-    <t>Maria Wern</t>
-  </si>
-  <si>
-    <t>Maria Wern: Et tidligere liv</t>
-  </si>
-  <si>
-    <t>Maria Wern: Plads 89</t>
-  </si>
-  <si>
-    <t>Mennesket</t>
-  </si>
-  <si>
-    <t>Mens vi venter på at dø</t>
-  </si>
-  <si>
-    <t>dr2.dk</t>
-  </si>
-  <si>
-    <t>Mens vi venter på at dø - Pelser vi haven</t>
-  </si>
-  <si>
-    <t>Mig og 60'erne</t>
-  </si>
-  <si>
-    <t>Min fars krig</t>
-  </si>
-  <si>
-    <t>Min fars krig (1:3) Besættelsen</t>
-  </si>
-  <si>
-    <t>Min fars krig Besættelsen</t>
-  </si>
-  <si>
-    <t>DR2 Denmark (DK,DA).dk; DR2.dk; dr2.dk</t>
-  </si>
-  <si>
-    <t>Mississippi i fortidens skygge</t>
-  </si>
-  <si>
-    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk; dr2.dk</t>
-  </si>
-  <si>
-    <t>Morgenandagten</t>
-  </si>
-  <si>
-    <t>Nak &amp; Æd</t>
-  </si>
-  <si>
-    <t>Nak &amp; Æd - en kanin på Endelave (1:8)</t>
-  </si>
-  <si>
-    <t>Nak &amp; Æd - en krokodille i Zambia</t>
-  </si>
-  <si>
-    <t>Nak And Æd - en krokodille i Zambia</t>
-  </si>
-  <si>
-    <t>OBS</t>
-  </si>
-  <si>
-    <t>Otte dage for Rom</t>
-  </si>
-  <si>
-    <t>Otte dage, der skabte Rom (5:8) Boudiccas hævn</t>
-  </si>
-  <si>
-    <t>Otte dage, der skabte Rom Boudiccas hævn</t>
-  </si>
-  <si>
-    <t>P2 Radioavisen</t>
-  </si>
-  <si>
-    <t>P3 Essensen</t>
-  </si>
-  <si>
-    <t>P3 Essensen - 3 attentater der ændrede verden</t>
-  </si>
-  <si>
-    <t>Parterapi</t>
-  </si>
-  <si>
-    <t>På roadtrip i Indokina</t>
-  </si>
-  <si>
-    <t>På roadtrip i Indokina (3:7)</t>
-  </si>
-  <si>
-    <t>På roadtrip i Indokina (4:7)</t>
-  </si>
-  <si>
-    <t>På skuldrene af H. C. Ørsted</t>
-  </si>
-  <si>
-    <t>På skuldrene af H. C. Ørsted - Kan mennesket skabe som en Gud?</t>
-  </si>
-  <si>
-    <t>Radioavisen</t>
-  </si>
-  <si>
-    <t>Rick Stein elsker mad</t>
-  </si>
-  <si>
-    <t>Rick Stein elsker mad (14:15)</t>
-  </si>
-  <si>
-    <t>RO PÅ i naturen</t>
-  </si>
-  <si>
-    <t>RO PÅ med DR Symfoniorkestret</t>
-  </si>
-  <si>
-    <t>RO PÅ med DR Symfoniorkestret: Lys over havet</t>
-  </si>
-  <si>
-    <t>Scavenius og Kær på tur i kunsthistorien</t>
-  </si>
-  <si>
-    <t>Scavenius og Kær på tur i kunsthistorien (3:4)</t>
-  </si>
-  <si>
-    <t>DR1.dk; DR2.dk; dr1.dk; dr2.dk</t>
-  </si>
-  <si>
-    <t>Seneste nyt fra TVA</t>
-  </si>
-  <si>
-    <t>Skattejægerne</t>
-  </si>
-  <si>
-    <t>Skattejægerne (6:10)</t>
-  </si>
-  <si>
-    <t>Smagen af Italien</t>
-  </si>
-  <si>
-    <t>Smagen af Italien (4:6)</t>
-  </si>
-  <si>
-    <t>Sommeren 1985</t>
-  </si>
-  <si>
-    <t>Sommeren 1985 (6:6)</t>
-  </si>
-  <si>
-    <t>Spise med Price</t>
-  </si>
-  <si>
-    <t>Sportsmagasinet</t>
-  </si>
-  <si>
-    <t>Stikkeren</t>
-  </si>
-  <si>
-    <t>Stikkeren (1:3)</t>
-  </si>
-  <si>
-    <t>Stjerner og Striber</t>
-  </si>
-  <si>
-    <t>Storbritanniens smukke floder</t>
-  </si>
-  <si>
-    <t>Storbritanniens smukke floder (2:4)</t>
-  </si>
-  <si>
-    <t>Storbritanniens smukkeste floder</t>
-  </si>
-  <si>
-    <t>Store danskere</t>
-  </si>
-  <si>
-    <t>Store danskere - Tine Bryld</t>
-  </si>
-  <si>
-    <t>Så er der mad</t>
-  </si>
-  <si>
-    <t>Så er der mad - I den gode smags tjeneste (4:5)</t>
-  </si>
-  <si>
-    <t>Så er der mad - Verdens bedste (5:5)</t>
-  </si>
-  <si>
-    <t>Søren Ryge</t>
-  </si>
-  <si>
-    <t>Team Bachstad</t>
-  </si>
-  <si>
-    <t>Team Bachstad i Caribien</t>
-  </si>
-  <si>
-    <t>Team Bachstad i Caribien (5:7)</t>
-  </si>
-  <si>
-    <t>Team Bachstad i Caribien (6:7)</t>
-  </si>
-  <si>
-    <t>The Burial</t>
-  </si>
-  <si>
-    <t>The Capture</t>
-  </si>
-  <si>
-    <t>The Capture III (1:6)</t>
-  </si>
-  <si>
-    <t>The Dark</t>
-  </si>
-  <si>
-    <t>The Dark (2:6)</t>
-  </si>
-  <si>
-    <t>To hjerner, et lærred</t>
-  </si>
-  <si>
-    <t>Troldspejlet</t>
-  </si>
-  <si>
-    <t>Tuva &amp; Ronny - et lille hotel i Grækenland</t>
-  </si>
-  <si>
-    <t>Tuva og Ronnys græske hotel</t>
-  </si>
-  <si>
-    <t>Tuva og Ronnys græske hotel (10:12)</t>
-  </si>
-  <si>
-    <t>Tuva og Ronnys græske hotel (6:12)</t>
-  </si>
-  <si>
-    <t>Tuva og Ronnys græske hotel (9:12)</t>
-  </si>
-  <si>
-    <t>TVA</t>
-  </si>
-  <si>
-    <t>Udsendelsesophør</t>
-  </si>
-  <si>
-    <t>Uforglemt</t>
-  </si>
-  <si>
-    <t>Uforglemt: Mordet på Hayley Reid (3:3)</t>
-  </si>
-  <si>
-    <t>Undergrundsbanken</t>
-  </si>
-  <si>
-    <t>Verdenssituationen med Clement</t>
-  </si>
-  <si>
-    <t>Verdenssituationen med Clement: Er Sverige blevet dansk?</t>
-  </si>
-  <si>
-    <t>Vilde haver - gør det selv</t>
-  </si>
-  <si>
-    <t>Vilde haver - gør det selv: Sådan laver du vandhuller</t>
-  </si>
-  <si>
-    <t>DR1 HD (T).dk; DR1.dk</t>
-  </si>
-  <si>
-    <t>Vores planet</t>
-  </si>
-  <si>
-    <t>Vores planet III</t>
-  </si>
-  <si>
-    <t>Vores planet III (5:8)</t>
-  </si>
-  <si>
-    <t>Vores vejr</t>
-  </si>
-  <si>
-    <t>Vores Vejr</t>
-  </si>
-  <si>
-    <t>Vores år</t>
-  </si>
-  <si>
-    <t>Værtshushistorier</t>
-  </si>
-  <si>
-    <t>Værtshushistorier: Café Viking</t>
-  </si>
-  <si>
-    <t>ATP Tour Highlights.jpg</t>
-  </si>
-  <si>
-    <t>ATP-1000.jpg</t>
-  </si>
-  <si>
-    <t>Aften Paris Nice.jpg</t>
-  </si>
-  <si>
-    <t>Aften Roubaix.jpg</t>
-  </si>
-  <si>
-    <t>Aftentour.jpg</t>
-  </si>
-  <si>
-    <t>Atletik Diamond League.jpg</t>
-  </si>
-  <si>
-    <t>Badminton.jpg</t>
-  </si>
-  <si>
-    <t>Betinia Liga.jpg</t>
-  </si>
-  <si>
-    <t>BetiniaStudio.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga Review of the Midseason.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga Special.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga_2.jpg</t>
-  </si>
-  <si>
-    <t>Champions League Weekly.jpg</t>
-  </si>
-  <si>
-    <t>Champions League Weekly2.jpg</t>
-  </si>
-  <si>
-    <t>Champions League.jpg</t>
-  </si>
-  <si>
-    <t>Coupe-Davis.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Clásica San Sebastián.jpg</t>
-  </si>
-  <si>
-    <t>Cykling La Vuelta Femenina.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Paris Nice.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Polen Rundt.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Postnord Danmark Rundt.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour Auvergne Rhone-Alpes.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de France Femmes.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de France.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de France2.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de Romandie.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Volta.jpg</t>
-  </si>
-  <si>
-    <t>Cykling-generic.jpg</t>
-  </si>
-  <si>
-    <t>Cykling-generic2.jpg</t>
-  </si>
-  <si>
-    <t>Cykling.jpg</t>
-  </si>
-  <si>
-    <t>DP World Tour Danish Golf Championship.jpg</t>
-  </si>
-  <si>
-    <t>Danskerklubben.jpg</t>
-  </si>
-  <si>
-    <t>Danskerklubben2.jpg</t>
-  </si>
-  <si>
-    <t>Davis Cup.jpg</t>
-  </si>
-  <si>
-    <t>EFL Championship Highligts.jpg</t>
-  </si>
-  <si>
-    <t>EFL Championship.jpg</t>
-  </si>
-  <si>
-    <t>EM i atletik.jpg</t>
-  </si>
-  <si>
-    <t>Endurance Car Racing.jpg</t>
-  </si>
-  <si>
-    <t>F1Q.JPG</t>
-  </si>
-  <si>
-    <t>F1T.JPG</t>
-  </si>
-  <si>
-    <t>FIA World Endurance Championship.jpg</t>
-  </si>
-  <si>
-    <t>Fodbold Friuli Venezia Giulia Cup - Kampe.jpg</t>
-  </si>
-  <si>
-    <t>Fodbold Serie A.jpg</t>
-  </si>
-  <si>
-    <t>Formel 1 Belgien Grand Prix.jpg</t>
-  </si>
-  <si>
-    <t>Formel 1.jpg</t>
-  </si>
-  <si>
-    <t>Formel E VM.jpg</t>
-  </si>
-  <si>
-    <t>Golf LPGA Tour.jpg</t>
-  </si>
-  <si>
-    <t>Golf PGA Champions Tour.jpg</t>
-  </si>
-  <si>
-    <t>Golf PGA Tour.jpg</t>
-  </si>
-  <si>
-    <t>Håndbold  Golden League.jpg</t>
-  </si>
-  <si>
-    <t>Håndbold Kvindeligaen.jpg</t>
-  </si>
-  <si>
-    <t>Højdepunkter fra Dansk Motorsport1.jpg</t>
-  </si>
-  <si>
-    <t>IndyCar1.jpg</t>
-  </si>
-  <si>
-    <t>Le Mans.jpg</t>
-  </si>
-  <si>
-    <t>Ligue 1 The Season Review Show.jpg</t>
-  </si>
-  <si>
-    <t>Ligue1.jpg</t>
-  </si>
-  <si>
-    <t>MotoGP.jpg</t>
-  </si>
-  <si>
-    <t>MotoGp Season Review.jpg</t>
-  </si>
-  <si>
-    <t>Motocross.jpg</t>
-  </si>
-  <si>
-    <t>Motorsport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Målfesten.jpg</t>
-  </si>
-  <si>
-    <t>NFL Gameday.jpg</t>
-  </si>
-  <si>
-    <t>NFL2.jpg</t>
-  </si>
-  <si>
-    <t>PDC European Tour.jpg</t>
-  </si>
-  <si>
-    <t>PDC World Series of Darts.jpg</t>
-  </si>
-  <si>
-    <t>Pokal-highligts.jpg</t>
-  </si>
-  <si>
-    <t>Pokalkampe.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Goals of the Season.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Netbusters.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Preview.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Review of the Season.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Review.jpg</t>
-  </si>
-  <si>
-    <t>Premier League-studiet.jpg</t>
-  </si>
-  <si>
-    <t>RaceTV_DK.jpg</t>
-  </si>
-  <si>
-    <t>Skisport.jpg</t>
-  </si>
-  <si>
-    <t>Sky Sports Deadline Day.jpg</t>
-  </si>
-  <si>
-    <t>Sky Sports Fan Club.jpg</t>
-  </si>
-  <si>
-    <t>Sky Sports Soccer Saturday.jpg</t>
-  </si>
-  <si>
-    <t>Snooker.jpg</t>
-  </si>
-  <si>
-    <t>Speedway FIM Speedway Grand Prix.jpg</t>
-  </si>
-  <si>
-    <t>Sporten.jpg</t>
-  </si>
-  <si>
-    <t>Spot på Betinia Liga.jpg</t>
-  </si>
-  <si>
     <t>Tennis ATP 1000.jpg</t>
   </si>
   <si>
@@ -1746,117 +1751,6 @@
   </si>
   <si>
     <t>tv3sport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Tidligere valgt billede</t>
-  </si>
-  <si>
-    <t>3F Superliga: FC Nordsjælland - AGF</t>
-  </si>
-  <si>
-    <t>Betinia LIGA</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Dortmund – Paderborn</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Elversberg - Bayern München</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: FC Köln - Werder Bremen</t>
-  </si>
-  <si>
-    <t>Bundesliga Highlights I: Bundesliga Highlights</t>
-  </si>
-  <si>
-    <t>Bundesliga Saturday Highlights: Bundesliga Highlights</t>
-  </si>
-  <si>
-    <t>Bundesliga: Dortmund – Paderborn</t>
-  </si>
-  <si>
-    <t>Bundesliga: Elversberg - Bayern München</t>
-  </si>
-  <si>
-    <t>Bundesliga: FC Köln - Werder Bremen</t>
-  </si>
-  <si>
-    <t>Champions Hockey League: Eisbären Berlin - Herning Blue Fox</t>
-  </si>
-  <si>
-    <t>Champions League Weekly: UEFA Champions League Weekly</t>
-  </si>
-  <si>
-    <t>Danskerklubben</t>
-  </si>
-  <si>
-    <t>EFL Championship Highlights</t>
-  </si>
-  <si>
-    <t>F1 Qualification: Spaniens Grand Prix - Kvalifikation</t>
-  </si>
-  <si>
-    <t>F2: Spaniens Grand Prix - Feature Race</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>F3: Spaniens Grand Prix - Feature Race</t>
-  </si>
-  <si>
-    <t>F3: Spaniens Grand Prix - Sprint Race</t>
-  </si>
-  <si>
-    <t>Formel 1 Studie: Spaniens Grand Prix - Løbet</t>
-  </si>
-  <si>
-    <t>Formel 1: Spaniens Grand Prix - Løbet</t>
-  </si>
-  <si>
-    <t>Formula 2: Chasing the Dream: Chasing the Dream - Madrid</t>
-  </si>
-  <si>
-    <t>Ligue 1: Brest - Paris Saint-Germain</t>
-  </si>
-  <si>
-    <t>PDC European Tour: Flanders Darts Trophy</t>
-  </si>
-  <si>
-    <t>Premier League: Coventry - Brighton</t>
-  </si>
-  <si>
-    <t>Superliga Studie: Lyngby BK - Sønderjyske Fodbold</t>
-  </si>
-  <si>
-    <t>Superliga: Lyngby Boldklub - Sønderjyske Fodbold</t>
-  </si>
-  <si>
-    <t>UEFA Champions League</t>
-  </si>
-  <si>
-    <t>A-Liga: Målfesten</t>
-  </si>
-  <si>
-    <t>ATP Tour Highlights</t>
-  </si>
-  <si>
-    <t>Atletik: Ultimate Championship - Studie</t>
-  </si>
-  <si>
-    <t>Cykling: Vuelta a España - Studiet</t>
-  </si>
-  <si>
-    <t>Herreligaen: Studiet</t>
-  </si>
-  <si>
-    <t>Serie A: Lazio-AC Milan</t>
-  </si>
-  <si>
-    <t>Serie A: Venezia-Fiorentina</t>
-  </si>
-  <si>
-    <t>Vuelta a España: 19. etape</t>
   </si>
   <si>
     <t>Sådan bruger du denne fil</t>
@@ -2341,13 +2235,13 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2355,19 +2249,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -2500,7 +2394,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -2517,7 +2411,7 @@
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
@@ -2534,7 +2428,7 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
@@ -2551,7 +2445,7 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
@@ -2568,7 +2462,7 @@
         <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -2585,7 +2479,7 @@
         <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -2602,7 +2496,7 @@
         <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
@@ -2619,7 +2513,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
         <v>20</v>
@@ -2636,7 +2530,7 @@
         <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
@@ -2653,7 +2547,7 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
@@ -2670,7 +2564,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
@@ -2687,7 +2581,7 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
@@ -2704,7 +2598,7 @@
         <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
         <v>20</v>
@@ -2721,7 +2615,7 @@
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
@@ -2738,7 +2632,7 @@
         <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
@@ -2752,10 +2646,10 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
@@ -2769,7 +2663,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
         <v>114</v>
@@ -2789,7 +2683,7 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
         <v>20</v>
@@ -2803,10 +2697,10 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
         <v>135</v>
-      </c>
-      <c r="C30" t="s">
-        <v>136</v>
       </c>
       <c r="D30" t="s">
         <v>20</v>
@@ -2820,7 +2714,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
         <v>137</v>
@@ -2837,10 +2731,10 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s">
         <v>20</v>
@@ -2854,7 +2748,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
         <v>142</v>
@@ -2868,13 +2762,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
         <v>20</v>
@@ -2885,13 +2779,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
         <v>20</v>
@@ -2902,13 +2796,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
         <v>20</v>
@@ -2919,13 +2813,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
         <v>20</v>
@@ -2936,13 +2830,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
         <v>20</v>
@@ -2953,13 +2847,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
@@ -2970,13 +2864,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
         <v>20</v>
@@ -2987,13 +2881,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
         <v>20</v>
@@ -3004,13 +2898,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
@@ -3021,13 +2915,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D43" t="s">
         <v>20</v>
@@ -3038,13 +2932,13 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D44" t="s">
         <v>20</v>
@@ -3055,13 +2949,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D45" t="s">
         <v>20</v>
@@ -3072,13 +2966,13 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
         <v>20</v>
@@ -3089,13 +2983,13 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D47" t="s">
         <v>20</v>
@@ -3106,13 +3000,13 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D48" t="s">
         <v>20</v>
@@ -3123,13 +3017,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B49" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D49" t="s">
         <v>20</v>
@@ -3140,16 +3034,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B50" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
@@ -3157,16 +3051,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B51" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D51" t="s">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
@@ -3174,13 +3068,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
@@ -3191,13 +3085,13 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D53" t="s">
         <v>20</v>
@@ -3208,13 +3102,13 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D54" t="s">
         <v>20</v>
@@ -3225,16 +3119,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D55" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
@@ -3242,16 +3136,16 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D56" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -3259,13 +3153,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B57" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D57" t="s">
         <v>20</v>
@@ -3276,13 +3170,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
@@ -3293,13 +3187,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="B59" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
@@ -3310,13 +3204,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="B60" t="s">
-        <v>233</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
@@ -3327,13 +3221,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="B61" t="s">
-        <v>235</v>
+        <v>152</v>
       </c>
       <c r="C61" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
@@ -3344,13 +3238,13 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="B62" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="C62" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
@@ -3361,13 +3255,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="B63" t="s">
-        <v>239</v>
+        <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D63" t="s">
         <v>20</v>
@@ -3378,13 +3272,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="B64" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="D64" t="s">
         <v>20</v>
@@ -3398,10 +3292,10 @@
         <v>230</v>
       </c>
       <c r="B65" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C65" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D65" t="s">
         <v>20</v>
@@ -3415,10 +3309,10 @@
         <v>230</v>
       </c>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C66" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
@@ -3432,10 +3326,10 @@
         <v>230</v>
       </c>
       <c r="B67" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C67" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
@@ -3449,10 +3343,10 @@
         <v>230</v>
       </c>
       <c r="B68" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C68" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
@@ -3466,10 +3360,10 @@
         <v>230</v>
       </c>
       <c r="B69" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C69" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
@@ -3483,10 +3377,10 @@
         <v>230</v>
       </c>
       <c r="B70" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C70" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
@@ -3503,7 +3397,7 @@
         <v>241</v>
       </c>
       <c r="C71" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
@@ -3517,10 +3411,10 @@
         <v>230</v>
       </c>
       <c r="B72" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C72" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D72" t="s">
         <v>20</v>
@@ -3534,10 +3428,10 @@
         <v>230</v>
       </c>
       <c r="B73" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C73" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D73" t="s">
         <v>20</v>
@@ -3551,10 +3445,10 @@
         <v>230</v>
       </c>
       <c r="B74" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C74" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D74" t="s">
         <v>20</v>
@@ -3568,10 +3462,10 @@
         <v>230</v>
       </c>
       <c r="B75" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D75" t="s">
         <v>20</v>
@@ -3588,7 +3482,7 @@
         <v>239</v>
       </c>
       <c r="C76" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D76" t="s">
         <v>20</v>
@@ -3605,7 +3499,7 @@
         <v>241</v>
       </c>
       <c r="C77" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D77" t="s">
         <v>20</v>
@@ -3619,10 +3513,10 @@
         <v>230</v>
       </c>
       <c r="B78" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C78" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D78" t="s">
         <v>20</v>
@@ -3636,10 +3530,10 @@
         <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D79" t="s">
         <v>20</v>
@@ -3653,10 +3547,10 @@
         <v>230</v>
       </c>
       <c r="B80" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C80" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
@@ -3670,10 +3564,10 @@
         <v>230</v>
       </c>
       <c r="B81" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C81" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D81" t="s">
         <v>20</v>
@@ -3687,10 +3581,10 @@
         <v>230</v>
       </c>
       <c r="B82" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C82" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D82" t="s">
         <v>20</v>
@@ -3704,10 +3598,10 @@
         <v>230</v>
       </c>
       <c r="B83" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="C83" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D83" t="s">
         <v>20</v>
@@ -3721,10 +3615,10 @@
         <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C84" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D84" t="s">
         <v>20</v>
@@ -3738,10 +3632,10 @@
         <v>230</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D85" t="s">
         <v>20</v>
@@ -3755,10 +3649,10 @@
         <v>230</v>
       </c>
       <c r="B86" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
@@ -3772,10 +3666,10 @@
         <v>230</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C87" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D87" t="s">
         <v>20</v>
@@ -3789,10 +3683,10 @@
         <v>230</v>
       </c>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C88" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>20</v>
@@ -3806,10 +3700,10 @@
         <v>230</v>
       </c>
       <c r="B89" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="C89" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D89" t="s">
         <v>20</v>
@@ -3826,7 +3720,7 @@
         <v>244</v>
       </c>
       <c r="C90" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D90" t="s">
         <v>20</v>
@@ -3840,10 +3734,10 @@
         <v>230</v>
       </c>
       <c r="B91" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C91" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D91" t="s">
         <v>20</v>
@@ -3857,10 +3751,10 @@
         <v>230</v>
       </c>
       <c r="B92" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="C92" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D92" t="s">
         <v>20</v>
@@ -3877,7 +3771,7 @@
         <v>244</v>
       </c>
       <c r="C93" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D93" t="s">
         <v>20</v>
@@ -3891,10 +3785,10 @@
         <v>230</v>
       </c>
       <c r="B94" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C94" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D94" t="s">
         <v>20</v>
@@ -3911,7 +3805,7 @@
         <v>231</v>
       </c>
       <c r="C95" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D95" t="s">
         <v>20</v>
@@ -3925,10 +3819,10 @@
         <v>230</v>
       </c>
       <c r="B96" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C96" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D96" t="s">
         <v>20</v>
@@ -3942,10 +3836,10 @@
         <v>230</v>
       </c>
       <c r="B97" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C97" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D97" t="s">
         <v>20</v>
@@ -3959,10 +3853,10 @@
         <v>230</v>
       </c>
       <c r="B98" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C98" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D98" t="s">
         <v>20</v>
@@ -3976,10 +3870,10 @@
         <v>230</v>
       </c>
       <c r="B99" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C99" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D99" t="s">
         <v>20</v>
@@ -3996,7 +3890,7 @@
         <v>241</v>
       </c>
       <c r="C100" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D100" t="s">
         <v>20</v>
@@ -4010,10 +3904,10 @@
         <v>230</v>
       </c>
       <c r="B101" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C101" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D101" t="s">
         <v>20</v>
@@ -4027,10 +3921,10 @@
         <v>230</v>
       </c>
       <c r="B102" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C102" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D102" t="s">
         <v>20</v>
@@ -4044,10 +3938,10 @@
         <v>230</v>
       </c>
       <c r="B103" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C103" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D103" t="s">
         <v>20</v>
@@ -4064,7 +3958,7 @@
         <v>237</v>
       </c>
       <c r="C104" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D104" t="s">
         <v>20</v>
@@ -4081,7 +3975,7 @@
         <v>239</v>
       </c>
       <c r="C105" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D105" t="s">
         <v>20</v>
@@ -4095,10 +3989,10 @@
         <v>230</v>
       </c>
       <c r="B106" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C106" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D106" t="s">
         <v>20</v>
@@ -4112,10 +4006,10 @@
         <v>230</v>
       </c>
       <c r="B107" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C107" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D107" t="s">
         <v>20</v>
@@ -4129,10 +4023,10 @@
         <v>230</v>
       </c>
       <c r="B108" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C108" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D108" t="s">
         <v>20</v>
@@ -4146,10 +4040,10 @@
         <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>291</v>
+        <v>241</v>
       </c>
       <c r="C109" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
@@ -4163,10 +4057,10 @@
         <v>230</v>
       </c>
       <c r="B110" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C110" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D110" t="s">
         <v>20</v>
@@ -4180,10 +4074,10 @@
         <v>230</v>
       </c>
       <c r="B111" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C111" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D111" t="s">
         <v>20</v>
@@ -4197,10 +4091,10 @@
         <v>230</v>
       </c>
       <c r="B112" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C112" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D112" t="s">
         <v>20</v>
@@ -4217,7 +4111,7 @@
         <v>244</v>
       </c>
       <c r="C113" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D113" t="s">
         <v>20</v>
@@ -4234,7 +4128,7 @@
         <v>244</v>
       </c>
       <c r="C114" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
@@ -4248,10 +4142,10 @@
         <v>230</v>
       </c>
       <c r="B115" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="C115" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D115" t="s">
         <v>20</v>
@@ -4265,10 +4159,10 @@
         <v>230</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C116" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D116" t="s">
         <v>20</v>
@@ -4282,10 +4176,10 @@
         <v>230</v>
       </c>
       <c r="B117" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C117" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D117" t="s">
         <v>20</v>
@@ -4299,10 +4193,10 @@
         <v>230</v>
       </c>
       <c r="B118" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C118" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D118" t="s">
         <v>20</v>
@@ -4316,10 +4210,10 @@
         <v>230</v>
       </c>
       <c r="B119" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C119" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D119" t="s">
         <v>20</v>
@@ -4336,7 +4230,7 @@
         <v>244</v>
       </c>
       <c r="C120" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D120" t="s">
         <v>20</v>
@@ -4350,10 +4244,10 @@
         <v>230</v>
       </c>
       <c r="B121" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="C121" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D121" t="s">
         <v>20</v>
@@ -4367,10 +4261,10 @@
         <v>230</v>
       </c>
       <c r="B122" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C122" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D122" t="s">
         <v>20</v>
@@ -4387,7 +4281,7 @@
         <v>241</v>
       </c>
       <c r="C123" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D123" t="s">
         <v>20</v>
@@ -4401,10 +4295,10 @@
         <v>230</v>
       </c>
       <c r="B124" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C124" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D124" t="s">
         <v>20</v>
@@ -4418,10 +4312,10 @@
         <v>230</v>
       </c>
       <c r="B125" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C125" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D125" t="s">
         <v>20</v>
@@ -4435,10 +4329,10 @@
         <v>230</v>
       </c>
       <c r="B126" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C126" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D126" t="s">
         <v>20</v>
@@ -4452,10 +4346,10 @@
         <v>230</v>
       </c>
       <c r="B127" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="C127" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D127" t="s">
         <v>20</v>
@@ -4469,10 +4363,10 @@
         <v>230</v>
       </c>
       <c r="B128" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C128" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D128" t="s">
         <v>20</v>
@@ -4489,7 +4383,7 @@
         <v>241</v>
       </c>
       <c r="C129" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D129" t="s">
         <v>20</v>
@@ -4503,10 +4397,10 @@
         <v>230</v>
       </c>
       <c r="B130" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C130" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D130" t="s">
         <v>20</v>
@@ -4520,10 +4414,10 @@
         <v>230</v>
       </c>
       <c r="B131" t="s">
-        <v>314</v>
+        <v>233</v>
       </c>
       <c r="C131" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D131" t="s">
         <v>20</v>
@@ -4537,10 +4431,10 @@
         <v>230</v>
       </c>
       <c r="B132" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C132" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="D132" t="s">
         <v>20</v>
@@ -4554,10 +4448,10 @@
         <v>230</v>
       </c>
       <c r="B133" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C133" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D133" t="s">
         <v>20</v>
@@ -4571,10 +4465,10 @@
         <v>230</v>
       </c>
       <c r="B134" t="s">
-        <v>318</v>
+        <v>237</v>
       </c>
       <c r="C134" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D134" t="s">
         <v>20</v>
@@ -4588,10 +4482,10 @@
         <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C135" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D135" t="s">
         <v>20</v>
@@ -4608,7 +4502,7 @@
         <v>241</v>
       </c>
       <c r="C136" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D136" t="s">
         <v>20</v>
@@ -4622,10 +4516,10 @@
         <v>230</v>
       </c>
       <c r="B137" t="s">
-        <v>239</v>
+        <v>314</v>
       </c>
       <c r="C137" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D137" t="s">
         <v>20</v>
@@ -4642,7 +4536,7 @@
         <v>237</v>
       </c>
       <c r="C138" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D138" t="s">
         <v>20</v>
@@ -4656,10 +4550,10 @@
         <v>230</v>
       </c>
       <c r="B139" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D139" t="s">
         <v>20</v>
@@ -4673,10 +4567,10 @@
         <v>230</v>
       </c>
       <c r="B140" t="s">
-        <v>244</v>
+        <v>318</v>
       </c>
       <c r="C140" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D140" t="s">
         <v>20</v>
@@ -4690,10 +4584,10 @@
         <v>230</v>
       </c>
       <c r="B141" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C141" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D141" t="s">
         <v>20</v>
@@ -4710,7 +4604,7 @@
         <v>241</v>
       </c>
       <c r="C142" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D142" t="s">
         <v>20</v>
@@ -4724,10 +4618,10 @@
         <v>230</v>
       </c>
       <c r="B143" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C143" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D143" t="s">
         <v>20</v>
@@ -4741,10 +4635,10 @@
         <v>230</v>
       </c>
       <c r="B144" t="s">
-        <v>329</v>
+        <v>237</v>
       </c>
       <c r="C144" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D144" t="s">
         <v>20</v>
@@ -4758,10 +4652,10 @@
         <v>230</v>
       </c>
       <c r="B145" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C145" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D145" t="s">
         <v>20</v>
@@ -4775,10 +4669,10 @@
         <v>230</v>
       </c>
       <c r="B146" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C146" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D146" t="s">
         <v>20</v>
@@ -4792,10 +4686,10 @@
         <v>230</v>
       </c>
       <c r="B147" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C147" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D147" t="s">
         <v>20</v>
@@ -4809,10 +4703,10 @@
         <v>230</v>
       </c>
       <c r="B148" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C148" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D148" t="s">
         <v>20</v>
@@ -4829,7 +4723,7 @@
         <v>241</v>
       </c>
       <c r="C149" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D149" t="s">
         <v>20</v>
@@ -4843,10 +4737,10 @@
         <v>230</v>
       </c>
       <c r="B150" t="s">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="C150" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D150" t="s">
         <v>20</v>
@@ -4863,7 +4757,7 @@
         <v>241</v>
       </c>
       <c r="C151" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D151" t="s">
         <v>20</v>
@@ -4880,7 +4774,7 @@
         <v>241</v>
       </c>
       <c r="C152" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D152" t="s">
         <v>20</v>
@@ -4894,10 +4788,10 @@
         <v>230</v>
       </c>
       <c r="B153" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C153" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D153" t="s">
         <v>20</v>
@@ -4911,10 +4805,10 @@
         <v>230</v>
       </c>
       <c r="B154" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C154" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D154" t="s">
         <v>20</v>
@@ -4931,7 +4825,7 @@
         <v>241</v>
       </c>
       <c r="C155" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D155" t="s">
         <v>20</v>
@@ -4945,10 +4839,10 @@
         <v>230</v>
       </c>
       <c r="B156" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C156" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D156" t="s">
         <v>20</v>
@@ -4962,10 +4856,10 @@
         <v>230</v>
       </c>
       <c r="B157" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C157" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D157" t="s">
         <v>20</v>
@@ -4979,10 +4873,10 @@
         <v>230</v>
       </c>
       <c r="B158" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C158" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D158" t="s">
         <v>20</v>
@@ -4996,10 +4890,10 @@
         <v>230</v>
       </c>
       <c r="B159" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C159" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D159" t="s">
         <v>20</v>
@@ -5013,10 +4907,10 @@
         <v>230</v>
       </c>
       <c r="B160" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D160" t="s">
         <v>20</v>
@@ -5030,10 +4924,10 @@
         <v>230</v>
       </c>
       <c r="B161" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C161" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D161" t="s">
         <v>20</v>
@@ -5047,10 +4941,10 @@
         <v>230</v>
       </c>
       <c r="B162" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C162" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D162" t="s">
         <v>20</v>
@@ -5064,10 +4958,10 @@
         <v>230</v>
       </c>
       <c r="B163" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C163" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D163" t="s">
         <v>20</v>
@@ -5081,10 +4975,10 @@
         <v>230</v>
       </c>
       <c r="B164" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C164" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D164" t="s">
         <v>20</v>
@@ -5098,10 +4992,10 @@
         <v>230</v>
       </c>
       <c r="B165" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C165" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D165" t="s">
         <v>20</v>
@@ -5115,10 +5009,10 @@
         <v>230</v>
       </c>
       <c r="B166" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C166" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D166" t="s">
         <v>20</v>
@@ -5135,7 +5029,7 @@
         <v>244</v>
       </c>
       <c r="C167" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D167" t="s">
         <v>20</v>
@@ -5149,10 +5043,10 @@
         <v>230</v>
       </c>
       <c r="B168" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C168" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D168" t="s">
         <v>20</v>
@@ -5166,10 +5060,10 @@
         <v>230</v>
       </c>
       <c r="B169" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C169" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D169" t="s">
         <v>20</v>
@@ -5186,7 +5080,7 @@
         <v>244</v>
       </c>
       <c r="C170" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D170" t="s">
         <v>20</v>
@@ -5200,10 +5094,10 @@
         <v>230</v>
       </c>
       <c r="B171" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C171" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
@@ -5217,10 +5111,10 @@
         <v>230</v>
       </c>
       <c r="B172" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C172" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D172" t="s">
         <v>20</v>
@@ -5234,10 +5128,10 @@
         <v>230</v>
       </c>
       <c r="B173" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C173" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D173" t="s">
         <v>20</v>
@@ -5251,10 +5145,10 @@
         <v>230</v>
       </c>
       <c r="B174" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C174" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D174" t="s">
         <v>20</v>
@@ -5268,10 +5162,10 @@
         <v>230</v>
       </c>
       <c r="B175" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C175" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D175" t="s">
         <v>20</v>
@@ -5285,10 +5179,10 @@
         <v>230</v>
       </c>
       <c r="B176" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C176" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D176" t="s">
         <v>20</v>
@@ -5302,10 +5196,10 @@
         <v>230</v>
       </c>
       <c r="B177" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C177" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D177" t="s">
         <v>20</v>
@@ -5319,10 +5213,10 @@
         <v>230</v>
       </c>
       <c r="B178" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C178" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D178" t="s">
         <v>20</v>
@@ -5339,7 +5233,7 @@
         <v>231</v>
       </c>
       <c r="C179" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D179" t="s">
         <v>20</v>
@@ -5356,7 +5250,7 @@
         <v>244</v>
       </c>
       <c r="C180" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D180" t="s">
         <v>20</v>
@@ -5370,10 +5264,10 @@
         <v>230</v>
       </c>
       <c r="B181" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C181" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D181" t="s">
         <v>20</v>
@@ -5387,10 +5281,10 @@
         <v>230</v>
       </c>
       <c r="B182" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C182" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D182" t="s">
         <v>20</v>
@@ -5404,10 +5298,10 @@
         <v>230</v>
       </c>
       <c r="B183" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C183" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D183" t="s">
         <v>20</v>
@@ -5424,7 +5318,7 @@
         <v>241</v>
       </c>
       <c r="C184" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D184" t="s">
         <v>20</v>
@@ -5438,10 +5332,10 @@
         <v>230</v>
       </c>
       <c r="B185" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C185" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D185" t="s">
         <v>20</v>
@@ -5458,7 +5352,7 @@
         <v>244</v>
       </c>
       <c r="C186" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D186" t="s">
         <v>20</v>
@@ -5472,10 +5366,10 @@
         <v>230</v>
       </c>
       <c r="B187" t="s">
-        <v>373</v>
+        <v>244</v>
       </c>
       <c r="C187" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D187" t="s">
         <v>20</v>
@@ -5489,10 +5383,10 @@
         <v>230</v>
       </c>
       <c r="B188" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C188" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D188" t="s">
         <v>20</v>
@@ -5506,10 +5400,10 @@
         <v>230</v>
       </c>
       <c r="B189" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="C189" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D189" t="s">
         <v>20</v>
@@ -5523,10 +5417,10 @@
         <v>230</v>
       </c>
       <c r="B190" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C190" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D190" t="s">
         <v>20</v>
@@ -5540,10 +5434,10 @@
         <v>230</v>
       </c>
       <c r="B191" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C191" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D191" t="s">
         <v>20</v>
@@ -5557,10 +5451,10 @@
         <v>230</v>
       </c>
       <c r="B192" t="s">
-        <v>379</v>
+        <v>244</v>
       </c>
       <c r="C192" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D192" t="s">
         <v>20</v>
@@ -5574,10 +5468,10 @@
         <v>230</v>
       </c>
       <c r="B193" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C193" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="D193" t="s">
         <v>20</v>
@@ -5591,10 +5485,10 @@
         <v>230</v>
       </c>
       <c r="B194" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C194" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D194" t="s">
         <v>20</v>
@@ -5608,10 +5502,10 @@
         <v>230</v>
       </c>
       <c r="B195" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C195" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D195" t="s">
         <v>20</v>
@@ -5625,10 +5519,10 @@
         <v>230</v>
       </c>
       <c r="B196" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C196" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D196" t="s">
         <v>20</v>
@@ -5642,10 +5536,10 @@
         <v>230</v>
       </c>
       <c r="B197" t="s">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="C197" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D197" t="s">
         <v>20</v>
@@ -5659,10 +5553,10 @@
         <v>230</v>
       </c>
       <c r="B198" t="s">
-        <v>235</v>
+        <v>379</v>
       </c>
       <c r="C198" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D198" t="s">
         <v>20</v>
@@ -5676,10 +5570,10 @@
         <v>230</v>
       </c>
       <c r="B199" t="s">
-        <v>263</v>
+        <v>381</v>
       </c>
       <c r="C199" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D199" t="s">
         <v>20</v>
@@ -5693,10 +5587,10 @@
         <v>230</v>
       </c>
       <c r="B200" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C200" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D200" t="s">
         <v>20</v>
@@ -5710,10 +5604,10 @@
         <v>230</v>
       </c>
       <c r="B201" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C201" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D201" t="s">
         <v>20</v>
@@ -5727,10 +5621,10 @@
         <v>230</v>
       </c>
       <c r="B202" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C202" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D202" t="s">
         <v>20</v>
@@ -5744,10 +5638,10 @@
         <v>230</v>
       </c>
       <c r="B203" t="s">
-        <v>237</v>
+        <v>314</v>
       </c>
       <c r="C203" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D203" t="s">
         <v>20</v>
@@ -5761,10 +5655,10 @@
         <v>230</v>
       </c>
       <c r="B204" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C204" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D204" t="s">
         <v>20</v>
@@ -5778,10 +5672,10 @@
         <v>230</v>
       </c>
       <c r="B205" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C205" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="D205" t="s">
         <v>20</v>
@@ -5795,10 +5689,10 @@
         <v>230</v>
       </c>
       <c r="B206" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C206" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D206" t="s">
         <v>20</v>
@@ -5812,10 +5706,10 @@
         <v>230</v>
       </c>
       <c r="B207" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C207" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D207" t="s">
         <v>20</v>
@@ -5829,10 +5723,10 @@
         <v>230</v>
       </c>
       <c r="B208" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D208" t="s">
         <v>20</v>
@@ -5846,10 +5740,10 @@
         <v>230</v>
       </c>
       <c r="B209" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C209" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D209" t="s">
         <v>20</v>
@@ -5863,10 +5757,10 @@
         <v>230</v>
       </c>
       <c r="B210" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C210" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D210" t="s">
         <v>20</v>
@@ -5880,10 +5774,10 @@
         <v>230</v>
       </c>
       <c r="B211" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C211" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D211" t="s">
         <v>20</v>
@@ -5897,10 +5791,10 @@
         <v>230</v>
       </c>
       <c r="B212" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C212" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D212" t="s">
         <v>20</v>
@@ -5914,10 +5808,10 @@
         <v>230</v>
       </c>
       <c r="B213" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C213" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D213" t="s">
         <v>20</v>
@@ -5931,10 +5825,10 @@
         <v>230</v>
       </c>
       <c r="B214" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C214" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D214" t="s">
         <v>20</v>
@@ -5948,10 +5842,10 @@
         <v>230</v>
       </c>
       <c r="B215" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C215" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D215" t="s">
         <v>20</v>
@@ -5968,7 +5862,7 @@
         <v>244</v>
       </c>
       <c r="C216" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D216" t="s">
         <v>20</v>
@@ -5982,10 +5876,10 @@
         <v>230</v>
       </c>
       <c r="B217" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C217" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D217" t="s">
         <v>20</v>
@@ -5999,10 +5893,10 @@
         <v>230</v>
       </c>
       <c r="B218" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C218" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D218" t="s">
         <v>20</v>
@@ -6016,10 +5910,10 @@
         <v>230</v>
       </c>
       <c r="B219" t="s">
-        <v>408</v>
+        <v>244</v>
       </c>
       <c r="C219" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D219" t="s">
         <v>20</v>
@@ -6033,10 +5927,10 @@
         <v>230</v>
       </c>
       <c r="B220" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C220" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D220" t="s">
         <v>20</v>
@@ -6050,10 +5944,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D221" t="s">
         <v>20</v>
@@ -6067,10 +5961,10 @@
         <v>230</v>
       </c>
       <c r="B222" t="s">
-        <v>291</v>
+        <v>244</v>
       </c>
       <c r="C222" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D222" t="s">
         <v>20</v>
@@ -6084,10 +5978,10 @@
         <v>230</v>
       </c>
       <c r="B223" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C223" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="D223" t="s">
         <v>20</v>
@@ -6101,10 +5995,10 @@
         <v>230</v>
       </c>
       <c r="B224" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C224" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D224" t="s">
         <v>20</v>
@@ -6118,10 +6012,10 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>314</v>
+        <v>408</v>
       </c>
       <c r="C225" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D225" t="s">
         <v>20</v>
@@ -6135,10 +6029,10 @@
         <v>230</v>
       </c>
       <c r="B226" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C226" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D226" t="s">
         <v>20</v>
@@ -6155,7 +6049,7 @@
         <v>241</v>
       </c>
       <c r="C227" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D227" t="s">
         <v>20</v>
@@ -6169,10 +6063,10 @@
         <v>230</v>
       </c>
       <c r="B228" t="s">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="C228" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D228" t="s">
         <v>20</v>
@@ -6186,10 +6080,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D229" t="s">
         <v>20</v>
@@ -6203,10 +6097,10 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C230" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D230" t="s">
         <v>20</v>
@@ -6220,10 +6114,10 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="C231" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D231" t="s">
         <v>20</v>
@@ -6237,10 +6131,10 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C232" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D232" t="s">
         <v>20</v>
@@ -6254,10 +6148,10 @@
         <v>230</v>
       </c>
       <c r="B233" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C233" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D233" t="s">
         <v>20</v>
@@ -6271,10 +6165,10 @@
         <v>230</v>
       </c>
       <c r="B234" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C234" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D234" t="s">
         <v>20</v>
@@ -6288,10 +6182,10 @@
         <v>230</v>
       </c>
       <c r="B235" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D235" t="s">
         <v>20</v>
@@ -6305,10 +6199,10 @@
         <v>230</v>
       </c>
       <c r="B236" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C236" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D236" t="s">
         <v>20</v>
@@ -6322,10 +6216,10 @@
         <v>230</v>
       </c>
       <c r="B237" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C237" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D237" t="s">
         <v>20</v>
@@ -6339,10 +6233,10 @@
         <v>230</v>
       </c>
       <c r="B238" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C238" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D238" t="s">
         <v>20</v>
@@ -6356,10 +6250,10 @@
         <v>230</v>
       </c>
       <c r="B239" t="s">
-        <v>329</v>
+        <v>231</v>
       </c>
       <c r="C239" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D239" t="s">
         <v>20</v>
@@ -6373,10 +6267,10 @@
         <v>230</v>
       </c>
       <c r="B240" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C240" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D240" t="s">
         <v>20</v>
@@ -6390,10 +6284,10 @@
         <v>230</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C241" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D241" t="s">
         <v>20</v>
@@ -6407,10 +6301,10 @@
         <v>230</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C242" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D242" t="s">
         <v>20</v>
@@ -6424,10 +6318,10 @@
         <v>230</v>
       </c>
       <c r="B243" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C243" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D243" t="s">
         <v>20</v>
@@ -6444,7 +6338,7 @@
         <v>233</v>
       </c>
       <c r="C244" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D244" t="s">
         <v>20</v>
@@ -6458,10 +6352,10 @@
         <v>230</v>
       </c>
       <c r="B245" t="s">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="C245" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D245" t="s">
         <v>20</v>
@@ -6475,10 +6369,10 @@
         <v>230</v>
       </c>
       <c r="B246" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C246" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D246" t="s">
         <v>20</v>
@@ -6492,10 +6386,10 @@
         <v>230</v>
       </c>
       <c r="B247" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C247" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D247" t="s">
         <v>20</v>
@@ -6512,7 +6406,7 @@
         <v>241</v>
       </c>
       <c r="C248" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D248" t="s">
         <v>20</v>
@@ -6526,10 +6420,10 @@
         <v>230</v>
       </c>
       <c r="B249" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C249" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D249" t="s">
         <v>20</v>
@@ -6543,10 +6437,10 @@
         <v>230</v>
       </c>
       <c r="B250" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C250" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D250" t="s">
         <v>20</v>
@@ -6563,7 +6457,7 @@
         <v>237</v>
       </c>
       <c r="C251" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D251" t="s">
         <v>20</v>
@@ -6577,10 +6471,10 @@
         <v>230</v>
       </c>
       <c r="B252" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C252" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D252" t="s">
         <v>20</v>
@@ -6594,10 +6488,10 @@
         <v>230</v>
       </c>
       <c r="B253" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C253" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="D253" t="s">
         <v>20</v>
@@ -6611,10 +6505,10 @@
         <v>230</v>
       </c>
       <c r="B254" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C254" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D254" t="s">
         <v>20</v>
@@ -6628,10 +6522,10 @@
         <v>230</v>
       </c>
       <c r="B255" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C255" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D255" t="s">
         <v>20</v>
@@ -6645,10 +6539,10 @@
         <v>230</v>
       </c>
       <c r="B256" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="C256" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D256" t="s">
         <v>20</v>
@@ -6662,10 +6556,10 @@
         <v>230</v>
       </c>
       <c r="B257" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C257" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D257" t="s">
         <v>20</v>
@@ -6679,10 +6573,10 @@
         <v>230</v>
       </c>
       <c r="B258" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C258" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D258" t="s">
         <v>20</v>
@@ -6696,10 +6590,10 @@
         <v>230</v>
       </c>
       <c r="B259" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C259" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D259" t="s">
         <v>20</v>
@@ -6713,10 +6607,10 @@
         <v>230</v>
       </c>
       <c r="B260" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C260" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D260" t="s">
         <v>20</v>
@@ -6730,10 +6624,10 @@
         <v>230</v>
       </c>
       <c r="B261" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C261" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D261" t="s">
         <v>20</v>
@@ -6747,10 +6641,10 @@
         <v>230</v>
       </c>
       <c r="B262" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="C262" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D262" t="s">
         <v>20</v>
@@ -6764,10 +6658,10 @@
         <v>230</v>
       </c>
       <c r="B263" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C263" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D263" t="s">
         <v>20</v>
@@ -6781,10 +6675,10 @@
         <v>230</v>
       </c>
       <c r="B264" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C264" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D264" t="s">
         <v>20</v>
@@ -6798,10 +6692,10 @@
         <v>230</v>
       </c>
       <c r="B265" t="s">
-        <v>455</v>
+        <v>239</v>
       </c>
       <c r="C265" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="D265" t="s">
         <v>20</v>
@@ -6815,10 +6709,10 @@
         <v>230</v>
       </c>
       <c r="B266" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C266" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="D266" t="s">
         <v>20</v>
@@ -6832,10 +6726,10 @@
         <v>230</v>
       </c>
       <c r="B267" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C267" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D267" t="s">
         <v>20</v>
@@ -6849,10 +6743,10 @@
         <v>230</v>
       </c>
       <c r="B268" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C268" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="D268" t="s">
         <v>20</v>
@@ -6866,10 +6760,10 @@
         <v>230</v>
       </c>
       <c r="B269" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C269" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="D269" t="s">
         <v>20</v>
@@ -6883,10 +6777,10 @@
         <v>230</v>
       </c>
       <c r="B270" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C270" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="D270" t="s">
         <v>20</v>
@@ -6900,10 +6794,10 @@
         <v>230</v>
       </c>
       <c r="B271" t="s">
-        <v>231</v>
+        <v>455</v>
       </c>
       <c r="C271" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D271" t="s">
         <v>20</v>
@@ -6917,306 +6811,303 @@
         <v>230</v>
       </c>
       <c r="B272" t="s">
+        <v>254</v>
+      </c>
+      <c r="C272" t="s">
+        <v>457</v>
+      </c>
+      <c r="D272" t="s">
+        <v>20</v>
+      </c>
+      <c r="G272" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>230</v>
+      </c>
+      <c r="B273" t="s">
+        <v>239</v>
+      </c>
+      <c r="C273" t="s">
+        <v>458</v>
+      </c>
+      <c r="D273" t="s">
+        <v>20</v>
+      </c>
+      <c r="G273" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>230</v>
+      </c>
+      <c r="B274" t="s">
+        <v>237</v>
+      </c>
+      <c r="C274" t="s">
+        <v>459</v>
+      </c>
+      <c r="D274" t="s">
+        <v>20</v>
+      </c>
+      <c r="G274" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>230</v>
+      </c>
+      <c r="B275" t="s">
+        <v>239</v>
+      </c>
+      <c r="C275" t="s">
+        <v>460</v>
+      </c>
+      <c r="D275" t="s">
+        <v>20</v>
+      </c>
+      <c r="G275" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>230</v>
+      </c>
+      <c r="B276" t="s">
         <v>244</v>
       </c>
-      <c r="C272" t="s">
+      <c r="C276" t="s">
+        <v>461</v>
+      </c>
+      <c r="D276" t="s">
+        <v>20</v>
+      </c>
+      <c r="G276" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>230</v>
+      </c>
+      <c r="B277" t="s">
+        <v>231</v>
+      </c>
+      <c r="C277" t="s">
+        <v>462</v>
+      </c>
+      <c r="D277" t="s">
+        <v>20</v>
+      </c>
+      <c r="G277" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>230</v>
+      </c>
+      <c r="B278" t="s">
+        <v>244</v>
+      </c>
+      <c r="C278" t="s">
         <v>463</v>
       </c>
-      <c r="D272" t="s">
-        <v>20</v>
-      </c>
-      <c r="G272" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>8</v>
-      </c>
-      <c r="B273" t="s">
-        <v>9</v>
-      </c>
-      <c r="C273" t="s">
-        <v>10</v>
-      </c>
-      <c r="D273" t="s">
-        <v>11</v>
-      </c>
-      <c r="F273" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>8</v>
-      </c>
-      <c r="B274" t="s">
-        <v>13</v>
-      </c>
-      <c r="C274" t="s">
-        <v>14</v>
-      </c>
-      <c r="D274" t="s">
-        <v>11</v>
-      </c>
-      <c r="F274" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>8</v>
-      </c>
-      <c r="B275" t="s">
-        <v>15</v>
-      </c>
-      <c r="C275" t="s">
-        <v>16</v>
-      </c>
-      <c r="D275" t="s">
-        <v>17</v>
-      </c>
-      <c r="E275" t="s">
-        <v>17</v>
-      </c>
-      <c r="F275" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>8</v>
-      </c>
-      <c r="B276" t="s">
-        <v>23</v>
-      </c>
-      <c r="C276" t="s">
-        <v>24</v>
-      </c>
-      <c r="D276" t="s">
-        <v>11</v>
-      </c>
-      <c r="E276" t="s">
-        <v>11</v>
-      </c>
-      <c r="F276" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>8</v>
-      </c>
-      <c r="B277" t="s">
-        <v>21</v>
-      </c>
-      <c r="C277" t="s">
-        <v>25</v>
-      </c>
-      <c r="D277" t="s">
-        <v>26</v>
-      </c>
-      <c r="F277" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>8</v>
-      </c>
-      <c r="B278" t="s">
-        <v>27</v>
-      </c>
-      <c r="C278" t="s">
-        <v>28</v>
-      </c>
       <c r="D278" t="s">
-        <v>29</v>
-      </c>
-      <c r="E278" t="s">
-        <v>29</v>
-      </c>
-      <c r="F278" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="G278" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>8</v>
       </c>
       <c r="B279" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C279" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D279" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F279" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>8</v>
       </c>
       <c r="B280" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D280" t="s">
-        <v>38</v>
-      </c>
-      <c r="E280" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>8</v>
       </c>
       <c r="B281" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C281" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D281" t="s">
-        <v>42</v>
+        <v>17</v>
+      </c>
+      <c r="E281" t="s">
+        <v>17</v>
       </c>
       <c r="F281" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>8</v>
       </c>
       <c r="B282" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C282" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D282" t="s">
-        <v>50</v>
+        <v>11</v>
+      </c>
+      <c r="E282" t="s">
+        <v>11</v>
       </c>
       <c r="F282" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>8</v>
       </c>
       <c r="B283" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C283" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>50</v>
-      </c>
-      <c r="E283" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="F283" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>8</v>
       </c>
       <c r="B284" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C284" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D284" t="s">
-        <v>53</v>
+        <v>29</v>
+      </c>
+      <c r="E284" t="s">
+        <v>29</v>
       </c>
       <c r="F284" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>8</v>
       </c>
       <c r="B285" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C285" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D285" t="s">
-        <v>60</v>
+        <v>32</v>
+      </c>
+      <c r="E285" t="s">
+        <v>32</v>
       </c>
       <c r="F285" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>8</v>
       </c>
       <c r="B286" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C286" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D286" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E286" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F286" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>8</v>
       </c>
       <c r="B287" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C287" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D287" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="E287" t="s">
+        <v>32</v>
       </c>
       <c r="F287" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>8</v>
       </c>
       <c r="B288" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D288" t="s">
-        <v>67</v>
-      </c>
-      <c r="E288" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F288" t="s">
         <v>12</v>
@@ -7227,13 +7118,16 @@
         <v>8</v>
       </c>
       <c r="B289" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C289" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D289" t="s">
-        <v>69</v>
+        <v>38</v>
+      </c>
+      <c r="E289" t="s">
+        <v>38</v>
       </c>
       <c r="F289" t="s">
         <v>12</v>
@@ -7244,16 +7138,13 @@
         <v>8</v>
       </c>
       <c r="B290" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C290" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="D290" t="s">
-        <v>75</v>
-      </c>
-      <c r="E290" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="F290" t="s">
         <v>12</v>
@@ -7267,13 +7158,13 @@
         <v>43</v>
       </c>
       <c r="C291" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="D291" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="E291" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="F291" t="s">
         <v>12</v>
@@ -7284,13 +7175,13 @@
         <v>8</v>
       </c>
       <c r="B292" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C292" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D292" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F292" t="s">
         <v>12</v>
@@ -7301,13 +7192,16 @@
         <v>8</v>
       </c>
       <c r="B293" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C293" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D293" t="s">
-        <v>94</v>
+        <v>50</v>
+      </c>
+      <c r="E293" t="s">
+        <v>50</v>
       </c>
       <c r="F293" t="s">
         <v>12</v>
@@ -7318,16 +7212,13 @@
         <v>8</v>
       </c>
       <c r="B294" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C294" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="D294" t="s">
-        <v>98</v>
-      </c>
-      <c r="E294" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="F294" t="s">
         <v>12</v>
@@ -7338,13 +7229,13 @@
         <v>8</v>
       </c>
       <c r="B295" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C295" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="D295" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="F295" t="s">
         <v>12</v>
@@ -7355,13 +7246,13 @@
         <v>8</v>
       </c>
       <c r="B296" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="D296" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F296" t="s">
         <v>12</v>
@@ -7372,16 +7263,13 @@
         <v>8</v>
       </c>
       <c r="B297" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C297" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="D297" t="s">
-        <v>102</v>
-      </c>
-      <c r="E297" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="F297" t="s">
         <v>12</v>
@@ -7392,16 +7280,16 @@
         <v>8</v>
       </c>
       <c r="B298" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C298" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="D298" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="E298" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="F298" t="s">
         <v>12</v>
@@ -7412,16 +7300,13 @@
         <v>8</v>
       </c>
       <c r="B299" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C299" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="D299" t="s">
-        <v>102</v>
-      </c>
-      <c r="E299" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="F299" t="s">
         <v>12</v>
@@ -7432,13 +7317,16 @@
         <v>8</v>
       </c>
       <c r="B300" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C300" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D300" t="s">
-        <v>118</v>
+        <v>67</v>
+      </c>
+      <c r="E300" t="s">
+        <v>67</v>
       </c>
       <c r="F300" t="s">
         <v>12</v>
@@ -7449,13 +7337,13 @@
         <v>8</v>
       </c>
       <c r="B301" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D301" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="F301" t="s">
         <v>12</v>
@@ -7466,13 +7354,16 @@
         <v>8</v>
       </c>
       <c r="B302" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C302" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="D302" t="s">
-        <v>122</v>
+        <v>75</v>
+      </c>
+      <c r="E302" t="s">
+        <v>75</v>
       </c>
       <c r="F302" t="s">
         <v>12</v>
@@ -7483,13 +7374,16 @@
         <v>8</v>
       </c>
       <c r="B303" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C303" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="D303" t="s">
-        <v>17</v>
+        <v>84</v>
+      </c>
+      <c r="E303" t="s">
+        <v>84</v>
       </c>
       <c r="F303" t="s">
         <v>12</v>
@@ -7503,13 +7397,10 @@
         <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="D304" t="s">
-        <v>125</v>
-      </c>
-      <c r="E304" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="F304" t="s">
         <v>12</v>
@@ -7520,16 +7411,13 @@
         <v>8</v>
       </c>
       <c r="B305" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C305" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="D305" t="s">
-        <v>17</v>
-      </c>
-      <c r="E305" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="F305" t="s">
         <v>12</v>
@@ -7540,16 +7428,16 @@
         <v>8</v>
       </c>
       <c r="B306" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="C306" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D306" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="E306" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="F306" t="s">
         <v>12</v>
@@ -7560,16 +7448,13 @@
         <v>8</v>
       </c>
       <c r="B307" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="C307" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="D307" t="s">
-        <v>139</v>
-      </c>
-      <c r="E307" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="F307" t="s">
         <v>12</v>
@@ -7580,16 +7465,13 @@
         <v>8</v>
       </c>
       <c r="B308" t="s">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="C308" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D308" t="s">
-        <v>149</v>
-      </c>
-      <c r="E308" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="F308" t="s">
         <v>12</v>
@@ -7597,16 +7479,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B309" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="C309" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="D309" t="s">
-        <v>17</v>
+        <v>103</v>
+      </c>
+      <c r="E309" t="s">
+        <v>103</v>
       </c>
       <c r="F309" t="s">
         <v>12</v>
@@ -7614,19 +7499,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B310" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="C310" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="D310" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="E310" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="F310" t="s">
         <v>12</v>
@@ -7634,19 +7519,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B311" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="C311" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="D311" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="E311" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="F311" t="s">
         <v>12</v>
@@ -7654,19 +7539,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B312" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="C312" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="D312" t="s">
-        <v>17</v>
-      </c>
-      <c r="E312" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="F312" t="s">
         <v>12</v>
@@ -7674,19 +7556,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B313" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="C313" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="D313" t="s">
-        <v>167</v>
-      </c>
-      <c r="E313" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="F313" t="s">
         <v>12</v>
@@ -7694,19 +7573,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B314" t="s">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="C314" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="D314" t="s">
-        <v>171</v>
-      </c>
-      <c r="E314" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="F314" t="s">
         <v>12</v>
@@ -7714,19 +7590,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B315" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
       <c r="C315" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="D315" t="s">
-        <v>173</v>
-      </c>
-      <c r="E315" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="F315" t="s">
         <v>12</v>
@@ -7734,19 +7607,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B316" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="C316" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="D316" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E316" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F316" t="s">
         <v>12</v>
@@ -7754,16 +7627,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B317" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="C317" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="D317" t="s">
-        <v>167</v>
+        <v>17</v>
+      </c>
+      <c r="E317" t="s">
+        <v>17</v>
       </c>
       <c r="F317" t="s">
         <v>12</v>
@@ -7771,19 +7647,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B318" t="s">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="C318" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="D318" t="s">
-        <v>187</v>
+        <v>42</v>
       </c>
       <c r="E318" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="F318" t="s">
         <v>12</v>
@@ -7791,16 +7667,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B319" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="C319" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D319" t="s">
-        <v>189</v>
+        <v>140</v>
+      </c>
+      <c r="E319" t="s">
+        <v>140</v>
       </c>
       <c r="F319" t="s">
         <v>12</v>
@@ -7808,19 +7687,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B320" t="s">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="C320" t="s">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D320" t="s">
-        <v>196</v>
-      </c>
-      <c r="E320" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="F320" t="s">
         <v>12</v>
@@ -7828,19 +7704,16 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="B321" t="s">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="C321" t="s">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="D321" t="s">
-        <v>196</v>
-      </c>
-      <c r="E321" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="F321" t="s">
         <v>12</v>
@@ -7848,19 +7721,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>8</v>
+      </c>
+      <c r="B322" t="s">
+        <v>148</v>
+      </c>
+      <c r="C322" t="s">
+        <v>149</v>
+      </c>
+      <c r="D322" t="s">
         <v>150</v>
       </c>
-      <c r="B322" t="s">
-        <v>176</v>
-      </c>
-      <c r="C322" t="s">
-        <v>198</v>
-      </c>
-      <c r="D322" t="s">
-        <v>196</v>
-      </c>
       <c r="E322" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="F322" t="s">
         <v>12</v>
@@ -7868,19 +7741,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B323" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C323" t="s">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="D323" t="s">
-        <v>203</v>
-      </c>
-      <c r="E323" t="s">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="F323" t="s">
         <v>12</v>
@@ -7888,19 +7758,19 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B324" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="C324" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="D324" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="E324" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="F324" t="s">
         <v>12</v>
@@ -7908,19 +7778,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B325" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C325" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="D325" t="s">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="E325" t="s">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="F325" t="s">
         <v>12</v>
@@ -7928,16 +7798,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B326" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C326" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="D326" t="s">
-        <v>125</v>
+        <v>163</v>
+      </c>
+      <c r="E326" t="s">
+        <v>163</v>
       </c>
       <c r="F326" t="s">
         <v>12</v>
@@ -7945,19 +7818,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B327" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C327" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="D327" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="E327" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="F327" t="s">
         <v>12</v>
@@ -7965,19 +7838,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B328" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C328" t="s">
-        <v>227</v>
+        <v>165</v>
       </c>
       <c r="D328" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="E328" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="F328" t="s">
         <v>12</v>
@@ -7985,19 +7858,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B329" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C329" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="D329" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="E329" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="F329" t="s">
         <v>12</v>
@@ -8005,19 +7878,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="B330" t="s">
-        <v>30</v>
+        <v>159</v>
       </c>
       <c r="C330" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="D330" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="E330" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="F330" t="s">
         <v>12</v>
@@ -8025,19 +7898,19 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="B331" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="C331" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="D331" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="E331" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="F331" t="s">
         <v>12</v>
@@ -8045,19 +7918,19 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="B332" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="C332" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="D332" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="E332" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="F332" t="s">
         <v>12</v>
@@ -8065,19 +7938,19 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="B333" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="C333" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="D333" t="s">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="E333" t="s">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="F333" t="s">
         <v>12</v>
@@ -8085,16 +7958,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="B334" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="C334" t="s">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="D334" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="F334" t="s">
         <v>12</v>
@@ -8102,16 +7975,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="B335" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="C335" t="s">
-        <v>57</v>
+        <v>185</v>
       </c>
       <c r="D335" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="F335" t="s">
         <v>12</v>
@@ -8119,361 +7992,397 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>151</v>
+      </c>
+      <c r="B336" t="s">
+        <v>186</v>
+      </c>
+      <c r="C336" t="s">
+        <v>187</v>
+      </c>
+      <c r="D336" t="s">
+        <v>188</v>
+      </c>
+      <c r="E336" t="s">
+        <v>188</v>
+      </c>
+      <c r="F336" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>151</v>
+      </c>
+      <c r="B337" t="s">
+        <v>158</v>
+      </c>
+      <c r="C337" t="s">
+        <v>189</v>
+      </c>
+      <c r="D337" t="s">
+        <v>190</v>
+      </c>
+      <c r="F337" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>151</v>
+      </c>
+      <c r="B338" t="s">
+        <v>170</v>
+      </c>
+      <c r="C338" t="s">
+        <v>196</v>
+      </c>
+      <c r="D338" t="s">
+        <v>197</v>
+      </c>
+      <c r="E338" t="s">
+        <v>197</v>
+      </c>
+      <c r="F338" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>151</v>
+      </c>
+      <c r="B339" t="s">
+        <v>170</v>
+      </c>
+      <c r="C339" t="s">
+        <v>198</v>
+      </c>
+      <c r="D339" t="s">
+        <v>197</v>
+      </c>
+      <c r="E339" t="s">
+        <v>197</v>
+      </c>
+      <c r="F339" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>151</v>
+      </c>
+      <c r="B340" t="s">
+        <v>177</v>
+      </c>
+      <c r="C340" t="s">
+        <v>199</v>
+      </c>
+      <c r="D340" t="s">
+        <v>197</v>
+      </c>
+      <c r="E340" t="s">
+        <v>197</v>
+      </c>
+      <c r="F340" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>151</v>
+      </c>
+      <c r="B341" t="s">
+        <v>177</v>
+      </c>
+      <c r="C341" t="s">
+        <v>200</v>
+      </c>
+      <c r="D341" t="s">
+        <v>201</v>
+      </c>
+      <c r="F341" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>151</v>
+      </c>
+      <c r="B342" t="s">
+        <v>177</v>
+      </c>
+      <c r="C342" t="s">
+        <v>203</v>
+      </c>
+      <c r="D342" t="s">
+        <v>204</v>
+      </c>
+      <c r="E342" t="s">
+        <v>204</v>
+      </c>
+      <c r="F342" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>151</v>
+      </c>
+      <c r="B343" t="s">
+        <v>170</v>
+      </c>
+      <c r="C343" t="s">
+        <v>205</v>
+      </c>
+      <c r="D343" t="s">
+        <v>204</v>
+      </c>
+      <c r="F343" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>151</v>
+      </c>
+      <c r="B344" t="s">
+        <v>170</v>
+      </c>
+      <c r="C344" t="s">
+        <v>206</v>
+      </c>
+      <c r="D344" t="s">
+        <v>204</v>
+      </c>
+      <c r="F344" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>151</v>
+      </c>
+      <c r="B345" t="s">
+        <v>177</v>
+      </c>
+      <c r="C345" t="s">
+        <v>210</v>
+      </c>
+      <c r="D345" t="s">
+        <v>211</v>
+      </c>
+      <c r="E345" t="s">
+        <v>211</v>
+      </c>
+      <c r="F345" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>151</v>
+      </c>
+      <c r="B346" t="s">
+        <v>221</v>
+      </c>
+      <c r="C346" t="s">
+        <v>222</v>
+      </c>
+      <c r="D346" t="s">
+        <v>188</v>
+      </c>
+      <c r="E346" t="s">
+        <v>188</v>
+      </c>
+      <c r="F346" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>151</v>
+      </c>
+      <c r="B347" t="s">
+        <v>159</v>
+      </c>
+      <c r="C347" t="s">
+        <v>223</v>
+      </c>
+      <c r="D347" t="s">
+        <v>188</v>
+      </c>
+      <c r="E347" t="s">
+        <v>188</v>
+      </c>
+      <c r="F347" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>151</v>
+      </c>
+      <c r="B348" t="s">
+        <v>158</v>
+      </c>
+      <c r="C348" t="s">
+        <v>125</v>
+      </c>
+      <c r="D348" t="s">
+        <v>126</v>
+      </c>
+      <c r="F348" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>151</v>
+      </c>
+      <c r="B349" t="s">
+        <v>170</v>
+      </c>
+      <c r="C349" t="s">
+        <v>226</v>
+      </c>
+      <c r="D349" t="s">
+        <v>179</v>
+      </c>
+      <c r="E349" t="s">
+        <v>179</v>
+      </c>
+      <c r="F349" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>151</v>
+      </c>
+      <c r="B350" t="s">
+        <v>170</v>
+      </c>
+      <c r="C350" t="s">
+        <v>227</v>
+      </c>
+      <c r="D350" t="s">
+        <v>179</v>
+      </c>
+      <c r="E350" t="s">
+        <v>179</v>
+      </c>
+      <c r="F350" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>151</v>
+      </c>
+      <c r="B351" t="s">
+        <v>170</v>
+      </c>
+      <c r="C351" t="s">
+        <v>228</v>
+      </c>
+      <c r="D351" t="s">
+        <v>229</v>
+      </c>
+      <c r="E351" t="s">
+        <v>229</v>
+      </c>
+      <c r="F351" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
         <v>8</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B352" t="s">
         <v>27</v>
       </c>
-      <c r="C336" t="s">
+      <c r="C352" t="s">
         <v>79</v>
       </c>
-      <c r="D336" t="s">
-        <v>20</v>
-      </c>
-      <c r="E336" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
+      <c r="D352" t="s">
+        <v>80</v>
+      </c>
+      <c r="E352" t="s">
+        <v>517</v>
+      </c>
+      <c r="F352" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
         <v>8</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B353" t="s">
         <v>65</v>
       </c>
-      <c r="C337" t="s">
-        <v>80</v>
-      </c>
-      <c r="D337" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
+      <c r="C353" t="s">
+        <v>81</v>
+      </c>
+      <c r="E353" t="s">
+        <v>517</v>
+      </c>
+      <c r="F353" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
         <v>8</v>
       </c>
-      <c r="B338" t="s">
-        <v>65</v>
-      </c>
-      <c r="C338" t="s">
-        <v>113</v>
-      </c>
-      <c r="D338" t="s">
-        <v>20</v>
-      </c>
-      <c r="G338" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
+      <c r="B354" t="s">
+        <v>128</v>
+      </c>
+      <c r="C354" t="s">
+        <v>129</v>
+      </c>
+      <c r="D354" t="s">
+        <v>42</v>
+      </c>
+      <c r="F354" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
         <v>8</v>
       </c>
-      <c r="B339" t="s">
-        <v>127</v>
-      </c>
-      <c r="C339" t="s">
-        <v>128</v>
-      </c>
-      <c r="D339" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
+      <c r="B355" t="s">
+        <v>23</v>
+      </c>
+      <c r="C355" t="s">
+        <v>131</v>
+      </c>
+      <c r="D355" t="s">
+        <v>42</v>
+      </c>
+      <c r="F355" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
         <v>8</v>
       </c>
-      <c r="B340" t="s">
-        <v>23</v>
-      </c>
-      <c r="C340" t="s">
-        <v>130</v>
-      </c>
-      <c r="D340" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>8</v>
-      </c>
-      <c r="B341" t="s">
+      <c r="B356" t="s">
         <v>13</v>
       </c>
-      <c r="C341" t="s">
+      <c r="C356" t="s">
+        <v>141</v>
+      </c>
+      <c r="D356" t="s">
         <v>140</v>
       </c>
-      <c r="D341" t="s">
-        <v>42</v>
-      </c>
-      <c r="E341" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>8</v>
-      </c>
-      <c r="B342" t="s">
-        <v>70</v>
-      </c>
-      <c r="C342" t="s">
-        <v>143</v>
-      </c>
-      <c r="D342" t="s">
-        <v>20</v>
-      </c>
-      <c r="G342" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>8</v>
-      </c>
-      <c r="B343" t="s">
-        <v>54</v>
-      </c>
-      <c r="C343" t="s">
-        <v>144</v>
-      </c>
-      <c r="D343" t="s">
-        <v>145</v>
-      </c>
-      <c r="F343" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>8</v>
-      </c>
-      <c r="B344" t="s">
-        <v>13</v>
-      </c>
-      <c r="C344" t="s">
-        <v>146</v>
-      </c>
-      <c r="D344" t="s">
-        <v>145</v>
-      </c>
-      <c r="F344" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>150</v>
-      </c>
-      <c r="B345" t="s">
-        <v>158</v>
-      </c>
-      <c r="C345" t="s">
-        <v>159</v>
-      </c>
-      <c r="D345" t="s">
-        <v>129</v>
-      </c>
-      <c r="E345" t="s">
-        <v>17</v>
-      </c>
-      <c r="F345" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>150</v>
-      </c>
-      <c r="B346" t="s">
-        <v>158</v>
-      </c>
-      <c r="C346" t="s">
-        <v>160</v>
-      </c>
-      <c r="D346" t="s">
-        <v>129</v>
-      </c>
-      <c r="E346" t="s">
-        <v>17</v>
-      </c>
-      <c r="F346" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
-        <v>150</v>
-      </c>
-      <c r="B347" t="s">
-        <v>158</v>
-      </c>
-      <c r="C347" t="s">
-        <v>165</v>
-      </c>
-      <c r="D347" t="s">
-        <v>17</v>
-      </c>
-      <c r="E347" t="s">
-        <v>17</v>
-      </c>
-      <c r="F347" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>150</v>
-      </c>
-      <c r="B348" t="s">
-        <v>151</v>
-      </c>
-      <c r="C348" t="s">
-        <v>182</v>
-      </c>
-      <c r="D348" t="s">
-        <v>20</v>
-      </c>
-      <c r="G348" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>150</v>
-      </c>
-      <c r="B349" t="s">
-        <v>157</v>
-      </c>
-      <c r="C349" t="s">
-        <v>183</v>
-      </c>
-      <c r="D349" t="s">
-        <v>167</v>
-      </c>
-      <c r="F349" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>150</v>
-      </c>
-      <c r="B350" t="s">
-        <v>176</v>
-      </c>
-      <c r="C350" t="s">
-        <v>199</v>
-      </c>
-      <c r="D350" t="s">
-        <v>200</v>
-      </c>
-      <c r="F350" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>150</v>
-      </c>
-      <c r="B351" t="s">
-        <v>169</v>
-      </c>
-      <c r="C351" t="s">
-        <v>204</v>
-      </c>
-      <c r="D351" t="s">
-        <v>203</v>
-      </c>
-      <c r="F351" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>150</v>
-      </c>
-      <c r="B352" t="s">
-        <v>169</v>
-      </c>
-      <c r="C352" t="s">
-        <v>205</v>
-      </c>
-      <c r="D352" t="s">
-        <v>203</v>
-      </c>
-      <c r="F352" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>150</v>
-      </c>
-      <c r="B353" t="s">
-        <v>151</v>
-      </c>
-      <c r="C353" t="s">
-        <v>206</v>
-      </c>
-      <c r="D353" t="s">
-        <v>20</v>
-      </c>
-      <c r="G353" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>150</v>
-      </c>
-      <c r="B354" t="s">
-        <v>151</v>
-      </c>
-      <c r="C354" t="s">
-        <v>207</v>
-      </c>
-      <c r="D354" t="s">
-        <v>20</v>
-      </c>
-      <c r="G354" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
-        <v>150</v>
-      </c>
-      <c r="B355" t="s">
-        <v>220</v>
-      </c>
-      <c r="C355" t="s">
-        <v>221</v>
-      </c>
-      <c r="D355" t="s">
-        <v>222</v>
-      </c>
-      <c r="E355" t="s">
-        <v>187</v>
-      </c>
-      <c r="F355" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
-        <v>150</v>
-      </c>
-      <c r="B356" t="s">
-        <v>151</v>
-      </c>
-      <c r="C356" t="s">
-        <v>224</v>
-      </c>
-      <c r="D356" t="s">
-        <v>20</v>
-      </c>
-      <c r="G356" t="s">
+      <c r="E356" t="s">
+        <v>140</v>
+      </c>
+      <c r="F356" t="s">
         <v>12</v>
       </c>
     </row>
@@ -8497,7 +8406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A152"/>
+  <dimension ref="A1:A154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -8507,7 +8416,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -8532,7 +8441,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -8722,17 +8631,17 @@
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>499</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
@@ -8742,7 +8651,7 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -8752,7 +8661,7 @@
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -8767,7 +8676,7 @@
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
@@ -8782,72 +8691,72 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
@@ -8857,247 +8766,247 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>517</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>518</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>518</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>519</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>210</v>
+        <v>525</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>526</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>94</v>
+        <v>526</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>527</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>528</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>529</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>60</v>
+        <v>535</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>536</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>536</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>537</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>187</v>
+        <v>537</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>538</v>
+        <v>188</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>116</v>
+        <v>540</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>541</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>118</v>
+        <v>541</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>542</v>
+        <v>119</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>120</v>
+        <v>543</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>544</v>
+        <v>121</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>122</v>
+        <v>544</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>545</v>
+        <v>123</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>125</v>
+        <v>545</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>139</v>
+        <v>546</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>546</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
@@ -9122,17 +9031,17 @@
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>189</v>
+        <v>551</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>552</v>
+        <v>190</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
@@ -9182,17 +9091,17 @@
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>173</v>
+        <v>562</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>563</v>
+        <v>174</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
@@ -9202,32 +9111,32 @@
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>565</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>178</v>
+        <v>567</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>566</v>
+        <v>229</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>567</v>
+        <v>179</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
@@ -9242,22 +9151,32 @@
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>149</v>
+        <v>570</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>571</v>
+        <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>572</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -9267,432 +9186,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>574</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>575</v>
-      </c>
-      <c r="C3" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>576</v>
-      </c>
-      <c r="C4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>577</v>
-      </c>
-      <c r="C5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>578</v>
-      </c>
-      <c r="C6" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>579</v>
-      </c>
-      <c r="C7" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>580</v>
-      </c>
-      <c r="C8" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>581</v>
-      </c>
-      <c r="C9" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>582</v>
-      </c>
-      <c r="C10" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>583</v>
-      </c>
-      <c r="C11" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>584</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>585</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>586</v>
-      </c>
-      <c r="C14" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>587</v>
-      </c>
-      <c r="C15" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>588</v>
-      </c>
-      <c r="C16" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>589</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>590</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>591</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>592</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>593</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>594</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>595</v>
-      </c>
-      <c r="C23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>596</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>597</v>
-      </c>
-      <c r="C25" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>598</v>
-      </c>
-      <c r="C26" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>599</v>
-      </c>
-      <c r="C27" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>600</v>
-      </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>601</v>
-      </c>
-      <c r="C29" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>150</v>
-      </c>
-      <c r="B30" t="s">
-        <v>602</v>
-      </c>
-      <c r="C30" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" t="s">
-        <v>603</v>
-      </c>
-      <c r="C31" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>150</v>
-      </c>
-      <c r="B32" t="s">
-        <v>604</v>
-      </c>
-      <c r="C32" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" t="s">
-        <v>605</v>
-      </c>
-      <c r="C33" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>150</v>
-      </c>
-      <c r="B34" t="s">
-        <v>606</v>
-      </c>
-      <c r="C34" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>150</v>
-      </c>
-      <c r="B35" t="s">
-        <v>607</v>
-      </c>
-      <c r="C35" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" t="s">
-        <v>608</v>
-      </c>
-      <c r="C36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" t="s">
-        <v>609</v>
-      </c>
-      <c r="C37" t="s">
-        <v>178</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9702,7 +9195,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>610</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -9710,50 +9203,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>611</v>
+        <v>576</v>
       </c>
       <c r="B3" t="s">
-        <v>612</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>613</v>
+        <v>578</v>
       </c>
       <c r="B4" t="s">
-        <v>614</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>615</v>
+        <v>580</v>
       </c>
       <c r="B5" t="s">
-        <v>616</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>617</v>
+        <v>582</v>
       </c>
       <c r="B6" t="s">
-        <v>618</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>619</v>
+        <v>584</v>
       </c>
       <c r="B7" t="s">
-        <v>620</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>621</v>
+        <v>586</v>
       </c>
       <c r="B8" t="s">
-        <v>622</v>
+        <v>587</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -9761,42 +9254,42 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="B10" t="s">
-        <v>624</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="B11" t="s">
-        <v>625</v>
+        <v>590</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="B12" t="s">
-        <v>626</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="B13" t="s">
-        <v>627</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="B14" t="s">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90078082-294F-429F-BDE3-7C2FC4459CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991F2DD8-260F-4E3D-A73B-7D405737BC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="811">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -2457,6 +2457,9 @@
   </si>
   <si>
     <t>Rækker der ikke længere er aktuelle, men SOM havde et udfyldt valg (og ikke er ignoreret), havner i arket 'Forsvundne (havde valg)' - intet forsvinder usporligt.</t>
+  </si>
+  <si>
+    <t>TMDB</t>
   </si>
 </sst>
 </file>
@@ -5913,9 +5916,9 @@
         <v>418</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
-      </c>
-      <c r="G181" t="s">
+        <v>810</v>
+      </c>
+      <c r="F181" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9120,15 +9123,15 @@
         <v>8</v>
       </c>
       <c r="B370" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C370" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D370" t="s">
-        <v>23</v>
-      </c>
-      <c r="F370" t="s">
+        <v>11</v>
+      </c>
+      <c r="G370" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9137,15 +9140,15 @@
         <v>8</v>
       </c>
       <c r="B371" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C371" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D371" t="s">
-        <v>25</v>
-      </c>
-      <c r="F371" t="s">
+        <v>11</v>
+      </c>
+      <c r="G371" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9154,15 +9157,15 @@
         <v>8</v>
       </c>
       <c r="B372" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C372" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="D372" t="s">
-        <v>28</v>
-      </c>
-      <c r="F372" t="s">
+        <v>11</v>
+      </c>
+      <c r="G372" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9171,18 +9174,15 @@
         <v>8</v>
       </c>
       <c r="B373" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C373" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D373" t="s">
-        <v>31</v>
-      </c>
-      <c r="E373" t="s">
-        <v>31</v>
-      </c>
-      <c r="F373" t="s">
+        <v>11</v>
+      </c>
+      <c r="G373" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9191,18 +9191,15 @@
         <v>8</v>
       </c>
       <c r="B374" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C374" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="D374" t="s">
-        <v>33</v>
-      </c>
-      <c r="E374" t="s">
-        <v>33</v>
-      </c>
-      <c r="F374" t="s">
+        <v>11</v>
+      </c>
+      <c r="G374" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9211,18 +9208,15 @@
         <v>8</v>
       </c>
       <c r="B375" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="C375" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="D375" t="s">
-        <v>37</v>
-      </c>
-      <c r="E375" t="s">
-        <v>37</v>
-      </c>
-      <c r="F375" t="s">
+        <v>11</v>
+      </c>
+      <c r="G375" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9231,18 +9225,15 @@
         <v>8</v>
       </c>
       <c r="B376" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C376" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="D376" t="s">
-        <v>37</v>
-      </c>
-      <c r="E376" t="s">
-        <v>37</v>
-      </c>
-      <c r="F376" t="s">
+        <v>11</v>
+      </c>
+      <c r="G376" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9251,18 +9242,15 @@
         <v>8</v>
       </c>
       <c r="B377" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C377" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="D377" t="s">
-        <v>37</v>
-      </c>
-      <c r="E377" t="s">
-        <v>37</v>
-      </c>
-      <c r="F377" t="s">
+        <v>11</v>
+      </c>
+      <c r="G377" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9271,18 +9259,15 @@
         <v>8</v>
       </c>
       <c r="B378" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C378" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="D378" t="s">
-        <v>37</v>
-      </c>
-      <c r="E378" t="s">
-        <v>37</v>
-      </c>
-      <c r="F378" t="s">
+        <v>11</v>
+      </c>
+      <c r="G378" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9291,18 +9276,15 @@
         <v>8</v>
       </c>
       <c r="B379" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C379" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="D379" t="s">
-        <v>37</v>
-      </c>
-      <c r="E379" t="s">
-        <v>37</v>
-      </c>
-      <c r="F379" t="s">
+        <v>11</v>
+      </c>
+      <c r="G379" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9311,18 +9293,15 @@
         <v>8</v>
       </c>
       <c r="B380" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C380" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="D380" t="s">
-        <v>37</v>
-      </c>
-      <c r="E380" t="s">
-        <v>37</v>
-      </c>
-      <c r="F380" t="s">
+        <v>11</v>
+      </c>
+      <c r="G380" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9331,18 +9310,15 @@
         <v>8</v>
       </c>
       <c r="B381" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="C381" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="D381" t="s">
-        <v>37</v>
-      </c>
-      <c r="E381" t="s">
-        <v>37</v>
-      </c>
-      <c r="F381" t="s">
+        <v>11</v>
+      </c>
+      <c r="G381" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9351,18 +9327,15 @@
         <v>8</v>
       </c>
       <c r="B382" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C382" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="D382" t="s">
-        <v>52</v>
-      </c>
-      <c r="E382" t="s">
-        <v>52</v>
-      </c>
-      <c r="F382" t="s">
+        <v>11</v>
+      </c>
+      <c r="G382" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9371,15 +9344,15 @@
         <v>8</v>
       </c>
       <c r="B383" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="C383" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="D383" t="s">
-        <v>56</v>
-      </c>
-      <c r="F383" t="s">
+        <v>11</v>
+      </c>
+      <c r="G383" t="s">
         <v>12</v>
       </c>
     </row>
@@ -9388,611 +9361,581 @@
         <v>8</v>
       </c>
       <c r="B384" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C384" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="D384" t="s">
-        <v>52</v>
-      </c>
-      <c r="F384" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="G384" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>8</v>
       </c>
       <c r="B385" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C385" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="D385" t="s">
+        <v>11</v>
+      </c>
+      <c r="G385" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>8</v>
+      </c>
+      <c r="B386" t="s">
+        <v>17</v>
+      </c>
+      <c r="C386" t="s">
+        <v>177</v>
+      </c>
+      <c r="D386" t="s">
+        <v>11</v>
+      </c>
+      <c r="G386" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>179</v>
+      </c>
+      <c r="B387" t="s">
+        <v>182</v>
+      </c>
+      <c r="C387" t="s">
+        <v>186</v>
+      </c>
+      <c r="D387" t="s">
+        <v>11</v>
+      </c>
+      <c r="G387" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>179</v>
+      </c>
+      <c r="B388" t="s">
+        <v>182</v>
+      </c>
+      <c r="C388" t="s">
+        <v>189</v>
+      </c>
+      <c r="D388" t="s">
+        <v>11</v>
+      </c>
+      <c r="G388" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>179</v>
+      </c>
+      <c r="B389" t="s">
+        <v>182</v>
+      </c>
+      <c r="C389" t="s">
+        <v>192</v>
+      </c>
+      <c r="D389" t="s">
+        <v>11</v>
+      </c>
+      <c r="G389" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>179</v>
+      </c>
+      <c r="B390" t="s">
+        <v>182</v>
+      </c>
+      <c r="C390" t="s">
+        <v>196</v>
+      </c>
+      <c r="D390" t="s">
+        <v>11</v>
+      </c>
+      <c r="G390" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>179</v>
+      </c>
+      <c r="B391" t="s">
+        <v>182</v>
+      </c>
+      <c r="C391" t="s">
+        <v>197</v>
+      </c>
+      <c r="D391" t="s">
+        <v>11</v>
+      </c>
+      <c r="G391" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>179</v>
+      </c>
+      <c r="B392" t="s">
+        <v>203</v>
+      </c>
+      <c r="C392" t="s">
+        <v>215</v>
+      </c>
+      <c r="D392" t="s">
+        <v>11</v>
+      </c>
+      <c r="G392" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>179</v>
+      </c>
+      <c r="B393" t="s">
+        <v>203</v>
+      </c>
+      <c r="C393" t="s">
+        <v>242</v>
+      </c>
+      <c r="D393" t="s">
+        <v>11</v>
+      </c>
+      <c r="G393" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>179</v>
+      </c>
+      <c r="B394" t="s">
+        <v>182</v>
+      </c>
+      <c r="C394" t="s">
+        <v>246</v>
+      </c>
+      <c r="D394" t="s">
+        <v>11</v>
+      </c>
+      <c r="G394" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>179</v>
+      </c>
+      <c r="B395" t="s">
+        <v>182</v>
+      </c>
+      <c r="C395" t="s">
+        <v>247</v>
+      </c>
+      <c r="D395" t="s">
+        <v>11</v>
+      </c>
+      <c r="G395" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>179</v>
+      </c>
+      <c r="B396" t="s">
+        <v>182</v>
+      </c>
+      <c r="C396" t="s">
+        <v>250</v>
+      </c>
+      <c r="D396" t="s">
+        <v>11</v>
+      </c>
+      <c r="G396" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>179</v>
+      </c>
+      <c r="B397" t="s">
+        <v>180</v>
+      </c>
+      <c r="C397" t="s">
+        <v>252</v>
+      </c>
+      <c r="D397" t="s">
+        <v>11</v>
+      </c>
+      <c r="G397" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>179</v>
+      </c>
+      <c r="B398" t="s">
+        <v>182</v>
+      </c>
+      <c r="C398" t="s">
+        <v>253</v>
+      </c>
+      <c r="D398" t="s">
+        <v>11</v>
+      </c>
+      <c r="G398" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>179</v>
+      </c>
+      <c r="B399" t="s">
+        <v>182</v>
+      </c>
+      <c r="C399" t="s">
+        <v>255</v>
+      </c>
+      <c r="D399" t="s">
+        <v>11</v>
+      </c>
+      <c r="G399" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>179</v>
+      </c>
+      <c r="B400" t="s">
+        <v>182</v>
+      </c>
+      <c r="C400" t="s">
+        <v>276</v>
+      </c>
+      <c r="D400" t="s">
+        <v>11</v>
+      </c>
+      <c r="G400" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>179</v>
+      </c>
+      <c r="B401" t="s">
+        <v>182</v>
+      </c>
+      <c r="C401" t="s">
+        <v>279</v>
+      </c>
+      <c r="D401" t="s">
+        <v>11</v>
+      </c>
+      <c r="G401" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>179</v>
+      </c>
+      <c r="B402" t="s">
+        <v>203</v>
+      </c>
+      <c r="C402" t="s">
+        <v>280</v>
+      </c>
+      <c r="D402" t="s">
+        <v>11</v>
+      </c>
+      <c r="G402" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>179</v>
+      </c>
+      <c r="B403" t="s">
+        <v>203</v>
+      </c>
+      <c r="C403" t="s">
+        <v>282</v>
+      </c>
+      <c r="D403" t="s">
+        <v>11</v>
+      </c>
+      <c r="G403" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>179</v>
+      </c>
+      <c r="B404" t="s">
+        <v>264</v>
+      </c>
+      <c r="C404" t="s">
+        <v>286</v>
+      </c>
+      <c r="D404" t="s">
+        <v>207</v>
+      </c>
+      <c r="G404" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>179</v>
+      </c>
+      <c r="B405" t="s">
+        <v>264</v>
+      </c>
+      <c r="C405" t="s">
+        <v>290</v>
+      </c>
+      <c r="D405" t="s">
+        <v>268</v>
+      </c>
+      <c r="G405" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>8</v>
+      </c>
+      <c r="B406" t="s">
+        <v>21</v>
+      </c>
+      <c r="C406" t="s">
+        <v>22</v>
+      </c>
+      <c r="D406" t="s">
+        <v>23</v>
+      </c>
+      <c r="F406" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>8</v>
+      </c>
+      <c r="B407" t="s">
+        <v>21</v>
+      </c>
+      <c r="C407" t="s">
+        <v>24</v>
+      </c>
+      <c r="D407" t="s">
+        <v>25</v>
+      </c>
+      <c r="F407" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>8</v>
+      </c>
+      <c r="B408" t="s">
+        <v>26</v>
+      </c>
+      <c r="C408" t="s">
+        <v>27</v>
+      </c>
+      <c r="D408" t="s">
         <v>28</v>
       </c>
-      <c r="F385" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
-        <v>8</v>
-      </c>
-      <c r="B386" t="s">
+      <c r="F408" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>8</v>
+      </c>
+      <c r="B409" t="s">
+        <v>29</v>
+      </c>
+      <c r="C409" t="s">
+        <v>30</v>
+      </c>
+      <c r="D409" t="s">
+        <v>31</v>
+      </c>
+      <c r="E409" t="s">
+        <v>31</v>
+      </c>
+      <c r="F409" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>8</v>
+      </c>
+      <c r="B410" t="s">
+        <v>26</v>
+      </c>
+      <c r="C410" t="s">
+        <v>32</v>
+      </c>
+      <c r="D410" t="s">
+        <v>33</v>
+      </c>
+      <c r="E410" t="s">
+        <v>33</v>
+      </c>
+      <c r="F410" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>8</v>
+      </c>
+      <c r="B411" t="s">
+        <v>35</v>
+      </c>
+      <c r="C411" t="s">
+        <v>36</v>
+      </c>
+      <c r="D411" t="s">
+        <v>37</v>
+      </c>
+      <c r="E411" t="s">
+        <v>37</v>
+      </c>
+      <c r="F411" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>8</v>
+      </c>
+      <c r="B412" t="s">
         <v>38</v>
       </c>
-      <c r="C386" t="s">
-        <v>69</v>
-      </c>
-      <c r="D386" t="s">
-        <v>52</v>
-      </c>
-      <c r="E386" t="s">
-        <v>52</v>
-      </c>
-      <c r="F386" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>8</v>
-      </c>
-      <c r="B387" t="s">
-        <v>15</v>
-      </c>
-      <c r="C387" t="s">
-        <v>70</v>
-      </c>
-      <c r="D387" t="s">
-        <v>52</v>
-      </c>
-      <c r="E387" t="s">
-        <v>52</v>
-      </c>
-      <c r="F387" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A388" t="s">
-        <v>8</v>
-      </c>
-      <c r="B388" t="s">
-        <v>21</v>
-      </c>
-      <c r="C388" t="s">
-        <v>78</v>
-      </c>
-      <c r="D388" t="s">
-        <v>11</v>
-      </c>
-      <c r="F388" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
-        <v>8</v>
-      </c>
-      <c r="B389" t="s">
-        <v>54</v>
-      </c>
-      <c r="C389" t="s">
-        <v>84</v>
-      </c>
-      <c r="D389" t="s">
-        <v>85</v>
-      </c>
-      <c r="F389" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A390" t="s">
-        <v>8</v>
-      </c>
-      <c r="B390" t="s">
+      <c r="C412" t="s">
+        <v>39</v>
+      </c>
+      <c r="D412" t="s">
+        <v>37</v>
+      </c>
+      <c r="E412" t="s">
+        <v>37</v>
+      </c>
+      <c r="F412" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>8</v>
+      </c>
+      <c r="B413" t="s">
+        <v>44</v>
+      </c>
+      <c r="C413" t="s">
+        <v>45</v>
+      </c>
+      <c r="D413" t="s">
+        <v>37</v>
+      </c>
+      <c r="E413" t="s">
+        <v>37</v>
+      </c>
+      <c r="F413" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>8</v>
+      </c>
+      <c r="B414" t="s">
         <v>26</v>
       </c>
-      <c r="C390" t="s">
-        <v>94</v>
-      </c>
-      <c r="D390" t="s">
-        <v>95</v>
-      </c>
-      <c r="F390" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A391" t="s">
-        <v>8</v>
-      </c>
-      <c r="B391" t="s">
-        <v>35</v>
-      </c>
-      <c r="C391" t="s">
-        <v>109</v>
-      </c>
-      <c r="D391" t="s">
-        <v>105</v>
-      </c>
-      <c r="E391" t="s">
-        <v>105</v>
-      </c>
-      <c r="F391" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
-        <v>8</v>
-      </c>
-      <c r="B392" t="s">
-        <v>38</v>
-      </c>
-      <c r="C392" t="s">
-        <v>110</v>
-      </c>
-      <c r="D392" t="s">
-        <v>105</v>
-      </c>
-      <c r="E392" t="s">
-        <v>105</v>
-      </c>
-      <c r="F392" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
-        <v>8</v>
-      </c>
-      <c r="B393" t="s">
+      <c r="C414" t="s">
+        <v>46</v>
+      </c>
+      <c r="D414" t="s">
+        <v>37</v>
+      </c>
+      <c r="E414" t="s">
+        <v>37</v>
+      </c>
+      <c r="F414" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>8</v>
+      </c>
+      <c r="B415" t="s">
+        <v>47</v>
+      </c>
+      <c r="C415" t="s">
+        <v>48</v>
+      </c>
+      <c r="D415" t="s">
+        <v>37</v>
+      </c>
+      <c r="E415" t="s">
+        <v>37</v>
+      </c>
+      <c r="F415" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>8</v>
+      </c>
+      <c r="B416" t="s">
         <v>26</v>
       </c>
-      <c r="C393" t="s">
-        <v>111</v>
-      </c>
-      <c r="D393" t="s">
-        <v>105</v>
-      </c>
-      <c r="E393" t="s">
-        <v>105</v>
-      </c>
-      <c r="F393" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
-        <v>8</v>
-      </c>
-      <c r="B394" t="s">
-        <v>38</v>
-      </c>
-      <c r="C394" t="s">
-        <v>112</v>
-      </c>
-      <c r="D394" t="s">
-        <v>105</v>
-      </c>
-      <c r="E394" t="s">
-        <v>105</v>
-      </c>
-      <c r="F394" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A395" t="s">
-        <v>8</v>
-      </c>
-      <c r="B395" t="s">
-        <v>21</v>
-      </c>
-      <c r="C395" t="s">
-        <v>121</v>
-      </c>
-      <c r="D395" t="s">
-        <v>122</v>
-      </c>
-      <c r="F395" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
-        <v>8</v>
-      </c>
-      <c r="B396" t="s">
-        <v>147</v>
-      </c>
-      <c r="C396" t="s">
-        <v>148</v>
-      </c>
-      <c r="D396" t="s">
-        <v>149</v>
-      </c>
-      <c r="F396" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A397" t="s">
-        <v>8</v>
-      </c>
-      <c r="B397" t="s">
-        <v>147</v>
-      </c>
-      <c r="C397" t="s">
-        <v>150</v>
-      </c>
-      <c r="D397" t="s">
-        <v>149</v>
-      </c>
-      <c r="F397" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A398" t="s">
-        <v>8</v>
-      </c>
-      <c r="B398" t="s">
-        <v>147</v>
-      </c>
-      <c r="C398" t="s">
-        <v>151</v>
-      </c>
-      <c r="D398" t="s">
-        <v>152</v>
-      </c>
-      <c r="F398" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A399" t="s">
-        <v>8</v>
-      </c>
-      <c r="B399" t="s">
-        <v>153</v>
-      </c>
-      <c r="C399" t="s">
-        <v>154</v>
-      </c>
-      <c r="D399" t="s">
-        <v>155</v>
-      </c>
-      <c r="F399" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
-        <v>8</v>
-      </c>
-      <c r="B400" t="s">
-        <v>147</v>
-      </c>
-      <c r="C400" t="s">
-        <v>156</v>
-      </c>
-      <c r="D400" t="s">
-        <v>155</v>
-      </c>
-      <c r="E400" t="s">
-        <v>155</v>
-      </c>
-      <c r="F400" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A401" t="s">
-        <v>8</v>
-      </c>
-      <c r="B401" t="s">
-        <v>135</v>
-      </c>
-      <c r="C401" t="s">
-        <v>163</v>
-      </c>
-      <c r="D401" t="s">
-        <v>164</v>
-      </c>
-      <c r="F401" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
-        <v>8</v>
-      </c>
-      <c r="B402" t="s">
-        <v>166</v>
-      </c>
-      <c r="C402" t="s">
-        <v>167</v>
-      </c>
-      <c r="D402" t="s">
-        <v>168</v>
-      </c>
-      <c r="E402" t="s">
-        <v>168</v>
-      </c>
-      <c r="F402" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
-        <v>8</v>
-      </c>
-      <c r="B403" t="s">
-        <v>169</v>
-      </c>
-      <c r="C403" t="s">
-        <v>170</v>
-      </c>
-      <c r="D403" t="s">
-        <v>168</v>
-      </c>
-      <c r="E403" t="s">
-        <v>168</v>
-      </c>
-      <c r="F403" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A404" t="s">
-        <v>8</v>
-      </c>
-      <c r="B404" t="s">
-        <v>15</v>
-      </c>
-      <c r="C404" t="s">
-        <v>172</v>
-      </c>
-      <c r="D404" t="s">
-        <v>11</v>
-      </c>
-      <c r="F404" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A405" t="s">
-        <v>8</v>
-      </c>
-      <c r="B405" t="s">
-        <v>147</v>
-      </c>
-      <c r="C405" t="s">
-        <v>173</v>
-      </c>
-      <c r="D405" t="s">
-        <v>174</v>
-      </c>
-      <c r="E405" t="s">
-        <v>174</v>
-      </c>
-      <c r="F405" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A406" t="s">
-        <v>179</v>
-      </c>
-      <c r="B406" t="s">
-        <v>198</v>
-      </c>
-      <c r="C406" t="s">
-        <v>199</v>
-      </c>
-      <c r="D406" t="s">
-        <v>200</v>
-      </c>
-      <c r="F406" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A407" t="s">
-        <v>179</v>
-      </c>
-      <c r="B407" t="s">
-        <v>198</v>
-      </c>
-      <c r="C407" t="s">
-        <v>201</v>
-      </c>
-      <c r="D407" t="s">
-        <v>200</v>
-      </c>
-      <c r="F407" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A408" t="s">
-        <v>179</v>
-      </c>
-      <c r="B408" t="s">
-        <v>198</v>
-      </c>
-      <c r="C408" t="s">
-        <v>202</v>
-      </c>
-      <c r="D408" t="s">
-        <v>200</v>
-      </c>
-      <c r="F408" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A409" t="s">
-        <v>179</v>
-      </c>
-      <c r="B409" t="s">
-        <v>218</v>
-      </c>
-      <c r="C409" t="s">
-        <v>219</v>
-      </c>
-      <c r="D409" t="s">
-        <v>220</v>
-      </c>
-      <c r="E409" t="s">
-        <v>220</v>
-      </c>
-      <c r="F409" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
-        <v>179</v>
-      </c>
-      <c r="B410" t="s">
-        <v>221</v>
-      </c>
-      <c r="C410" t="s">
-        <v>222</v>
-      </c>
-      <c r="D410" t="s">
-        <v>220</v>
-      </c>
-      <c r="E410" t="s">
-        <v>220</v>
-      </c>
-      <c r="F410" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A411" t="s">
-        <v>179</v>
-      </c>
-      <c r="B411" t="s">
-        <v>223</v>
-      </c>
-      <c r="C411" t="s">
-        <v>224</v>
-      </c>
-      <c r="D411" t="s">
-        <v>220</v>
-      </c>
-      <c r="E411" t="s">
-        <v>220</v>
-      </c>
-      <c r="F411" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
-        <v>179</v>
-      </c>
-      <c r="B412" t="s">
-        <v>225</v>
-      </c>
-      <c r="C412" t="s">
-        <v>226</v>
-      </c>
-      <c r="D412" t="s">
-        <v>220</v>
-      </c>
-      <c r="E412" t="s">
-        <v>220</v>
-      </c>
-      <c r="F412" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A413" t="s">
-        <v>179</v>
-      </c>
-      <c r="B413" t="s">
-        <v>225</v>
-      </c>
-      <c r="C413" t="s">
-        <v>227</v>
-      </c>
-      <c r="D413" t="s">
-        <v>220</v>
-      </c>
-      <c r="E413" t="s">
-        <v>220</v>
-      </c>
-      <c r="F413" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
-        <v>179</v>
-      </c>
-      <c r="B414" t="s">
-        <v>225</v>
-      </c>
-      <c r="C414" t="s">
-        <v>228</v>
-      </c>
-      <c r="D414" t="s">
-        <v>220</v>
-      </c>
-      <c r="E414" t="s">
-        <v>220</v>
-      </c>
-      <c r="F414" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
-        <v>179</v>
-      </c>
-      <c r="B415" t="s">
-        <v>225</v>
-      </c>
-      <c r="C415" t="s">
-        <v>229</v>
-      </c>
-      <c r="D415" t="s">
-        <v>220</v>
-      </c>
-      <c r="E415" t="s">
-        <v>220</v>
-      </c>
-      <c r="F415" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
-        <v>179</v>
-      </c>
-      <c r="B416" t="s">
-        <v>225</v>
-      </c>
       <c r="C416" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="D416" t="s">
-        <v>220</v>
+        <v>37</v>
       </c>
       <c r="E416" t="s">
-        <v>220</v>
+        <v>37</v>
       </c>
       <c r="F416" t="s">
         <v>12</v>
@@ -10000,19 +9943,19 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B417" t="s">
-        <v>225</v>
+        <v>47</v>
       </c>
       <c r="C417" t="s">
-        <v>232</v>
+        <v>50</v>
       </c>
       <c r="D417" t="s">
-        <v>220</v>
+        <v>37</v>
       </c>
       <c r="E417" t="s">
-        <v>220</v>
+        <v>37</v>
       </c>
       <c r="F417" t="s">
         <v>12</v>
@@ -10020,19 +9963,19 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B418" t="s">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="C418" t="s">
-        <v>233</v>
+        <v>51</v>
       </c>
       <c r="D418" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="E418" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="F418" t="s">
         <v>12</v>
@@ -10040,19 +9983,16 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B419" t="s">
-        <v>234</v>
+        <v>54</v>
       </c>
       <c r="C419" t="s">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="D419" t="s">
-        <v>220</v>
-      </c>
-      <c r="E419" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="F419" t="s">
         <v>12</v>
@@ -10060,19 +10000,16 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B420" t="s">
-        <v>225</v>
+        <v>62</v>
       </c>
       <c r="C420" t="s">
-        <v>237</v>
+        <v>63</v>
       </c>
       <c r="D420" t="s">
-        <v>220</v>
-      </c>
-      <c r="E420" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="F420" t="s">
         <v>12</v>
@@ -10080,19 +10017,16 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B421" t="s">
-        <v>225</v>
+        <v>64</v>
       </c>
       <c r="C421" t="s">
-        <v>239</v>
+        <v>65</v>
       </c>
       <c r="D421" t="s">
-        <v>220</v>
-      </c>
-      <c r="E421" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="F421" t="s">
         <v>12</v>
@@ -10100,19 +10034,19 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B422" t="s">
-        <v>225</v>
+        <v>38</v>
       </c>
       <c r="C422" t="s">
-        <v>240</v>
+        <v>69</v>
       </c>
       <c r="D422" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="E422" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="F422" t="s">
         <v>12</v>
@@ -10120,16 +10054,19 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B423" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C423" t="s">
-        <v>256</v>
+        <v>70</v>
       </c>
       <c r="D423" t="s">
-        <v>28</v>
+        <v>52</v>
+      </c>
+      <c r="E423" t="s">
+        <v>52</v>
       </c>
       <c r="F423" t="s">
         <v>12</v>
@@ -10137,19 +10074,16 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B424" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="C424" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="D424" t="s">
-        <v>259</v>
-      </c>
-      <c r="E424" t="s">
-        <v>259</v>
+        <v>11</v>
       </c>
       <c r="F424" t="s">
         <v>12</v>
@@ -10157,16 +10091,16 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B425" t="s">
-        <v>262</v>
+        <v>54</v>
       </c>
       <c r="C425" t="s">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="D425" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="F425" t="s">
         <v>12</v>
@@ -10174,16 +10108,16 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B426" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="C426" t="s">
-        <v>265</v>
+        <v>94</v>
       </c>
       <c r="D426" t="s">
-        <v>259</v>
+        <v>95</v>
       </c>
       <c r="F426" t="s">
         <v>12</v>
@@ -10191,16 +10125,19 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B427" t="s">
-        <v>205</v>
+        <v>35</v>
       </c>
       <c r="C427" t="s">
-        <v>266</v>
+        <v>109</v>
       </c>
       <c r="D427" t="s">
-        <v>259</v>
+        <v>105</v>
+      </c>
+      <c r="E427" t="s">
+        <v>105</v>
       </c>
       <c r="F427" t="s">
         <v>12</v>
@@ -10208,16 +10145,19 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B428" t="s">
-        <v>264</v>
+        <v>38</v>
       </c>
       <c r="C428" t="s">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="D428" t="s">
-        <v>268</v>
+        <v>105</v>
+      </c>
+      <c r="E428" t="s">
+        <v>105</v>
       </c>
       <c r="F428" t="s">
         <v>12</v>
@@ -10225,16 +10165,19 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B429" t="s">
-        <v>205</v>
+        <v>26</v>
       </c>
       <c r="C429" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="D429" t="s">
-        <v>259</v>
+        <v>105</v>
+      </c>
+      <c r="E429" t="s">
+        <v>105</v>
       </c>
       <c r="F429" t="s">
         <v>12</v>
@@ -10242,19 +10185,19 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B430" t="s">
-        <v>205</v>
+        <v>38</v>
       </c>
       <c r="C430" t="s">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="D430" t="s">
-        <v>271</v>
+        <v>105</v>
       </c>
       <c r="E430" t="s">
-        <v>271</v>
+        <v>105</v>
       </c>
       <c r="F430" t="s">
         <v>12</v>
@@ -10262,19 +10205,16 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B431" t="s">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="C431" t="s">
-        <v>285</v>
+        <v>121</v>
       </c>
       <c r="D431" t="s">
-        <v>268</v>
-      </c>
-      <c r="E431" t="s">
-        <v>268</v>
+        <v>122</v>
       </c>
       <c r="F431" t="s">
         <v>12</v>
@@ -10282,205 +10222,184 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B432" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="C432" t="s">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="D432" t="s">
-        <v>288</v>
-      </c>
-      <c r="E432" t="s">
-        <v>288</v>
+        <v>149</v>
       </c>
       <c r="F432" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B433" t="s">
-        <v>262</v>
+        <v>147</v>
       </c>
       <c r="C433" t="s">
-        <v>289</v>
+        <v>150</v>
       </c>
       <c r="D433" t="s">
-        <v>268</v>
-      </c>
-      <c r="E433" t="s">
-        <v>268</v>
+        <v>149</v>
       </c>
       <c r="F433" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B434" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="C434" t="s">
-        <v>291</v>
+        <v>151</v>
       </c>
       <c r="D434" t="s">
-        <v>288</v>
-      </c>
-      <c r="E434" t="s">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="F434" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B435" t="s">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="C435" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="D435" t="s">
-        <v>293</v>
-      </c>
-      <c r="E435" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="F435" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B436" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="C436" t="s">
-        <v>294</v>
+        <v>156</v>
       </c>
       <c r="D436" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="E436" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="F436" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B437" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="C437" t="s">
-        <v>296</v>
+        <v>163</v>
       </c>
       <c r="D437" t="s">
-        <v>220</v>
-      </c>
-      <c r="E437" t="s">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="F437" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B438" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C438" t="s">
-        <v>302</v>
+        <v>167</v>
       </c>
       <c r="D438" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="E438" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="F438" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B439" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="C439" t="s">
-        <v>303</v>
+        <v>170</v>
       </c>
       <c r="D439" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="E439" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="F439" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B440" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C440" t="s">
-        <v>304</v>
-      </c>
-      <c r="D440" t="s">
-        <v>220</v>
-      </c>
-      <c r="E440" t="s">
-        <v>220</v>
+        <v>172</v>
       </c>
       <c r="F440" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B441" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="C441" t="s">
-        <v>308</v>
+        <v>173</v>
       </c>
       <c r="D441" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="E441" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="F441" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>179</v>
       </c>
@@ -10488,19 +10407,16 @@
         <v>198</v>
       </c>
       <c r="C442" t="s">
-        <v>309</v>
+        <v>199</v>
       </c>
       <c r="D442" t="s">
-        <v>220</v>
-      </c>
-      <c r="E442" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F442" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>179</v>
       </c>
@@ -10508,19 +10424,16 @@
         <v>198</v>
       </c>
       <c r="C443" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="D443" t="s">
-        <v>220</v>
-      </c>
-      <c r="E443" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F443" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>179</v>
       </c>
@@ -10528,27 +10441,24 @@
         <v>198</v>
       </c>
       <c r="C444" t="s">
-        <v>312</v>
+        <v>202</v>
       </c>
       <c r="D444" t="s">
-        <v>220</v>
-      </c>
-      <c r="E444" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F444" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>179</v>
       </c>
       <c r="B445" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="C445" t="s">
-        <v>313</v>
+        <v>219</v>
       </c>
       <c r="D445" t="s">
         <v>220</v>
@@ -10560,628 +10470,712 @@
         <v>12</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>179</v>
       </c>
       <c r="B446" t="s">
+        <v>221</v>
+      </c>
+      <c r="C446" t="s">
+        <v>222</v>
+      </c>
+      <c r="D446" t="s">
+        <v>220</v>
+      </c>
+      <c r="E446" t="s">
+        <v>220</v>
+      </c>
+      <c r="F446" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>179</v>
+      </c>
+      <c r="B447" t="s">
+        <v>223</v>
+      </c>
+      <c r="C447" t="s">
+        <v>224</v>
+      </c>
+      <c r="D447" t="s">
+        <v>220</v>
+      </c>
+      <c r="E447" t="s">
+        <v>220</v>
+      </c>
+      <c r="F447" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>179</v>
+      </c>
+      <c r="B448" t="s">
+        <v>225</v>
+      </c>
+      <c r="C448" t="s">
+        <v>226</v>
+      </c>
+      <c r="D448" t="s">
+        <v>220</v>
+      </c>
+      <c r="E448" t="s">
+        <v>220</v>
+      </c>
+      <c r="F448" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>179</v>
+      </c>
+      <c r="B449" t="s">
+        <v>225</v>
+      </c>
+      <c r="C449" t="s">
+        <v>227</v>
+      </c>
+      <c r="D449" t="s">
+        <v>220</v>
+      </c>
+      <c r="E449" t="s">
+        <v>220</v>
+      </c>
+      <c r="F449" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>179</v>
+      </c>
+      <c r="B450" t="s">
+        <v>225</v>
+      </c>
+      <c r="C450" t="s">
+        <v>228</v>
+      </c>
+      <c r="D450" t="s">
+        <v>220</v>
+      </c>
+      <c r="E450" t="s">
+        <v>220</v>
+      </c>
+      <c r="F450" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>179</v>
+      </c>
+      <c r="B451" t="s">
+        <v>225</v>
+      </c>
+      <c r="C451" t="s">
+        <v>229</v>
+      </c>
+      <c r="D451" t="s">
+        <v>220</v>
+      </c>
+      <c r="E451" t="s">
+        <v>220</v>
+      </c>
+      <c r="F451" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>179</v>
+      </c>
+      <c r="B452" t="s">
+        <v>225</v>
+      </c>
+      <c r="C452" t="s">
+        <v>231</v>
+      </c>
+      <c r="D452" t="s">
+        <v>220</v>
+      </c>
+      <c r="E452" t="s">
+        <v>220</v>
+      </c>
+      <c r="F452" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>179</v>
+      </c>
+      <c r="B453" t="s">
+        <v>225</v>
+      </c>
+      <c r="C453" t="s">
+        <v>232</v>
+      </c>
+      <c r="D453" t="s">
+        <v>220</v>
+      </c>
+      <c r="E453" t="s">
+        <v>220</v>
+      </c>
+      <c r="F453" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>179</v>
+      </c>
+      <c r="B454" t="s">
+        <v>225</v>
+      </c>
+      <c r="C454" t="s">
+        <v>233</v>
+      </c>
+      <c r="D454" t="s">
+        <v>220</v>
+      </c>
+      <c r="E454" t="s">
+        <v>220</v>
+      </c>
+      <c r="F454" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>179</v>
+      </c>
+      <c r="B455" t="s">
+        <v>234</v>
+      </c>
+      <c r="C455" t="s">
+        <v>235</v>
+      </c>
+      <c r="D455" t="s">
+        <v>220</v>
+      </c>
+      <c r="E455" t="s">
+        <v>220</v>
+      </c>
+      <c r="F455" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>179</v>
+      </c>
+      <c r="B456" t="s">
+        <v>225</v>
+      </c>
+      <c r="C456" t="s">
+        <v>237</v>
+      </c>
+      <c r="D456" t="s">
+        <v>220</v>
+      </c>
+      <c r="E456" t="s">
+        <v>220</v>
+      </c>
+      <c r="F456" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>179</v>
+      </c>
+      <c r="B457" t="s">
+        <v>225</v>
+      </c>
+      <c r="C457" t="s">
+        <v>239</v>
+      </c>
+      <c r="D457" t="s">
+        <v>220</v>
+      </c>
+      <c r="E457" t="s">
+        <v>220</v>
+      </c>
+      <c r="F457" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>179</v>
+      </c>
+      <c r="B458" t="s">
+        <v>225</v>
+      </c>
+      <c r="C458" t="s">
+        <v>240</v>
+      </c>
+      <c r="D458" t="s">
+        <v>220</v>
+      </c>
+      <c r="E458" t="s">
+        <v>220</v>
+      </c>
+      <c r="F458" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>179</v>
+      </c>
+      <c r="B459" t="s">
+        <v>198</v>
+      </c>
+      <c r="C459" t="s">
+        <v>256</v>
+      </c>
+      <c r="D459" t="s">
+        <v>28</v>
+      </c>
+      <c r="F459" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>179</v>
+      </c>
+      <c r="B460" t="s">
+        <v>198</v>
+      </c>
+      <c r="C460" t="s">
+        <v>258</v>
+      </c>
+      <c r="D460" t="s">
+        <v>259</v>
+      </c>
+      <c r="E460" t="s">
+        <v>259</v>
+      </c>
+      <c r="F460" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>179</v>
+      </c>
+      <c r="B461" t="s">
+        <v>262</v>
+      </c>
+      <c r="C461" t="s">
+        <v>263</v>
+      </c>
+      <c r="D461" t="s">
+        <v>259</v>
+      </c>
+      <c r="F461" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>179</v>
+      </c>
+      <c r="B462" t="s">
+        <v>264</v>
+      </c>
+      <c r="C462" t="s">
+        <v>265</v>
+      </c>
+      <c r="D462" t="s">
+        <v>259</v>
+      </c>
+      <c r="F462" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>179</v>
+      </c>
+      <c r="B463" t="s">
         <v>205</v>
       </c>
-      <c r="C446" t="s">
-        <v>314</v>
-      </c>
-      <c r="D446" t="s">
-        <v>315</v>
-      </c>
-      <c r="F446" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
-        <v>8</v>
-      </c>
-      <c r="B447" t="s">
-        <v>17</v>
-      </c>
-      <c r="C447" t="s">
-        <v>18</v>
-      </c>
-      <c r="D447" t="s">
-        <v>11</v>
-      </c>
-      <c r="G447" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
-        <v>8</v>
-      </c>
-      <c r="B448" t="s">
-        <v>38</v>
-      </c>
-      <c r="C448" t="s">
-        <v>40</v>
-      </c>
-      <c r="D448" t="s">
-        <v>41</v>
-      </c>
-      <c r="E448" t="s">
-        <v>37</v>
-      </c>
-      <c r="F448" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A449" t="s">
-        <v>8</v>
-      </c>
-      <c r="B449" t="s">
-        <v>26</v>
-      </c>
-      <c r="C449" t="s">
-        <v>42</v>
-      </c>
-      <c r="D449" t="s">
-        <v>37</v>
-      </c>
-      <c r="E449" t="s">
-        <v>37</v>
-      </c>
-      <c r="F449" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A450" t="s">
-        <v>8</v>
-      </c>
-      <c r="B450" t="s">
-        <v>26</v>
-      </c>
-      <c r="C450" t="s">
-        <v>43</v>
-      </c>
-      <c r="D450" t="s">
-        <v>41</v>
-      </c>
-      <c r="E450" t="s">
-        <v>37</v>
-      </c>
-      <c r="F450" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A451" t="s">
-        <v>8</v>
-      </c>
-      <c r="B451" t="s">
-        <v>9</v>
-      </c>
-      <c r="C451" t="s">
-        <v>53</v>
-      </c>
-      <c r="D451" t="s">
-        <v>11</v>
-      </c>
-      <c r="G451" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
-        <v>8</v>
-      </c>
-      <c r="B452" t="s">
-        <v>26</v>
-      </c>
-      <c r="C452" t="s">
-        <v>57</v>
-      </c>
-      <c r="D452" t="s">
-        <v>56</v>
-      </c>
-      <c r="F452" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A453" t="s">
-        <v>8</v>
-      </c>
-      <c r="B453" t="s">
-        <v>35</v>
-      </c>
-      <c r="C453" t="s">
-        <v>58</v>
-      </c>
-      <c r="D453" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
-        <v>8</v>
-      </c>
-      <c r="B454" t="s">
-        <v>38</v>
-      </c>
-      <c r="C454" t="s">
-        <v>60</v>
-      </c>
-      <c r="D454" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
-        <v>8</v>
-      </c>
-      <c r="B455" t="s">
-        <v>26</v>
-      </c>
-      <c r="C455" t="s">
-        <v>61</v>
-      </c>
-      <c r="D455" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
-        <v>8</v>
-      </c>
-      <c r="B456" t="s">
-        <v>66</v>
-      </c>
-      <c r="C456" t="s">
-        <v>67</v>
-      </c>
-      <c r="D456" t="s">
-        <v>28</v>
-      </c>
-      <c r="F456" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A457" t="s">
-        <v>8</v>
-      </c>
-      <c r="B457" t="s">
-        <v>17</v>
-      </c>
-      <c r="C457" t="s">
-        <v>75</v>
-      </c>
-      <c r="D457" t="s">
-        <v>11</v>
-      </c>
-      <c r="G457" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
-        <v>8</v>
-      </c>
-      <c r="B458" t="s">
-        <v>17</v>
-      </c>
-      <c r="C458" t="s">
-        <v>77</v>
-      </c>
-      <c r="D458" t="s">
-        <v>11</v>
-      </c>
-      <c r="G458" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A459" t="s">
-        <v>8</v>
-      </c>
-      <c r="B459" t="s">
-        <v>17</v>
-      </c>
-      <c r="C459" t="s">
-        <v>82</v>
-      </c>
-      <c r="D459" t="s">
-        <v>11</v>
-      </c>
-      <c r="G459" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
-        <v>8</v>
-      </c>
-      <c r="B460" t="s">
-        <v>88</v>
-      </c>
-      <c r="C460" t="s">
-        <v>89</v>
-      </c>
-      <c r="D460" t="s">
-        <v>11</v>
-      </c>
-      <c r="G460" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
-        <v>8</v>
-      </c>
-      <c r="B461" t="s">
-        <v>88</v>
-      </c>
-      <c r="C461" t="s">
-        <v>97</v>
-      </c>
-      <c r="D461" t="s">
-        <v>11</v>
-      </c>
-      <c r="G461" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
-        <v>8</v>
-      </c>
-      <c r="B462" t="s">
-        <v>17</v>
-      </c>
-      <c r="C462" t="s">
-        <v>101</v>
-      </c>
-      <c r="D462" t="s">
-        <v>11</v>
-      </c>
-      <c r="G462" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A463" t="s">
-        <v>8</v>
-      </c>
-      <c r="B463" t="s">
-        <v>17</v>
-      </c>
       <c r="C463" t="s">
-        <v>106</v>
+        <v>266</v>
       </c>
       <c r="D463" t="s">
-        <v>11</v>
-      </c>
-      <c r="G463" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="F463" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B464" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C464" t="s">
-        <v>114</v>
+        <v>267</v>
       </c>
       <c r="D464" t="s">
-        <v>11</v>
-      </c>
-      <c r="G464" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="E464" t="s">
+        <v>268</v>
+      </c>
+      <c r="F464" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B465" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="C465" t="s">
-        <v>126</v>
+        <v>269</v>
       </c>
       <c r="D465" t="s">
-        <v>11</v>
-      </c>
-      <c r="G465" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="F465" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B466" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C466" t="s">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="D466" t="s">
-        <v>11</v>
-      </c>
-      <c r="G466" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="E466" t="s">
+        <v>271</v>
+      </c>
+      <c r="F466" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B467" t="s">
-        <v>88</v>
+        <v>262</v>
       </c>
       <c r="C467" t="s">
-        <v>133</v>
+        <v>285</v>
       </c>
       <c r="D467" t="s">
-        <v>11</v>
-      </c>
-      <c r="G467" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="E467" t="s">
+        <v>268</v>
+      </c>
+      <c r="F467" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B468" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="C468" t="s">
-        <v>141</v>
+        <v>287</v>
       </c>
       <c r="D468" t="s">
-        <v>11</v>
-      </c>
-      <c r="G468" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="E468" t="s">
+        <v>288</v>
+      </c>
+      <c r="F468" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B469" t="s">
-        <v>88</v>
+        <v>262</v>
       </c>
       <c r="C469" t="s">
-        <v>146</v>
+        <v>289</v>
       </c>
       <c r="D469" t="s">
-        <v>11</v>
-      </c>
-      <c r="G469" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="E469" t="s">
+        <v>268</v>
+      </c>
+      <c r="F469" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B470" t="s">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="C470" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="D470" t="s">
-        <v>11</v>
-      </c>
-      <c r="G470" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="E470" t="s">
+        <v>288</v>
+      </c>
+      <c r="F470" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B471" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
       <c r="C471" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="D471" t="s">
-        <v>162</v>
+        <v>293</v>
+      </c>
+      <c r="E471" t="s">
+        <v>293</v>
       </c>
       <c r="F471" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B472" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="C472" t="s">
-        <v>171</v>
+        <v>294</v>
       </c>
       <c r="D472" t="s">
-        <v>168</v>
+        <v>293</v>
+      </c>
+      <c r="E472" t="s">
+        <v>293</v>
       </c>
       <c r="F472" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="B473" t="s">
-        <v>17</v>
+        <v>198</v>
       </c>
       <c r="C473" t="s">
-        <v>177</v>
+        <v>296</v>
       </c>
       <c r="D473" t="s">
-        <v>11</v>
-      </c>
-      <c r="G473" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="E473" t="s">
+        <v>220</v>
+      </c>
+      <c r="F473" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>179</v>
       </c>
       <c r="B474" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C474" t="s">
-        <v>186</v>
+        <v>302</v>
       </c>
       <c r="D474" t="s">
-        <v>11</v>
-      </c>
-      <c r="G474" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="E474" t="s">
+        <v>220</v>
+      </c>
+      <c r="F474" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>179</v>
       </c>
       <c r="B475" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C475" t="s">
-        <v>189</v>
+        <v>303</v>
       </c>
       <c r="D475" t="s">
-        <v>11</v>
-      </c>
-      <c r="G475" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="E475" t="s">
+        <v>220</v>
+      </c>
+      <c r="F475" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>179</v>
       </c>
       <c r="B476" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C476" t="s">
-        <v>192</v>
+        <v>304</v>
       </c>
       <c r="D476" t="s">
-        <v>11</v>
-      </c>
-      <c r="G476" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="E476" t="s">
+        <v>220</v>
+      </c>
+      <c r="F476" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>179</v>
       </c>
       <c r="B477" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C477" t="s">
-        <v>196</v>
+        <v>308</v>
       </c>
       <c r="D477" t="s">
-        <v>11</v>
-      </c>
-      <c r="G477" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="E477" t="s">
+        <v>220</v>
+      </c>
+      <c r="F477" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>179</v>
       </c>
       <c r="B478" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C478" t="s">
-        <v>197</v>
+        <v>309</v>
       </c>
       <c r="D478" t="s">
-        <v>11</v>
-      </c>
-      <c r="G478" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="E478" t="s">
+        <v>220</v>
+      </c>
+      <c r="F478" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>179</v>
       </c>
       <c r="B479" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C479" t="s">
-        <v>206</v>
+        <v>311</v>
       </c>
       <c r="D479" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E479" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="F479" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>179</v>
       </c>
       <c r="B480" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C480" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="D480" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E480" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="F480" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>179</v>
       </c>
       <c r="B481" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C481" t="s">
-        <v>209</v>
+        <v>313</v>
       </c>
       <c r="D481" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E481" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="F481" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>179</v>
       </c>
@@ -11189,357 +11183,384 @@
         <v>205</v>
       </c>
       <c r="C482" t="s">
+        <v>314</v>
+      </c>
+      <c r="D482" t="s">
+        <v>315</v>
+      </c>
+      <c r="F482" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>8</v>
+      </c>
+      <c r="B483" t="s">
+        <v>38</v>
+      </c>
+      <c r="C483" t="s">
+        <v>40</v>
+      </c>
+      <c r="D483" t="s">
+        <v>41</v>
+      </c>
+      <c r="E483" t="s">
+        <v>37</v>
+      </c>
+      <c r="F483" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>8</v>
+      </c>
+      <c r="B484" t="s">
+        <v>26</v>
+      </c>
+      <c r="C484" t="s">
+        <v>42</v>
+      </c>
+      <c r="D484" t="s">
+        <v>37</v>
+      </c>
+      <c r="E484" t="s">
+        <v>37</v>
+      </c>
+      <c r="F484" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>8</v>
+      </c>
+      <c r="B485" t="s">
+        <v>26</v>
+      </c>
+      <c r="C485" t="s">
+        <v>43</v>
+      </c>
+      <c r="D485" t="s">
+        <v>41</v>
+      </c>
+      <c r="E485" t="s">
+        <v>37</v>
+      </c>
+      <c r="F485" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>8</v>
+      </c>
+      <c r="B486" t="s">
+        <v>26</v>
+      </c>
+      <c r="C486" t="s">
+        <v>57</v>
+      </c>
+      <c r="D486" t="s">
+        <v>56</v>
+      </c>
+      <c r="F486" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>8</v>
+      </c>
+      <c r="B487" t="s">
+        <v>66</v>
+      </c>
+      <c r="C487" t="s">
+        <v>67</v>
+      </c>
+      <c r="D487" t="s">
+        <v>28</v>
+      </c>
+      <c r="F487" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>8</v>
+      </c>
+      <c r="B488" t="s">
+        <v>26</v>
+      </c>
+      <c r="C488" t="s">
+        <v>161</v>
+      </c>
+      <c r="D488" t="s">
+        <v>162</v>
+      </c>
+      <c r="F488" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>8</v>
+      </c>
+      <c r="B489" t="s">
+        <v>26</v>
+      </c>
+      <c r="C489" t="s">
+        <v>171</v>
+      </c>
+      <c r="D489" t="s">
+        <v>168</v>
+      </c>
+      <c r="F489" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>179</v>
+      </c>
+      <c r="B490" t="s">
+        <v>205</v>
+      </c>
+      <c r="C490" t="s">
+        <v>206</v>
+      </c>
+      <c r="D490" t="s">
+        <v>207</v>
+      </c>
+      <c r="E490" t="s">
+        <v>288</v>
+      </c>
+      <c r="F490" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>179</v>
+      </c>
+      <c r="B491" t="s">
+        <v>205</v>
+      </c>
+      <c r="C491" t="s">
+        <v>208</v>
+      </c>
+      <c r="D491" t="s">
+        <v>207</v>
+      </c>
+      <c r="E491" t="s">
+        <v>288</v>
+      </c>
+      <c r="F491" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>179</v>
+      </c>
+      <c r="B492" t="s">
+        <v>205</v>
+      </c>
+      <c r="C492" t="s">
+        <v>209</v>
+      </c>
+      <c r="D492" t="s">
+        <v>207</v>
+      </c>
+      <c r="E492" t="s">
+        <v>288</v>
+      </c>
+      <c r="F492" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>179</v>
+      </c>
+      <c r="B493" t="s">
+        <v>205</v>
+      </c>
+      <c r="C493" t="s">
         <v>210</v>
       </c>
-      <c r="D482" t="s">
+      <c r="D493" t="s">
         <v>207</v>
       </c>
-      <c r="E482" t="s">
+      <c r="E493" t="s">
         <v>288</v>
       </c>
-      <c r="F482" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A483" t="s">
-        <v>179</v>
-      </c>
-      <c r="B483" t="s">
+      <c r="F493" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>179</v>
+      </c>
+      <c r="B494" t="s">
         <v>205</v>
       </c>
-      <c r="C483" t="s">
+      <c r="C494" t="s">
         <v>211</v>
       </c>
-      <c r="D483" t="s">
+      <c r="D494" t="s">
         <v>207</v>
       </c>
-      <c r="E483" t="s">
+      <c r="E494" t="s">
         <v>288</v>
       </c>
-      <c r="F483" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
-        <v>179</v>
-      </c>
-      <c r="B484" t="s">
+      <c r="F494" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>179</v>
+      </c>
+      <c r="B495" t="s">
         <v>205</v>
       </c>
-      <c r="C484" t="s">
+      <c r="C495" t="s">
         <v>212</v>
       </c>
-      <c r="D484" t="s">
+      <c r="D495" t="s">
         <v>207</v>
       </c>
-      <c r="E484" t="s">
+      <c r="E495" t="s">
         <v>288</v>
       </c>
-      <c r="F484" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A485" t="s">
-        <v>179</v>
-      </c>
-      <c r="B485" t="s">
-        <v>203</v>
-      </c>
-      <c r="C485" t="s">
-        <v>215</v>
-      </c>
-      <c r="D485" t="s">
-        <v>11</v>
-      </c>
-      <c r="G485" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
-        <v>179</v>
-      </c>
-      <c r="B486" t="s">
+      <c r="F495" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>179</v>
+      </c>
+      <c r="B496" t="s">
         <v>225</v>
       </c>
-      <c r="C486" t="s">
+      <c r="C496" t="s">
         <v>230</v>
       </c>
-      <c r="D486" t="s">
+      <c r="D496" t="s">
         <v>59</v>
       </c>
-      <c r="E486" t="s">
+      <c r="E496" t="s">
         <v>220</v>
       </c>
-      <c r="F486" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A487" t="s">
-        <v>179</v>
-      </c>
-      <c r="B487" t="s">
+      <c r="F496" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>179</v>
+      </c>
+      <c r="B497" t="s">
         <v>225</v>
       </c>
-      <c r="C487" t="s">
+      <c r="C497" t="s">
         <v>236</v>
       </c>
-      <c r="D487" t="s">
+      <c r="D497" t="s">
         <v>59</v>
       </c>
-      <c r="E487" t="s">
+      <c r="E497" t="s">
         <v>220</v>
       </c>
-      <c r="F487" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
-        <v>179</v>
-      </c>
-      <c r="B488" t="s">
+      <c r="F497" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>179</v>
+      </c>
+      <c r="B498" t="s">
         <v>234</v>
       </c>
-      <c r="C488" t="s">
+      <c r="C498" t="s">
         <v>238</v>
       </c>
-      <c r="D488" t="s">
+      <c r="D498" t="s">
         <v>59</v>
       </c>
-      <c r="E488" t="s">
+      <c r="E498" t="s">
         <v>220</v>
       </c>
-      <c r="F488" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
-        <v>179</v>
-      </c>
-      <c r="B489" t="s">
-        <v>203</v>
-      </c>
-      <c r="C489" t="s">
-        <v>242</v>
-      </c>
-      <c r="D489" t="s">
-        <v>11</v>
-      </c>
-      <c r="G489" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
-        <v>179</v>
-      </c>
-      <c r="B490" t="s">
-        <v>182</v>
-      </c>
-      <c r="C490" t="s">
-        <v>246</v>
-      </c>
-      <c r="D490" t="s">
-        <v>11</v>
-      </c>
-      <c r="G490" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
-        <v>179</v>
-      </c>
-      <c r="B491" t="s">
-        <v>182</v>
-      </c>
-      <c r="C491" t="s">
-        <v>247</v>
-      </c>
-      <c r="D491" t="s">
-        <v>11</v>
-      </c>
-      <c r="G491" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
-        <v>179</v>
-      </c>
-      <c r="B492" t="s">
-        <v>182</v>
-      </c>
-      <c r="C492" t="s">
-        <v>250</v>
-      </c>
-      <c r="D492" t="s">
-        <v>11</v>
-      </c>
-      <c r="G492" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
-        <v>179</v>
-      </c>
-      <c r="B493" t="s">
-        <v>180</v>
-      </c>
-      <c r="C493" t="s">
-        <v>252</v>
-      </c>
-      <c r="D493" t="s">
-        <v>11</v>
-      </c>
-      <c r="G493" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
-        <v>179</v>
-      </c>
-      <c r="B494" t="s">
-        <v>182</v>
-      </c>
-      <c r="C494" t="s">
-        <v>253</v>
-      </c>
-      <c r="D494" t="s">
-        <v>11</v>
-      </c>
-      <c r="G494" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
-        <v>179</v>
-      </c>
-      <c r="B495" t="s">
-        <v>182</v>
-      </c>
-      <c r="C495" t="s">
-        <v>255</v>
-      </c>
-      <c r="D495" t="s">
-        <v>11</v>
-      </c>
-      <c r="G495" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
-        <v>179</v>
-      </c>
-      <c r="B496" t="s">
-        <v>182</v>
-      </c>
-      <c r="C496" t="s">
-        <v>276</v>
-      </c>
-      <c r="D496" t="s">
-        <v>11</v>
-      </c>
-      <c r="G496" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
-        <v>179</v>
-      </c>
-      <c r="B497" t="s">
-        <v>182</v>
-      </c>
-      <c r="C497" t="s">
-        <v>279</v>
-      </c>
-      <c r="D497" t="s">
-        <v>11</v>
-      </c>
-      <c r="G497" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
-        <v>179</v>
-      </c>
-      <c r="B498" t="s">
-        <v>203</v>
-      </c>
-      <c r="C498" t="s">
-        <v>280</v>
-      </c>
-      <c r="D498" t="s">
-        <v>11</v>
-      </c>
-      <c r="G498" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F498" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>179</v>
       </c>
       <c r="B499" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C499" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D499" t="s">
-        <v>11</v>
-      </c>
-      <c r="G499" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="E499" t="s">
+        <v>220</v>
+      </c>
+      <c r="F499" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>179</v>
       </c>
       <c r="B500" t="s">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="C500" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="D500" t="s">
-        <v>207</v>
-      </c>
-      <c r="G500" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="E500" t="s">
+        <v>220</v>
+      </c>
+      <c r="F500" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>179</v>
       </c>
       <c r="B501" t="s">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="C501" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D501" t="s">
-        <v>268</v>
-      </c>
-      <c r="G501" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="E501" t="s">
+        <v>220</v>
+      </c>
+      <c r="F501" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>179</v>
       </c>
@@ -11547,7 +11568,7 @@
         <v>198</v>
       </c>
       <c r="C502" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D502" t="s">
         <v>298</v>
@@ -11559,15 +11580,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>179</v>
       </c>
       <c r="B503" t="s">
-        <v>198</v>
+        <v>305</v>
       </c>
       <c r="C503" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D503" t="s">
         <v>298</v>
@@ -11579,7 +11600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>179</v>
       </c>
@@ -11587,7 +11608,7 @@
         <v>198</v>
       </c>
       <c r="C504" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D504" t="s">
         <v>298</v>
@@ -11599,7 +11620,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>179</v>
       </c>
@@ -11607,7 +11628,7 @@
         <v>198</v>
       </c>
       <c r="C505" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D505" t="s">
         <v>298</v>
@@ -11619,18 +11640,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>179</v>
       </c>
       <c r="B506" t="s">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="C506" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="D506" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="E506" t="s">
         <v>220</v>
@@ -11639,64 +11660,46 @@
         <v>12</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B507" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="C507" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="D507" t="s">
-        <v>298</v>
-      </c>
-      <c r="E507" t="s">
-        <v>220</v>
-      </c>
-      <c r="F507" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B508" t="s">
-        <v>198</v>
+        <v>38</v>
       </c>
       <c r="C508" t="s">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="D508" t="s">
-        <v>298</v>
-      </c>
-      <c r="E508" t="s">
-        <v>220</v>
-      </c>
-      <c r="F508" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="B509" t="s">
-        <v>205</v>
+        <v>26</v>
       </c>
       <c r="C509" t="s">
-        <v>316</v>
+        <v>61</v>
       </c>
       <c r="D509" t="s">
-        <v>315</v>
-      </c>
-      <c r="E509" t="s">
-        <v>220</v>
-      </c>
-      <c r="F509" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9930A843-9C8A-4B2A-9BE1-EC59E1969962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EF558C-5572-47A6-8C94-9EC5B90C83EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sport-artwork review" sheetId="1" r:id="rId1"/>
     <sheet name="BilledeListe" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Forsvundne (havde valg)" sheetId="3" r:id="rId3"/>
-    <sheet name="Vejledning" sheetId="4" r:id="rId4"/>
+    <sheet name="Vejledning" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sport-artwork review'!$A$1:$H$1</definedName>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="334">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -65,66 +64,63 @@
     <t>(intet billede)</t>
   </si>
   <si>
+    <t>Faster</t>
+  </si>
+  <si>
+    <t>Forsvundet sporløst</t>
+  </si>
+  <si>
+    <t>Gridiron Gang</t>
+  </si>
+  <si>
+    <t>Hawaii Five-0</t>
+  </si>
+  <si>
+    <t>Jane Got a Gun</t>
+  </si>
+  <si>
+    <t>Last Light</t>
+  </si>
+  <si>
+    <t>NCIS</t>
+  </si>
+  <si>
+    <t>NCIS: Los Angeles</t>
+  </si>
+  <si>
+    <t>Pacific Blue</t>
+  </si>
+  <si>
+    <t>S.W.A.T.</t>
+  </si>
+  <si>
+    <t>Shipping Wars</t>
+  </si>
+  <si>
+    <t>Snitch</t>
+  </si>
+  <si>
+    <t>The Man Who Stole The Scream</t>
+  </si>
+  <si>
+    <t>Walking Tall</t>
+  </si>
+  <si>
+    <t>We Got This</t>
+  </si>
+  <si>
+    <t>C - DR1/DR2</t>
+  </si>
+  <si>
+    <t>DR1.dk</t>
+  </si>
+  <si>
+    <t>Aftenshowet</t>
+  </si>
+  <si>
     <t>X</t>
   </si>
   <si>
-    <t>Faster</t>
-  </si>
-  <si>
-    <t>Forsvundet sporløst</t>
-  </si>
-  <si>
-    <t>Gridiron Gang</t>
-  </si>
-  <si>
-    <t>Hawaii Five-0</t>
-  </si>
-  <si>
-    <t>Jane Got a Gun</t>
-  </si>
-  <si>
-    <t>Last Light</t>
-  </si>
-  <si>
-    <t>NCIS</t>
-  </si>
-  <si>
-    <t>NCIS: Los Angeles</t>
-  </si>
-  <si>
-    <t>Pacific Blue</t>
-  </si>
-  <si>
-    <t>S.W.A.T.</t>
-  </si>
-  <si>
-    <t>Shipping Wars</t>
-  </si>
-  <si>
-    <t>Snitch</t>
-  </si>
-  <si>
-    <t>The Man Who Stole The Scream</t>
-  </si>
-  <si>
-    <t>Walking Tall</t>
-  </si>
-  <si>
-    <t>We Got This</t>
-  </si>
-  <si>
-    <t>C - DR1/DR2</t>
-  </si>
-  <si>
-    <t>DR1.dk</t>
-  </si>
-  <si>
-    <t>Aftenshowet</t>
-  </si>
-  <si>
-    <t>TMDb</t>
-  </si>
-  <si>
     <t>Alene i vildmarken Australien</t>
   </si>
   <si>
@@ -194,6 +190,9 @@
     <t>Deadline: Kampen om elbilerne</t>
   </si>
   <si>
+    <t>Deadline: Må en anklager bære tørklæde?</t>
+  </si>
+  <si>
     <t>Debatten</t>
   </si>
   <si>
@@ -972,231 +971,6 @@
   </si>
   <si>
     <t>tv3sport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Tidligere valgt billede</t>
-  </si>
-  <si>
-    <t>Danskerklubben</t>
-  </si>
-  <si>
-    <t>Darts: World Grand Prix</t>
-  </si>
-  <si>
-    <t>EHF European League</t>
-  </si>
-  <si>
-    <t>EHF European League: Karvina-TTH Holstebro (m)</t>
-  </si>
-  <si>
-    <t>EHF European League: Mors - Thy - MOL Tatabanya</t>
-  </si>
-  <si>
-    <t>EHF Men's European League: HCB Karvina - TTH Holstebro</t>
-  </si>
-  <si>
-    <t>EHF Men's European League: Mors-Thy - MOL Tatabanya</t>
-  </si>
-  <si>
-    <t>EHF Women's Champions League</t>
-  </si>
-  <si>
-    <t>EHF Women's Champions League: Odense Håndbold - Storhamar</t>
-  </si>
-  <si>
-    <t>EHF Women's Champions League: Odense-Storhamar (k)</t>
-  </si>
-  <si>
-    <t>EHF Women's Champions League: Team Esbjerg - Buducnost</t>
-  </si>
-  <si>
-    <t>EHF Women's Champions League: Team Esbjerg-Buducnost (k)</t>
-  </si>
-  <si>
-    <t>F1: Bahrains Grand Prix - Løbet</t>
-  </si>
-  <si>
-    <t>Formel 1: Bahrains Grand Prix</t>
-  </si>
-  <si>
-    <t>Formel 1: Studiet</t>
-  </si>
-  <si>
-    <t>NHL</t>
-  </si>
-  <si>
-    <t>NHL: New York Rangers - Utah Mammoth</t>
-  </si>
-  <si>
-    <t>NHL: Tampa Bay Lightning - Philadelphia Flyers</t>
-  </si>
-  <si>
-    <t>NHL: Tampa Bay-Philadelphia</t>
-  </si>
-  <si>
-    <t>Sportstalk: Sportstalk: Ronaldos uværdige exit</t>
-  </si>
-  <si>
-    <t>TV-Udbruddet</t>
-  </si>
-  <si>
-    <t>TV-Udbruddet: TV - udbruddet</t>
-  </si>
-  <si>
-    <t>Watt the F1!?</t>
-  </si>
-  <si>
-    <t>B - TV2 Sport/TV2 Sport X/TV2</t>
-  </si>
-  <si>
-    <t>ATP: Alcaraz-Shapovalov, kvartfinale, Tokyo</t>
-  </si>
-  <si>
-    <t>ATP: Kvartfinaler, Beijing</t>
-  </si>
-  <si>
-    <t>ATP: Semifinale, Beijing</t>
-  </si>
-  <si>
-    <t>ATP: Semifinale, Tokyo</t>
-  </si>
-  <si>
-    <t>ATP: Vacherot-Fils, kvartfinale, Tokyo</t>
-  </si>
-  <si>
-    <t>ATP: Zverev-Djokovic, kvartfinale, Beijing</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League - Det bedste fra dagen</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League - Studie</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League - Studie: UEFA Nations League: Studiet</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: Rumænien-Sverige</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Bosnien-Hercegovina - Polen</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Cypern-Letland</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: England-Tjekkiet</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Frankrig-Belgien</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Grækenland-Tyskland</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Holland-Serbien</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Italien-Tyrkiet</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Kasakhstan-Færøerne</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Kosovo-Østrig</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Kroatien-Spanien</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Portugal-Norge</t>
-  </si>
-  <si>
-    <t>Fodbold: Nations League: UEFA Nations League: Wales-Danmark</t>
-  </si>
-  <si>
-    <t>Mads Pedersens grønne Tour-triumf</t>
-  </si>
-  <si>
-    <t>NFL: NFL: Washington Commanders-Indianapolis Colts</t>
-  </si>
-  <si>
-    <t>Tennis ATP 500.jpg</t>
-  </si>
-  <si>
-    <t>NFL: Washington Commanders-Indianapolis Colts</t>
-  </si>
-  <si>
-    <t>Tennis: ATP - Tokyo</t>
-  </si>
-  <si>
-    <t>Tennis: ATP - Tokyo: ATP: Semifinale, Tokyo</t>
-  </si>
-  <si>
-    <t>Tennis: ATP 500 - Beijing - Kampe</t>
-  </si>
-  <si>
-    <t>Tennis: ATP 500 - Beijing - Kampe: ATP: Semifinale, Beijing</t>
-  </si>
-  <si>
-    <t>Tennis: WTA 1000 - Beijng - Kampe</t>
-  </si>
-  <si>
-    <t>Tennis: WTA 1000 - Beijng - Kampe: WTA: Beijing</t>
-  </si>
-  <si>
-    <t>UEFA Nations League - Det bedste fra dagen</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Aserbajdsjan-Litauen</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Bosnien-Hercegovina - Polen</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Cypern-Letland</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Frankrig-Belgien</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Før Wales-Danmark</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Grækenland-Tyskland</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Holland-Serbien</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Italien-Tyrkiet</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Kosovo-Østrig</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Kroatien-England</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Portugal-Norge</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Rumænien-Sverige</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Spanien-Tjekkiet</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Studiet</t>
-  </si>
-  <si>
-    <t>UEFA Nations League: Wales-Danmark</t>
-  </si>
-  <si>
-    <t>WTA: Muchova-Samsonova, Beijing</t>
   </si>
   <si>
     <t>Sådan bruger du denne fil</t>
@@ -1618,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1658,2391 +1432,2412 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D62" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C65" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D66" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G66" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D68" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G68" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D69" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
       </c>
       <c r="G71" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D72" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C73" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C74" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
       </c>
       <c r="G74" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
       </c>
       <c r="G76" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D77" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G77" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D79" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D80" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G80" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D81" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
       </c>
       <c r="G84" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
       </c>
       <c r="G86" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C87" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D89" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C92" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C95" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C96" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
       </c>
       <c r="G96" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
       </c>
       <c r="G97" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C99" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
       </c>
       <c r="G100" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C102" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D102" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G102" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D103" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G103" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="D104" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G104" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B105" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
       </c>
       <c r="G105" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D106" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G106" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B107" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
       </c>
       <c r="G107" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B108" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
       </c>
       <c r="G108" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C109" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
       </c>
       <c r="G109" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B110" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C110" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
         <v>11</v>
       </c>
       <c r="G110" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C111" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B112" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D112" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G112" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B113" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C113" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
       </c>
       <c r="G113" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B114" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C114" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G114" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C115" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
       </c>
       <c r="G115" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C116" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D116" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G116" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C117" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D117" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G117" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B118" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D118" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G118" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C119" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
       </c>
       <c r="G119" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B120" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C120" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D120" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G120" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C121" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
       </c>
       <c r="G121" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C122" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D122" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G122" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B123" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C123" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
       </c>
       <c r="G123" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B124" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D124" t="s">
         <v>11</v>
       </c>
       <c r="G124" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B125" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C125" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
       </c>
       <c r="G125" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B126" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D126" t="s">
         <v>11</v>
       </c>
       <c r="G126" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
       </c>
       <c r="G127" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
       </c>
       <c r="G128" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="D129" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G129" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
       </c>
       <c r="G130" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C131" t="s">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
       </c>
       <c r="G131" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="D132" t="s">
         <v>11</v>
       </c>
       <c r="G132" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
       </c>
       <c r="G133" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G134" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
       </c>
       <c r="G135" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G136" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
       </c>
       <c r="G137" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="D138" t="s">
         <v>11</v>
       </c>
       <c r="G138" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C139" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
       </c>
       <c r="G139" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C140" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="D140" t="s">
         <v>11</v>
       </c>
       <c r="G140" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G141" t="s">
-        <v>12</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" t="s">
+        <v>26</v>
+      </c>
+      <c r="D142" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H142">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E141" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E142" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>BilledeValgListe</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:G141" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:G142" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4852,828 +4647,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>322</v>
-      </c>
-      <c r="C8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>324</v>
-      </c>
-      <c r="C10" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>325</v>
-      </c>
-      <c r="C11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>326</v>
-      </c>
-      <c r="C12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>328</v>
-      </c>
-      <c r="C14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>329</v>
-      </c>
-      <c r="C15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>330</v>
-      </c>
-      <c r="C16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>331</v>
-      </c>
-      <c r="C17" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>332</v>
-      </c>
-      <c r="C18" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>333</v>
-      </c>
-      <c r="C19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>334</v>
-      </c>
-      <c r="C20" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>335</v>
-      </c>
-      <c r="C21" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>336</v>
-      </c>
-      <c r="C22" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>337</v>
-      </c>
-      <c r="C23" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>338</v>
-      </c>
-      <c r="C24" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>339</v>
-      </c>
-      <c r="B25" t="s">
-        <v>340</v>
-      </c>
-      <c r="C25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>339</v>
-      </c>
-      <c r="B26" t="s">
-        <v>341</v>
-      </c>
-      <c r="C26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>339</v>
-      </c>
-      <c r="B27" t="s">
-        <v>342</v>
-      </c>
-      <c r="C27" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>339</v>
-      </c>
-      <c r="B28" t="s">
-        <v>343</v>
-      </c>
-      <c r="C28" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>339</v>
-      </c>
-      <c r="B29" t="s">
-        <v>344</v>
-      </c>
-      <c r="C29" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>339</v>
-      </c>
-      <c r="B30" t="s">
-        <v>345</v>
-      </c>
-      <c r="C30" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>339</v>
-      </c>
-      <c r="B31" t="s">
-        <v>346</v>
-      </c>
-      <c r="C31" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>339</v>
-      </c>
-      <c r="B32" t="s">
-        <v>347</v>
-      </c>
-      <c r="C32" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>339</v>
-      </c>
-      <c r="B33" t="s">
-        <v>348</v>
-      </c>
-      <c r="C33" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>339</v>
-      </c>
-      <c r="B34" t="s">
-        <v>349</v>
-      </c>
-      <c r="C34" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>339</v>
-      </c>
-      <c r="B35" t="s">
-        <v>350</v>
-      </c>
-      <c r="C35" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>339</v>
-      </c>
-      <c r="B36" t="s">
-        <v>351</v>
-      </c>
-      <c r="C36" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>339</v>
-      </c>
-      <c r="B37" t="s">
-        <v>352</v>
-      </c>
-      <c r="C37" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>339</v>
-      </c>
-      <c r="B38" t="s">
-        <v>353</v>
-      </c>
-      <c r="C38" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>339</v>
-      </c>
-      <c r="B39" t="s">
-        <v>354</v>
-      </c>
-      <c r="C39" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>339</v>
-      </c>
-      <c r="B40" t="s">
-        <v>355</v>
-      </c>
-      <c r="C40" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>339</v>
-      </c>
-      <c r="B41" t="s">
-        <v>356</v>
-      </c>
-      <c r="C41" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>339</v>
-      </c>
-      <c r="B42" t="s">
-        <v>357</v>
-      </c>
-      <c r="C42" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>339</v>
-      </c>
-      <c r="B43" t="s">
-        <v>358</v>
-      </c>
-      <c r="C43" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>339</v>
-      </c>
-      <c r="B44" t="s">
-        <v>359</v>
-      </c>
-      <c r="C44" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>339</v>
-      </c>
-      <c r="B45" t="s">
-        <v>360</v>
-      </c>
-      <c r="C45" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>339</v>
-      </c>
-      <c r="B46" t="s">
-        <v>361</v>
-      </c>
-      <c r="C46" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>339</v>
-      </c>
-      <c r="B47" t="s">
-        <v>362</v>
-      </c>
-      <c r="C47" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>339</v>
-      </c>
-      <c r="B48" t="s">
-        <v>363</v>
-      </c>
-      <c r="C48" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>339</v>
-      </c>
-      <c r="B49" t="s">
-        <v>364</v>
-      </c>
-      <c r="C49" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>339</v>
-      </c>
-      <c r="B50" t="s">
-        <v>366</v>
-      </c>
-      <c r="C50" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>339</v>
-      </c>
-      <c r="B51" t="s">
-        <v>367</v>
-      </c>
-      <c r="C51" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>339</v>
-      </c>
-      <c r="B52" t="s">
-        <v>368</v>
-      </c>
-      <c r="C52" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>339</v>
-      </c>
-      <c r="B53" t="s">
-        <v>369</v>
-      </c>
-      <c r="C53" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>339</v>
-      </c>
-      <c r="B54" t="s">
-        <v>370</v>
-      </c>
-      <c r="C54" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>339</v>
-      </c>
-      <c r="B55" t="s">
-        <v>371</v>
-      </c>
-      <c r="C55" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>339</v>
-      </c>
-      <c r="B56" t="s">
-        <v>372</v>
-      </c>
-      <c r="C56" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>339</v>
-      </c>
-      <c r="B57" t="s">
-        <v>373</v>
-      </c>
-      <c r="C57" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>339</v>
-      </c>
-      <c r="B58" t="s">
-        <v>374</v>
-      </c>
-      <c r="C58" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>339</v>
-      </c>
-      <c r="B59" t="s">
-        <v>375</v>
-      </c>
-      <c r="C59" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>339</v>
-      </c>
-      <c r="B60" t="s">
-        <v>376</v>
-      </c>
-      <c r="C60" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>339</v>
-      </c>
-      <c r="B61" t="s">
-        <v>377</v>
-      </c>
-      <c r="C61" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>339</v>
-      </c>
-      <c r="B62" t="s">
-        <v>378</v>
-      </c>
-      <c r="C62" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>339</v>
-      </c>
-      <c r="B63" t="s">
-        <v>379</v>
-      </c>
-      <c r="C63" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>339</v>
-      </c>
-      <c r="B64" t="s">
-        <v>380</v>
-      </c>
-      <c r="C64" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>339</v>
-      </c>
-      <c r="B65" t="s">
-        <v>381</v>
-      </c>
-      <c r="C65" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>339</v>
-      </c>
-      <c r="B66" t="s">
-        <v>382</v>
-      </c>
-      <c r="C66" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>339</v>
-      </c>
-      <c r="B67" t="s">
-        <v>383</v>
-      </c>
-      <c r="C67" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>339</v>
-      </c>
-      <c r="B68" t="s">
-        <v>384</v>
-      </c>
-      <c r="C68" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>339</v>
-      </c>
-      <c r="B69" t="s">
-        <v>385</v>
-      </c>
-      <c r="C69" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>339</v>
-      </c>
-      <c r="B70" t="s">
-        <v>386</v>
-      </c>
-      <c r="C70" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>339</v>
-      </c>
-      <c r="B71" t="s">
-        <v>387</v>
-      </c>
-      <c r="C71" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>339</v>
-      </c>
-      <c r="B72" t="s">
-        <v>388</v>
-      </c>
-      <c r="C72" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>339</v>
-      </c>
-      <c r="B73" t="s">
-        <v>389</v>
-      </c>
-      <c r="C73" t="s">
-        <v>250</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5683,7 +4656,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>390</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5691,50 +4664,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>391</v>
+        <v>316</v>
       </c>
       <c r="B3" t="s">
-        <v>392</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>393</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>394</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>395</v>
+        <v>320</v>
       </c>
       <c r="B5" t="s">
-        <v>396</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>397</v>
+        <v>322</v>
       </c>
       <c r="B6" t="s">
-        <v>398</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>399</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
-        <v>400</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>401</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
-        <v>402</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5742,42 +4715,42 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
-        <v>404</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="B11" t="s">
-        <v>405</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="B12" t="s">
-        <v>406</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="B13" t="s">
-        <v>407</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>403</v>
+        <v>328</v>
       </c>
       <c r="B14" t="s">
-        <v>408</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EF558C-5572-47A6-8C94-9EC5B90C83EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E038A59F-3F2B-4B4D-82AB-C759C6631CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sport-artwork review" sheetId="1" r:id="rId1"/>
@@ -64,6 +64,9 @@
     <t>(intet billede)</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
     <t>Faster</t>
   </si>
   <si>
@@ -116,9 +119,6 @@
   </si>
   <si>
     <t>Aftenshowet</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>Alene i vildmarken Australien</t>
@@ -1432,2399 +1432,2399 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
         <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
         <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
         <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
         <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
         <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B57" t="s">
         <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B64" t="s">
         <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
       </c>
       <c r="G66" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
       </c>
       <c r="G71" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C72" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B73" t="s">
         <v>32</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B78" t="s">
         <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B80" t="s">
         <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
       </c>
       <c r="G80" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C81" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
       </c>
       <c r="G82" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C83" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B84" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C87" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B88" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B89" t="s">
         <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B91" t="s">
         <v>32</v>
       </c>
       <c r="C91" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B93" t="s">
         <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B94" t="s">
         <v>32</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B96" t="s">
         <v>32</v>
       </c>
       <c r="C96" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
       </c>
       <c r="G96" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B97" t="s">
         <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B98" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B99" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C99" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B100" t="s">
         <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
       </c>
       <c r="G100" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C101" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B102" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
       </c>
       <c r="G102" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C103" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B104" t="s">
         <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
       </c>
       <c r="G104" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
       </c>
       <c r="G105" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C106" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
       </c>
       <c r="G106" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
       </c>
       <c r="G107" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C108" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
       </c>
       <c r="G108" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B109" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
       </c>
       <c r="G109" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B110" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D110" t="s">
         <v>11</v>
       </c>
       <c r="G110" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B111" t="s">
         <v>32</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C112" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D112" t="s">
         <v>11</v>
       </c>
       <c r="G112" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C113" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
       </c>
       <c r="G113" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B114" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D114" t="s">
         <v>11</v>
       </c>
       <c r="G114" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
       </c>
       <c r="G115" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B116" t="s">
         <v>32</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D116" t="s">
         <v>11</v>
       </c>
       <c r="G116" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C118" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D118" t="s">
         <v>11</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B119" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C119" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
       </c>
       <c r="G119" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B120" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C120" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
       </c>
       <c r="G120" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C121" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
       </c>
       <c r="G121" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B122" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C122" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D122" t="s">
         <v>11</v>
       </c>
       <c r="G122" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B123" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
       </c>
       <c r="G123" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C124" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="D124" t="s">
         <v>11</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B125" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C125" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
       </c>
       <c r="G125" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B126" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C126" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D126" t="s">
         <v>11</v>
       </c>
       <c r="G126" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C127" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
       </c>
       <c r="G127" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C128" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
       </c>
       <c r="G128" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C129" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
       </c>
       <c r="G129" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C130" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
       </c>
       <c r="G130" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C131" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
       </c>
       <c r="G131" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C132" t="s">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="D132" t="s">
         <v>11</v>
       </c>
       <c r="G132" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
       </c>
       <c r="G133" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
       </c>
       <c r="G134" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C135" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
       </c>
       <c r="G135" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C136" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="D136" t="s">
         <v>11</v>
       </c>
       <c r="G136" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C137" t="s">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
       </c>
       <c r="G137" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B138" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C138" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="D138" t="s">
         <v>11</v>
       </c>
       <c r="G138" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C139" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
       </c>
       <c r="G139" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C140" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="D140" t="s">
         <v>11</v>
       </c>
       <c r="G140" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C141" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
       </c>
       <c r="G141" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C142" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="D142" t="s">
         <v>11</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E038A59F-3F2B-4B4D-82AB-C759C6631CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC18EA0-DCB6-45EF-93CD-F60137BD7D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="336">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -67,6 +67,9 @@
     <t>X</t>
   </si>
   <si>
+    <t>Black Adam</t>
+  </si>
+  <si>
     <t>Faster</t>
   </si>
   <si>
@@ -79,9 +82,6 @@
     <t>Hawaii Five-0</t>
   </si>
   <si>
-    <t>Jane Got a Gun</t>
-  </si>
-  <si>
     <t>Last Light</t>
   </si>
   <si>
@@ -127,9 +127,6 @@
     <t>DR2.dk</t>
   </si>
   <si>
-    <t>Alle Guds farver</t>
-  </si>
-  <si>
     <t>Alt forladt - Civilbunkeren Regan Vest</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>Angkor Vats hemmeligheder</t>
   </si>
   <si>
-    <t>Balladen om det beskidte vand</t>
-  </si>
-  <si>
     <t>Baywatch bag facaden</t>
   </si>
   <si>
@@ -172,9 +166,6 @@
     <t>Danmarkshistorien fortalt af Erik Kjersgaard</t>
   </si>
   <si>
-    <t>Dansk teater 300 år: Absurdismen og revyerne</t>
-  </si>
-  <si>
     <t>DR1.dk; DR2.dk</t>
   </si>
   <si>
@@ -202,12 +193,15 @@
     <t>Den klassiske musikquiz</t>
   </si>
   <si>
-    <t>Dengang vi var bønder</t>
+    <t>Dirch og de andre</t>
   </si>
   <si>
     <t>Drømmen om et liv på landet</t>
   </si>
   <si>
+    <t>Dyrenes underverden</t>
+  </si>
+  <si>
     <t>Dæknavn: Anna - jagten på en krigsforbryder</t>
   </si>
   <si>
@@ -220,60 +214,63 @@
     <t>Et hus af splinter</t>
   </si>
   <si>
-    <t>Farlig drømmedate</t>
-  </si>
-  <si>
-    <t>Filmperler: Love Lies Bleeding</t>
-  </si>
-  <si>
-    <t>Fjeldvinter i det nordlige Lapland</t>
+    <t>Fodbold: Canada - Danmark (k), direkte</t>
+  </si>
+  <si>
+    <t>Fodbold.jpg</t>
   </si>
   <si>
     <t>Folketingets åbning: Nyt år i dansk politik</t>
   </si>
   <si>
-    <t>Frank &amp; Kastaniegaarden - Automatvanding med fjer og fåreuld</t>
+    <t>FredagsTamTam</t>
   </si>
   <si>
     <t>Galskab: Journal nr. 3072 - Digterens kæreste</t>
   </si>
   <si>
+    <t>Galskab: Soldaten fra vestfronten</t>
+  </si>
+  <si>
     <t>Gift ved første blik</t>
   </si>
   <si>
-    <t>Guldkorn 1970'erne:</t>
-  </si>
-  <si>
     <t>Hammerslag 2022 - Den klassiske murermestervilla</t>
   </si>
   <si>
-    <t>Hammerslag 2022 - Rækkehuse fra 60'erne</t>
-  </si>
-  <si>
     <t>Hammerslag 2022 - Sommerhus i klitterne</t>
   </si>
   <si>
+    <t>Hammerslag 2022 - Vilde kvadratmeter</t>
+  </si>
+  <si>
     <t>Historien om den norske kongefamilie</t>
   </si>
   <si>
-    <t>Holgers største kamp - We are so back, baby!</t>
-  </si>
-  <si>
     <t>Huse med hemmeligheder</t>
   </si>
   <si>
+    <t>Huset på Christianshavn</t>
+  </si>
+  <si>
     <t>Husker du...</t>
   </si>
   <si>
     <t>Hvad tror danskerne på: Hvad har du stjålet?</t>
   </si>
   <si>
-    <t>Håbet i Himmerland</t>
+    <t>Hvornår var det nu det var</t>
+  </si>
+  <si>
+    <t>I haven med Søren Ryge: Alger, mos og lav</t>
   </si>
   <si>
     <t>I magtens korridorer</t>
   </si>
   <si>
+    <t>Jagten på Danmarkshistorien</t>
+  </si>
+  <si>
     <t>Jens i vildmarken</t>
   </si>
   <si>
@@ -295,18 +292,24 @@
     <t>Kender Du Typen? 2019 - med sansefest og færdigmad</t>
   </si>
   <si>
-    <t>Kender Du Typen? 2019 - med stripperstang og biksemad</t>
-  </si>
-  <si>
     <t>Kender Du Typen? 2020 - med kanindragt og kopsamling</t>
   </si>
   <si>
     <t>Kender Du Typen? 2020 - med slik og strømpebuksecreme</t>
   </si>
   <si>
+    <t>Kender Du Typen? 2020 - med træsko og designertøj</t>
+  </si>
+  <si>
+    <t>Kirsebærhaven 89</t>
+  </si>
+  <si>
     <t>Kodeknækkerne</t>
   </si>
   <si>
+    <t>Kommissionen</t>
+  </si>
+  <si>
     <t>Kommissionen - Bombetrussel i baghaven, DFs Trump-tricks og racistisk svinestop</t>
   </si>
   <si>
@@ -334,6 +337,9 @@
     <t>Kriminalkommissær Barnaby XII: Mord ved 13. hul</t>
   </si>
   <si>
+    <t>Kriminalkommissær Barnaby XII: Spioner</t>
+  </si>
+  <si>
     <t>Kriminelt: Drabene på de polske håndværkere</t>
   </si>
   <si>
@@ -343,21 +349,12 @@
     <t>Kunsten at bygge en metro</t>
   </si>
   <si>
-    <t>Kunstnerkolonien på Sydfyn</t>
-  </si>
-  <si>
     <t>Loppemarkedstips: Møbler og lamper</t>
   </si>
   <si>
-    <t>Ludere, lommetyve og lirekassemænd</t>
-  </si>
-  <si>
     <t>Mens vi venter på at dø - Pelser vi haven</t>
   </si>
   <si>
-    <t>Mesterstrikkerne</t>
-  </si>
-  <si>
     <t>Mig og 60'erne: Mode</t>
   </si>
   <si>
@@ -370,18 +367,18 @@
     <t>Nul stjerner - Ferie i landet der ikke findes</t>
   </si>
   <si>
-    <t>Nul stjerner - Finder forladte steder</t>
+    <t>Nul stjerner - På provinsferie i Gedser</t>
   </si>
   <si>
     <t>Nul stjerner - På toppen af Sverige</t>
   </si>
   <si>
-    <t>Nul stjerner - Storbyferie i Tokyo</t>
-  </si>
-  <si>
     <t>OBS</t>
   </si>
   <si>
+    <t>Once Upon a Time... in Hollywood</t>
+  </si>
+  <si>
     <t>Optimistens guide til planeten</t>
   </si>
   <si>
@@ -391,7 +388,10 @@
     <t>P3 Essensen: Derfor dør vi tidligere end svenskerne</t>
   </si>
   <si>
-    <t>På rejse med Griff - Sydstaterne</t>
+    <t>På et hængende hår</t>
+  </si>
+  <si>
+    <t>På skuldrene af H. C. Ørsted - Hvad var der før Big Bang?</t>
   </si>
   <si>
     <t>Radioavisen</t>
@@ -403,9 +403,6 @@
     <t>RO PÅ med DR Symfoniorkestret: Dyrehaven</t>
   </si>
   <si>
-    <t>RO PÅ med DR Symfoniorkestret: Lys over havet</t>
-  </si>
-  <si>
     <t>Råzone</t>
   </si>
   <si>
@@ -421,28 +418,46 @@
     <t>Signe Molde på udebane: Hash er harmløst</t>
   </si>
   <si>
+    <t>Skattejægerne</t>
+  </si>
+  <si>
     <t>Skærmfri på 100 dage</t>
   </si>
   <si>
     <t>Smagen af Italien</t>
   </si>
   <si>
+    <t>Smilehullet - Georg Carl "Crazy med Daisy"</t>
+  </si>
+  <si>
     <t>Sporløs UK</t>
   </si>
   <si>
+    <t>Sporløs UK - Sådan gik det</t>
+  </si>
+  <si>
     <t>Supermagternes kamp: USA vs. Kina</t>
   </si>
   <si>
+    <t>Syng med Puk og Claus</t>
+  </si>
+  <si>
     <t>Søren Vester bygger sommerhus</t>
   </si>
   <si>
+    <t>The A-Team</t>
+  </si>
+  <si>
     <t>The Capture</t>
   </si>
   <si>
     <t>The Dark</t>
   </si>
   <si>
-    <t>The Guest</t>
+    <t>Troldspejlet special - Troldspejlet nyder rædslerne</t>
+  </si>
+  <si>
+    <t>Troldspejlet: Odysseens monstre</t>
   </si>
   <si>
     <t>Trumps USA</t>
@@ -463,12 +478,6 @@
     <t>Verdens mest eftersøgte våbenhandler</t>
   </si>
   <si>
-    <t>Verdenssituationen med Clement: Hvis Putin tester os</t>
-  </si>
-  <si>
-    <t>Vi er stjernestøv</t>
-  </si>
-  <si>
     <t>Vild viden</t>
   </si>
   <si>
@@ -481,16 +490,13 @@
     <t>Vogter</t>
   </si>
   <si>
-    <t>Vores planet</t>
-  </si>
-  <si>
     <t>Vores største dage - Dåb</t>
   </si>
   <si>
-    <t>Vores største dage - Konfirmation</t>
-  </si>
-  <si>
     <t>Vores Vejr</t>
+  </si>
+  <si>
+    <t>Woman of the Hour</t>
   </si>
   <si>
     <t>Øgendahl og de store forfattere: Tove Ditlevsen</t>
@@ -1392,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1455,7 +1461,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1472,7 +1478,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1489,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1506,7 +1512,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1523,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -1540,7 +1546,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1557,7 +1563,7 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1574,7 +1580,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1591,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1608,7 +1614,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1625,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1642,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1659,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1676,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1687,13 +1693,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1710,7 +1716,7 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1724,10 +1730,10 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1744,7 +1750,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1761,7 +1767,7 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1778,7 +1784,7 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1792,10 +1798,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1812,7 +1818,7 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1826,10 +1832,10 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1846,7 +1852,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1863,7 +1869,7 @@
         <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -1880,7 +1886,7 @@
         <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1894,10 +1900,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -1911,10 +1917,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -1928,10 +1934,10 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -1945,10 +1951,10 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -1965,7 +1971,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -1982,7 +1988,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -1999,7 +2005,7 @@
         <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2013,10 +2019,10 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -2030,10 +2036,10 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -2047,10 +2053,10 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -2067,7 +2073,7 @@
         <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2081,10 +2087,10 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2101,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2118,7 +2124,7 @@
         <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2135,7 +2141,7 @@
         <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2152,7 +2158,7 @@
         <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -2169,7 +2175,7 @@
         <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -2186,7 +2192,7 @@
         <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -2200,13 +2206,13 @@
         <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -2220,7 +2226,7 @@
         <v>29</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2234,10 +2240,10 @@
         <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2251,10 +2257,10 @@
         <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2271,7 +2277,7 @@
         <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2288,7 +2294,7 @@
         <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2305,7 +2311,7 @@
         <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2322,7 +2328,7 @@
         <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2336,10 +2342,10 @@
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2353,10 +2359,10 @@
         <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2373,7 +2379,7 @@
         <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2387,10 +2393,10 @@
         <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -2404,10 +2410,10 @@
         <v>28</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C59" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2421,10 +2427,10 @@
         <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C60" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2441,7 +2447,7 @@
         <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -2458,7 +2464,7 @@
         <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2475,7 +2481,7 @@
         <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -2489,10 +2495,10 @@
         <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -2506,10 +2512,10 @@
         <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -2523,10 +2529,10 @@
         <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -2540,10 +2546,10 @@
         <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -2560,7 +2566,7 @@
         <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -2577,7 +2583,7 @@
         <v>32</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -2591,10 +2597,10 @@
         <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -2611,7 +2617,7 @@
         <v>29</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -2625,10 +2631,10 @@
         <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C72" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -2642,10 +2648,10 @@
         <v>28</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -2662,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="C74" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
@@ -2676,10 +2682,10 @@
         <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C75" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -2693,10 +2699,10 @@
         <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C76" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -2713,7 +2719,7 @@
         <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -2727,10 +2733,10 @@
         <v>28</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -2744,10 +2750,10 @@
         <v>28</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -2761,10 +2767,10 @@
         <v>28</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
@@ -2778,10 +2784,10 @@
         <v>28</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -2795,10 +2801,10 @@
         <v>28</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
@@ -2815,7 +2821,7 @@
         <v>29</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
@@ -2832,7 +2838,7 @@
         <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
@@ -2849,7 +2855,7 @@
         <v>29</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -2866,7 +2872,7 @@
         <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
@@ -2883,7 +2889,7 @@
         <v>29</v>
       </c>
       <c r="C87" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
@@ -2900,7 +2906,7 @@
         <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
@@ -2917,7 +2923,7 @@
         <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -2934,7 +2940,7 @@
         <v>32</v>
       </c>
       <c r="C90" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
@@ -2948,10 +2954,10 @@
         <v>28</v>
       </c>
       <c r="B91" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C91" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
@@ -2965,10 +2971,10 @@
         <v>28</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C92" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
@@ -2985,7 +2991,7 @@
         <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -3002,7 +3008,7 @@
         <v>32</v>
       </c>
       <c r="C94" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
@@ -3019,7 +3025,7 @@
         <v>29</v>
       </c>
       <c r="C95" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
@@ -3033,10 +3039,10 @@
         <v>28</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C96" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
@@ -3050,10 +3056,10 @@
         <v>28</v>
       </c>
       <c r="B97" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C97" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -3070,7 +3076,7 @@
         <v>29</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
@@ -3087,7 +3093,7 @@
         <v>29</v>
       </c>
       <c r="C99" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
@@ -3101,10 +3107,10 @@
         <v>28</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C100" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
@@ -3118,10 +3124,10 @@
         <v>28</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C101" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
@@ -3135,10 +3141,10 @@
         <v>28</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
@@ -3155,7 +3161,7 @@
         <v>29</v>
       </c>
       <c r="C103" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
@@ -3172,7 +3178,7 @@
         <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
@@ -3189,7 +3195,7 @@
         <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -3203,10 +3209,10 @@
         <v>28</v>
       </c>
       <c r="B106" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
@@ -3223,7 +3229,7 @@
         <v>32</v>
       </c>
       <c r="C107" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
@@ -3240,7 +3246,7 @@
         <v>32</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
@@ -3257,7 +3263,7 @@
         <v>32</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
@@ -3274,7 +3280,7 @@
         <v>32</v>
       </c>
       <c r="C110" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D110" t="s">
         <v>11</v>
@@ -3288,10 +3294,10 @@
         <v>28</v>
       </c>
       <c r="B111" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C111" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
@@ -3305,10 +3311,10 @@
         <v>28</v>
       </c>
       <c r="B112" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C112" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D112" t="s">
         <v>11</v>
@@ -3325,7 +3331,7 @@
         <v>32</v>
       </c>
       <c r="C113" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
@@ -3339,10 +3345,10 @@
         <v>28</v>
       </c>
       <c r="B114" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C114" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D114" t="s">
         <v>11</v>
@@ -3359,7 +3365,7 @@
         <v>29</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
@@ -3376,7 +3382,7 @@
         <v>32</v>
       </c>
       <c r="C116" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D116" t="s">
         <v>11</v>
@@ -3390,10 +3396,10 @@
         <v>28</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C117" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
@@ -3407,10 +3413,10 @@
         <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C118" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D118" t="s">
         <v>11</v>
@@ -3427,7 +3433,7 @@
         <v>29</v>
       </c>
       <c r="C119" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
@@ -3444,7 +3450,7 @@
         <v>32</v>
       </c>
       <c r="C120" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
@@ -3461,7 +3467,7 @@
         <v>29</v>
       </c>
       <c r="C121" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
@@ -3478,7 +3484,7 @@
         <v>29</v>
       </c>
       <c r="C122" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D122" t="s">
         <v>11</v>
@@ -3495,7 +3501,7 @@
         <v>29</v>
       </c>
       <c r="C123" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
@@ -3512,7 +3518,7 @@
         <v>29</v>
       </c>
       <c r="C124" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D124" t="s">
         <v>11</v>
@@ -3526,10 +3532,10 @@
         <v>28</v>
       </c>
       <c r="B125" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C125" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
@@ -3543,10 +3549,10 @@
         <v>28</v>
       </c>
       <c r="B126" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C126" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D126" t="s">
         <v>11</v>
@@ -3560,10 +3566,10 @@
         <v>28</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C127" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
@@ -3577,10 +3583,10 @@
         <v>28</v>
       </c>
       <c r="B128" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C128" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
@@ -3594,10 +3600,10 @@
         <v>28</v>
       </c>
       <c r="B129" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C129" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
@@ -3614,7 +3620,7 @@
         <v>32</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
@@ -3631,7 +3637,7 @@
         <v>29</v>
       </c>
       <c r="C131" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
@@ -3645,10 +3651,10 @@
         <v>28</v>
       </c>
       <c r="B132" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C132" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D132" t="s">
         <v>11</v>
@@ -3662,10 +3668,10 @@
         <v>28</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C133" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
@@ -3682,7 +3688,7 @@
         <v>29</v>
       </c>
       <c r="C134" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
@@ -3696,10 +3702,10 @@
         <v>28</v>
       </c>
       <c r="B135" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C135" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
@@ -3713,10 +3719,10 @@
         <v>28</v>
       </c>
       <c r="B136" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C136" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D136" t="s">
         <v>11</v>
@@ -3733,7 +3739,7 @@
         <v>29</v>
       </c>
       <c r="C137" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
@@ -3750,7 +3756,7 @@
         <v>32</v>
       </c>
       <c r="C138" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D138" t="s">
         <v>11</v>
@@ -3764,10 +3770,10 @@
         <v>28</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C139" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
@@ -3781,10 +3787,10 @@
         <v>28</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C140" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D140" t="s">
         <v>11</v>
@@ -3801,7 +3807,7 @@
         <v>32</v>
       </c>
       <c r="C141" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
@@ -3818,26 +3824,40 @@
         <v>32</v>
       </c>
       <c r="C142" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D142" t="s">
         <v>11</v>
       </c>
       <c r="G142" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" t="s">
+        <v>13</v>
+      </c>
+      <c r="D143" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H142">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H143">
       <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E142" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E143" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>BilledeValgListe</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:G142" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:G143" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3852,792 +3872,792 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4656,7 +4676,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4664,50 +4684,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4715,42 +4735,42 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC18EA0-DCB6-45EF-93CD-F60137BD7D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF09C96-1A5E-4FAB-B85C-2E6A7D06C6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="337">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -1034,6 +1034,9 @@
   </si>
   <si>
     <t>Rækker der ikke længere er aktuelle, men SOM havde et udfyldt valg (og ikke er ignoreret), havner i arket 'Forsvundne (havde valg)' - intet forsvinder usporligt.</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3845,6 +3848,14 @@
       </c>
       <c r="D143" t="s">
         <v>11</v>
+      </c>
+      <c r="G143" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G144" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FA656999CEDAAEEF63E30E577B213210DF138515" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E96612B-E39E-4382-936E-9A77A15ADDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sport-artwork review" sheetId="1" r:id="rId1"/>
     <sheet name="BilledeListe" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Forsvundne (havde valg)" sheetId="3" r:id="rId3"/>
-    <sheet name="Vejledning" sheetId="4" r:id="rId4"/>
+    <sheet name="Vejledning" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sport-artwork review'!$A$1:$H$1</definedName>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="353">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -1029,93 +1028,6 @@
   </si>
   <si>
     <t>tv3sport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Tidligere valgt billede</t>
-  </si>
-  <si>
-    <t>Champions Hockey League: Kölner Haie - Herning Blue Fox</t>
-  </si>
-  <si>
-    <t>Fodbold: Internationale Venskabskampe</t>
-  </si>
-  <si>
-    <t>Fodbold: Internationale Venskabskampe: Argentina - Benin</t>
-  </si>
-  <si>
-    <t>Football Friendly: Argentina - Benin</t>
-  </si>
-  <si>
-    <t>Formel 1 360°: Miami GP</t>
-  </si>
-  <si>
-    <t>Før Superligaen FC Midtjylland</t>
-  </si>
-  <si>
-    <t>Før Superligaen FC Midtjylland: Kan skaderne koste FCM mesterskabet?</t>
-  </si>
-  <si>
-    <t>NHL: Tampa Bay Lightning - Minnesota Wild</t>
-  </si>
-  <si>
-    <t>NHL: Washington Capitals - Pittsburgh Penguins</t>
-  </si>
-  <si>
-    <t>TV-Udbruddet: TV - Udbruddet: Skjelmoses sæson er slut</t>
-  </si>
-  <si>
-    <t>TV-Udbruddet: TV-Udbruddet: Skjelmoses sæson er slut</t>
-  </si>
-  <si>
-    <t>B - TV2 Sport/TV2 Sport X/TV2</t>
-  </si>
-  <si>
-    <t>ATP: Alcaraz-Lehecka, finale, Tokyo</t>
-  </si>
-  <si>
-    <t>ATP: Rune-Altmaier, Shanghai</t>
-  </si>
-  <si>
-    <t>ATP: Shanghai</t>
-  </si>
-  <si>
-    <t>Kvindeligaen: Viborg-Nykøbing F.</t>
-  </si>
-  <si>
-    <t>Tennis: ATP - Tokyo</t>
-  </si>
-  <si>
-    <t>Tennis: ATP - Tokyo: ATP: Alcaraz-Lehecka, finale, Tokyo</t>
-  </si>
-  <si>
-    <t>Tennis: ATP 1000 - Shanghai - Kampe</t>
-  </si>
-  <si>
-    <t>Tennis: ATP 1000 - Shanghai - Kampe: ATP: Shanghai</t>
-  </si>
-  <si>
-    <t>Tennis: ATP 500 - Beijing - Kampe</t>
-  </si>
-  <si>
-    <t>Tennis: ATP 500 - Beijing - Kampe: ATP: De Minaur-Djokovic, finale, Beijing</t>
-  </si>
-  <si>
-    <t>Tennis: WTA 1000 - Beijng - Kampe</t>
-  </si>
-  <si>
-    <t>Tennis: WTA 1000 - Beijng - Kampe: WTA: Beijing</t>
-  </si>
-  <si>
-    <t>Tennis: WTA 1000 - Beijng - Kampe: WTA: Kvartfinale, Beijing</t>
-  </si>
-  <si>
-    <t>WTA: Gauff-Mertens, Beijing</t>
-  </si>
-  <si>
-    <t>WTA: Kvartfinale, Beijing</t>
-  </si>
-  <si>
-    <t>WTA: Swiatek-Jovic, Beijing</t>
   </si>
   <si>
     <t>Sådan bruger du denne fil</t>
@@ -1600,10 +1512,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1614,10 +1529,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1628,7 +1546,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1645,10 +1563,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1659,7 +1580,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -1676,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1693,10 +1614,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1707,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1724,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1741,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1758,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1775,10 +1699,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1789,21 +1716,24 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1814,13 +1744,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1831,13 +1761,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1848,13 +1778,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1865,27 +1795,30 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>11</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1896,13 +1829,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1919,7 +1852,7 @@
         <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1933,10 +1866,10 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1950,10 +1883,10 @@
         <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -1967,10 +1900,10 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -1987,7 +1920,7 @@
         <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2004,7 +1937,7 @@
         <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -2021,7 +1954,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2038,7 +1971,7 @@
         <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -2055,7 +1988,7 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2069,10 +2002,10 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2086,10 +2019,10 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2103,10 +2036,10 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -2120,10 +2053,10 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2137,10 +2070,10 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -2154,10 +2087,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -2174,7 +2107,7 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -2188,10 +2121,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2208,7 +2141,7 @@
         <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2222,10 +2155,10 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2242,7 +2175,7 @@
         <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2256,10 +2189,10 @@
         <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2276,7 +2209,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -2290,10 +2223,10 @@
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -2307,10 +2240,10 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -2327,7 +2260,7 @@
         <v>42</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -2341,10 +2274,10 @@
         <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2358,10 +2291,10 @@
         <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2375,10 +2308,10 @@
         <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2392,13 +2325,13 @@
         <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
@@ -2412,7 +2345,7 @@
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2429,7 +2362,7 @@
         <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2443,10 +2376,10 @@
         <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2463,7 +2396,7 @@
         <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2477,10 +2410,10 @@
         <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2494,10 +2427,10 @@
         <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2514,10 +2447,10 @@
         <v>39</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D58" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G58" t="s">
         <v>12</v>
@@ -2531,7 +2464,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2548,7 +2481,7 @@
         <v>39</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2562,10 +2495,10 @@
         <v>38</v>
       </c>
       <c r="B61" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -2582,7 +2515,7 @@
         <v>42</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2599,7 +2532,7 @@
         <v>42</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -2613,10 +2546,10 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -2630,10 +2563,10 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -2647,10 +2580,10 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -2667,7 +2600,7 @@
         <v>39</v>
       </c>
       <c r="C67" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -2684,7 +2617,7 @@
         <v>42</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -2698,10 +2631,10 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -2715,10 +2648,10 @@
         <v>38</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C70" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -2735,7 +2668,7 @@
         <v>42</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -2752,7 +2685,7 @@
         <v>42</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -2766,10 +2699,10 @@
         <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -2786,7 +2719,7 @@
         <v>39</v>
       </c>
       <c r="C74" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
@@ -2803,7 +2736,7 @@
         <v>42</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -2817,10 +2750,10 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -2834,10 +2767,10 @@
         <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -2854,7 +2787,7 @@
         <v>42</v>
       </c>
       <c r="C78" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -2868,10 +2801,10 @@
         <v>38</v>
       </c>
       <c r="B79" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -2888,7 +2821,7 @@
         <v>39</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
@@ -2905,7 +2838,7 @@
         <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -2922,7 +2855,7 @@
         <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
@@ -2939,7 +2872,7 @@
         <v>42</v>
       </c>
       <c r="C83" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
@@ -2953,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="B84" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
@@ -2970,10 +2903,10 @@
         <v>38</v>
       </c>
       <c r="B85" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -2987,10 +2920,10 @@
         <v>38</v>
       </c>
       <c r="B86" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C86" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
@@ -3004,10 +2937,10 @@
         <v>38</v>
       </c>
       <c r="B87" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
@@ -3024,7 +2957,7 @@
         <v>39</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
@@ -3038,10 +2971,10 @@
         <v>38</v>
       </c>
       <c r="B89" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C89" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
@@ -3055,10 +2988,10 @@
         <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
@@ -3075,7 +3008,7 @@
         <v>39</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
@@ -3092,7 +3025,7 @@
         <v>39</v>
       </c>
       <c r="C92" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
@@ -3106,10 +3039,10 @@
         <v>38</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -3123,10 +3056,10 @@
         <v>38</v>
       </c>
       <c r="B94" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C94" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
@@ -3143,7 +3076,7 @@
         <v>39</v>
       </c>
       <c r="C95" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
@@ -3157,10 +3090,10 @@
         <v>38</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C96" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
@@ -3174,10 +3107,10 @@
         <v>38</v>
       </c>
       <c r="B97" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -3191,10 +3124,10 @@
         <v>38</v>
       </c>
       <c r="B98" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C98" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
@@ -3211,7 +3144,7 @@
         <v>39</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
@@ -3225,10 +3158,10 @@
         <v>38</v>
       </c>
       <c r="B100" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
@@ -3245,7 +3178,7 @@
         <v>39</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
@@ -3262,7 +3195,7 @@
         <v>39</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
@@ -3276,10 +3209,10 @@
         <v>38</v>
       </c>
       <c r="B103" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
@@ -3293,10 +3226,10 @@
         <v>38</v>
       </c>
       <c r="B104" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
@@ -3310,10 +3243,10 @@
         <v>38</v>
       </c>
       <c r="B105" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C105" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -3330,7 +3263,7 @@
         <v>39</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
@@ -3344,10 +3277,10 @@
         <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C107" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
@@ -3361,10 +3294,10 @@
         <v>38</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C108" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
@@ -3378,10 +3311,10 @@
         <v>38</v>
       </c>
       <c r="B109" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C109" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
@@ -3398,7 +3331,7 @@
         <v>39</v>
       </c>
       <c r="C110" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D110" t="s">
         <v>11</v>
@@ -3412,10 +3345,10 @@
         <v>38</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C111" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
@@ -3429,10 +3362,10 @@
         <v>38</v>
       </c>
       <c r="B112" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C112" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D112" t="s">
         <v>11</v>
@@ -3446,10 +3379,10 @@
         <v>38</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C113" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
@@ -3463,10 +3396,10 @@
         <v>38</v>
       </c>
       <c r="B114" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C114" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D114" t="s">
         <v>11</v>
@@ -3483,7 +3416,7 @@
         <v>42</v>
       </c>
       <c r="C115" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
@@ -3500,7 +3433,7 @@
         <v>42</v>
       </c>
       <c r="C116" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D116" t="s">
         <v>11</v>
@@ -3514,10 +3447,10 @@
         <v>38</v>
       </c>
       <c r="B117" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C117" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
@@ -3531,10 +3464,10 @@
         <v>38</v>
       </c>
       <c r="B118" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C118" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D118" t="s">
         <v>11</v>
@@ -3551,7 +3484,7 @@
         <v>42</v>
       </c>
       <c r="C119" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
@@ -3565,10 +3498,10 @@
         <v>38</v>
       </c>
       <c r="B120" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C120" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
@@ -3582,10 +3515,10 @@
         <v>38</v>
       </c>
       <c r="B121" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C121" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
@@ -3602,7 +3535,7 @@
         <v>42</v>
       </c>
       <c r="C122" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D122" t="s">
         <v>11</v>
@@ -3619,7 +3552,7 @@
         <v>42</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
@@ -3633,10 +3566,10 @@
         <v>38</v>
       </c>
       <c r="B124" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C124" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D124" t="s">
         <v>11</v>
@@ -3653,7 +3586,7 @@
         <v>39</v>
       </c>
       <c r="C125" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
@@ -3670,7 +3603,7 @@
         <v>42</v>
       </c>
       <c r="C126" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D126" t="s">
         <v>11</v>
@@ -3687,7 +3620,7 @@
         <v>39</v>
       </c>
       <c r="C127" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
@@ -3704,7 +3637,7 @@
         <v>39</v>
       </c>
       <c r="C128" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
@@ -3721,7 +3654,7 @@
         <v>42</v>
       </c>
       <c r="C129" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
@@ -3735,10 +3668,10 @@
         <v>38</v>
       </c>
       <c r="B130" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
@@ -3752,10 +3685,10 @@
         <v>38</v>
       </c>
       <c r="B131" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C131" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
@@ -3769,10 +3702,10 @@
         <v>38</v>
       </c>
       <c r="B132" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C132" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D132" t="s">
         <v>11</v>
@@ -3789,7 +3722,7 @@
         <v>42</v>
       </c>
       <c r="C133" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
@@ -3806,7 +3739,7 @@
         <v>39</v>
       </c>
       <c r="C134" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
@@ -3820,10 +3753,10 @@
         <v>38</v>
       </c>
       <c r="B135" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C135" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
@@ -3837,10 +3770,10 @@
         <v>38</v>
       </c>
       <c r="B136" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C136" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D136" t="s">
         <v>11</v>
@@ -3854,10 +3787,10 @@
         <v>38</v>
       </c>
       <c r="B137" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C137" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
@@ -3871,10 +3804,10 @@
         <v>38</v>
       </c>
       <c r="B138" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C138" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D138" t="s">
         <v>11</v>
@@ -3888,10 +3821,10 @@
         <v>38</v>
       </c>
       <c r="B139" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C139" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
@@ -3905,10 +3838,10 @@
         <v>38</v>
       </c>
       <c r="B140" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C140" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D140" t="s">
         <v>11</v>
@@ -3922,10 +3855,10 @@
         <v>38</v>
       </c>
       <c r="B141" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C141" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
@@ -3939,10 +3872,10 @@
         <v>38</v>
       </c>
       <c r="B142" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C142" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D142" t="s">
         <v>11</v>
@@ -3956,10 +3889,10 @@
         <v>38</v>
       </c>
       <c r="B143" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C143" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
@@ -3976,7 +3909,7 @@
         <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D144" t="s">
         <v>11</v>
@@ -3993,7 +3926,7 @@
         <v>39</v>
       </c>
       <c r="C145" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D145" t="s">
         <v>11</v>
@@ -4007,10 +3940,10 @@
         <v>38</v>
       </c>
       <c r="B146" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C146" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D146" t="s">
         <v>11</v>
@@ -4024,10 +3957,10 @@
         <v>38</v>
       </c>
       <c r="B147" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C147" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D147" t="s">
         <v>11</v>
@@ -4044,7 +3977,7 @@
         <v>42</v>
       </c>
       <c r="C148" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D148" t="s">
         <v>11</v>
@@ -4055,125 +3988,108 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C149" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="D149" t="s">
         <v>11</v>
-      </c>
-      <c r="G149" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>169</v>
+        <v>14</v>
       </c>
       <c r="D150" t="s">
-        <v>11</v>
-      </c>
-      <c r="G150" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>11</v>
-      </c>
-      <c r="G151" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C152" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="D152" t="s">
         <v>11</v>
-      </c>
-      <c r="G152" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C153" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="D153" t="s">
-        <v>11</v>
-      </c>
-      <c r="G153" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C154" t="s">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="D154" t="s">
-        <v>11</v>
-      </c>
-      <c r="G154" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C155" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="D155" t="s">
-        <v>11</v>
-      </c>
-      <c r="G155" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H155">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="E2:E155" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>BilledeValgListe</formula1>
@@ -5003,333 +4919,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>337</v>
-      </c>
-      <c r="C4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>338</v>
-      </c>
-      <c r="C5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>339</v>
-      </c>
-      <c r="C6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>340</v>
-      </c>
-      <c r="C7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>341</v>
-      </c>
-      <c r="C8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>342</v>
-      </c>
-      <c r="C9" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>343</v>
-      </c>
-      <c r="C10" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>344</v>
-      </c>
-      <c r="C11" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>346</v>
-      </c>
-      <c r="B13" t="s">
-        <v>347</v>
-      </c>
-      <c r="C13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>346</v>
-      </c>
-      <c r="B14" t="s">
-        <v>348</v>
-      </c>
-      <c r="C14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>346</v>
-      </c>
-      <c r="B15" t="s">
-        <v>349</v>
-      </c>
-      <c r="C15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>346</v>
-      </c>
-      <c r="B16" t="s">
-        <v>350</v>
-      </c>
-      <c r="C16" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>346</v>
-      </c>
-      <c r="B17" t="s">
-        <v>351</v>
-      </c>
-      <c r="C17" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>346</v>
-      </c>
-      <c r="B18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>346</v>
-      </c>
-      <c r="B19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C19" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>346</v>
-      </c>
-      <c r="B20" t="s">
-        <v>354</v>
-      </c>
-      <c r="C20" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>346</v>
-      </c>
-      <c r="B21" t="s">
-        <v>355</v>
-      </c>
-      <c r="C21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>346</v>
-      </c>
-      <c r="B22" t="s">
-        <v>356</v>
-      </c>
-      <c r="C22" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>346</v>
-      </c>
-      <c r="B23" t="s">
-        <v>357</v>
-      </c>
-      <c r="C23" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>346</v>
-      </c>
-      <c r="B24" t="s">
-        <v>358</v>
-      </c>
-      <c r="C24" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>346</v>
-      </c>
-      <c r="B25" t="s">
-        <v>359</v>
-      </c>
-      <c r="C25" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>346</v>
-      </c>
-      <c r="B26" t="s">
-        <v>360</v>
-      </c>
-      <c r="C26" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>346</v>
-      </c>
-      <c r="B27" t="s">
-        <v>361</v>
-      </c>
-      <c r="C27" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>346</v>
-      </c>
-      <c r="B28" t="s">
-        <v>362</v>
-      </c>
-      <c r="C28" t="s">
-        <v>180</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5339,7 +4928,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5347,50 +4936,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="B4" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="B5" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="B6" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="B7" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="B8" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5398,42 +4987,42 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="B10" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="B12" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="B13" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="B14" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A948C11FF65F11CE9343156F17823D11BF5071D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A948C11FF62F17DBF77301677BC03411BF507E45" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="757">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -3418,6 +3418,9 @@
       <c r="D52" t="s">
         <v>98</v>
       </c>
+      <c r="G52" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -3617,6 +3620,9 @@
       <c r="D66" t="s">
         <v>30</v>
       </c>
+      <c r="G66" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -3774,6 +3780,9 @@
       <c r="D77" t="s">
         <v>30</v>
       </c>
+      <c r="G77" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -4050,7 +4059,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -4064,7 +4073,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -4078,7 +4087,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -4092,7 +4101,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -4106,7 +4115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -4120,7 +4129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -4134,7 +4143,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -4147,8 +4156,11 @@
       <c r="D103" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G103" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -4161,8 +4173,11 @@
       <c r="D104" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G104" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -4176,7 +4191,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -4190,7 +4205,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -4203,8 +4218,11 @@
       <c r="D107" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G107" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -4218,7 +4236,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -4232,7 +4250,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -4246,7 +4264,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -4260,7 +4278,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -4301,6 +4319,9 @@
       <c r="D114" t="s">
         <v>30</v>
       </c>
+      <c r="G114" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
@@ -4315,6 +4336,9 @@
       <c r="D115" t="s">
         <v>30</v>
       </c>
+      <c r="G115" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
@@ -4329,6 +4353,9 @@
       <c r="D116" t="s">
         <v>30</v>
       </c>
+      <c r="G116" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
@@ -4530,6 +4557,9 @@
       </c>
       <c r="D130" t="s">
         <v>30</v>
+      </c>
+      <c r="G130" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5061,6 +5091,9 @@
       <c r="D167" t="s">
         <v>30</v>
       </c>
+      <c r="G167" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
@@ -5103,6 +5136,9 @@
       <c r="D170" t="s">
         <v>30</v>
       </c>
+      <c r="G170" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
@@ -5131,6 +5167,9 @@
       <c r="D172" t="s">
         <v>30</v>
       </c>
+      <c r="G172" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
@@ -5159,6 +5198,9 @@
       <c r="D174" t="s">
         <v>30</v>
       </c>
+      <c r="G174" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
@@ -5188,7 +5230,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>243</v>
       </c>
@@ -5201,8 +5243,11 @@
       <c r="D177" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G177" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>243</v>
       </c>
@@ -5216,7 +5261,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>243</v>
       </c>
@@ -5230,7 +5275,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>243</v>
       </c>
@@ -5244,7 +5289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>243</v>
       </c>
@@ -5258,7 +5303,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>243</v>
       </c>
@@ -5272,7 +5317,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>243</v>
       </c>
@@ -5286,7 +5331,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>243</v>
       </c>
@@ -5300,7 +5345,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>243</v>
       </c>
@@ -5314,7 +5359,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>243</v>
       </c>
@@ -5328,7 +5373,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>243</v>
       </c>
@@ -5342,7 +5387,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>243</v>
       </c>
@@ -5356,7 +5401,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>243</v>
       </c>
@@ -5370,7 +5415,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>243</v>
       </c>
@@ -5384,7 +5429,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>243</v>
       </c>
@@ -5398,7 +5443,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>243</v>
       </c>
@@ -5412,7 +5457,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>243</v>
       </c>
@@ -5426,7 +5471,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>243</v>
       </c>
@@ -5440,7 +5485,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>243</v>
       </c>
@@ -5454,7 +5499,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>243</v>
       </c>
@@ -5468,7 +5513,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>243</v>
       </c>
@@ -5482,7 +5527,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>243</v>
       </c>
@@ -5496,7 +5541,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>243</v>
       </c>
@@ -5509,8 +5554,11 @@
       <c r="D199" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G199" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>243</v>
       </c>
@@ -5523,8 +5571,11 @@
       <c r="D200" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G200" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>243</v>
       </c>
@@ -5538,7 +5589,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>243</v>
       </c>
@@ -5552,7 +5603,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>243</v>
       </c>
@@ -5566,7 +5617,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>243</v>
       </c>
@@ -5580,7 +5631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>243</v>
       </c>
@@ -5594,7 +5645,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>243</v>
       </c>
@@ -5608,7 +5659,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>243</v>
       </c>
@@ -5622,7 +5673,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>243</v>
       </c>
@@ -5635,8 +5686,11 @@
       <c r="D208" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G208" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>243</v>
       </c>
@@ -5650,7 +5704,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>243</v>
       </c>
@@ -5664,7 +5718,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>243</v>
       </c>
@@ -5677,8 +5731,11 @@
       <c r="D211" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G211" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>243</v>
       </c>
@@ -5692,7 +5749,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>243</v>
       </c>
@@ -5706,7 +5763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>243</v>
       </c>
@@ -5720,7 +5777,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>243</v>
       </c>
@@ -5734,7 +5791,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>243</v>
       </c>
@@ -5748,7 +5805,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>243</v>
       </c>
@@ -5762,7 +5819,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>243</v>
       </c>
@@ -5776,7 +5833,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>243</v>
       </c>
@@ -5790,7 +5847,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>243</v>
       </c>
@@ -5804,7 +5861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>243</v>
       </c>
@@ -5818,7 +5875,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>243</v>
       </c>
@@ -5832,7 +5889,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>243</v>
       </c>
@@ -5845,8 +5902,11 @@
       <c r="D223" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G223" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>243</v>
       </c>
@@ -5860,7 +5920,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>243</v>
       </c>
@@ -5874,7 +5934,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>243</v>
       </c>
@@ -5888,7 +5948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>243</v>
       </c>
@@ -5901,8 +5961,11 @@
       <c r="D227" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G227" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>243</v>
       </c>
@@ -5916,7 +5979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>243</v>
       </c>
@@ -5930,7 +5993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>243</v>
       </c>
@@ -5944,7 +6007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>243</v>
       </c>
@@ -5957,8 +6020,11 @@
       <c r="D231" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G231" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>243</v>
       </c>
@@ -5972,7 +6038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>243</v>
       </c>
@@ -5986,7 +6052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>243</v>
       </c>
@@ -5999,8 +6065,11 @@
       <c r="D234" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G234" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>243</v>
       </c>
@@ -6013,8 +6082,11 @@
       <c r="D235" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G235" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>243</v>
       </c>
@@ -6027,8 +6099,11 @@
       <c r="D236" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G236" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>243</v>
       </c>
@@ -6042,7 +6117,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>243</v>
       </c>
@@ -6056,7 +6131,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>243</v>
       </c>
@@ -6070,7 +6145,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>243</v>
       </c>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0097174-0A85-4221-B881-86CD511B4050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC2ADB-EF3F-4C95-A976-DE389B9663C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="492">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -64,6 +64,9 @@
     <t>BetiniaStudio.jpg</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
     <t>TV3+.dk</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>Fodbold.jpg</t>
   </si>
   <si>
+    <t>3F Superliga.jpg</t>
+  </si>
+  <si>
     <t>TV3+.dk; TV3.MAX.dk</t>
   </si>
   <si>
@@ -106,6 +112,9 @@
     <t>tv3sport-generic.jpg</t>
   </si>
   <si>
+    <t>Betinia Liga.jpg</t>
+  </si>
+  <si>
     <t>Viaplay.Sport.News.dk</t>
   </si>
   <si>
@@ -121,6 +130,9 @@
     <t>Bundesliga Fodbold: Dortmund-Werder Bremen</t>
   </si>
   <si>
+    <t>Bundesliga_3.JPG</t>
+  </si>
+  <si>
     <t>Bundesliga Fodbold: Freiburg - Schalke 04</t>
   </si>
   <si>
@@ -133,6 +145,9 @@
     <t>Champions League Goal Show</t>
   </si>
   <si>
+    <t>UEFA Champions League Goal Show.jpg</t>
+  </si>
+  <si>
     <t>TV3.MAX.dk; TV3.SPORT.dk</t>
   </si>
   <si>
@@ -157,12 +172,21 @@
     <t>Deutsche Tourenwagen Masters</t>
   </si>
   <si>
+    <t>DTM.jpg</t>
+  </si>
+  <si>
     <t>EFL Championship: Swansea - Norwich</t>
   </si>
   <si>
+    <t>EFL.jpg</t>
+  </si>
+  <si>
     <t>EHF European League: Batcho BM. Torrelavega - TTH Holstebro</t>
   </si>
   <si>
+    <t>EHF Mens Champions League.jpg</t>
+  </si>
+  <si>
     <t>Elysium</t>
   </si>
   <si>
@@ -202,9 +226,6 @@
     <t>Forsvundet sporløst</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>Før Superligaen</t>
   </si>
   <si>
@@ -262,6 +283,9 @@
     <t>Ligue 1: Paris Saint - Germain - Le Mans</t>
   </si>
   <si>
+    <t>Ligue 1_2.jpg</t>
+  </si>
+  <si>
     <t>MotoGP</t>
   </si>
   <si>
@@ -283,6 +307,9 @@
     <t>NHL: Buffalo-Florida</t>
   </si>
   <si>
+    <t>NFL.jpg</t>
+  </si>
+  <si>
     <t>NHL: Florida Panthers - Minnesota Wild</t>
   </si>
   <si>
@@ -301,6 +328,9 @@
     <t>Optakt til Champions League</t>
   </si>
   <si>
+    <t>Champions League.jpg</t>
+  </si>
+  <si>
     <t>Pacific Blue</t>
   </si>
   <si>
@@ -331,6 +361,9 @@
     <t>Premier League: Aston Villa - Brentford</t>
   </si>
   <si>
+    <t>PL.jpg</t>
+  </si>
+  <si>
     <t>Premier League: Chelsea - Bournemouth</t>
   </si>
   <si>
@@ -529,15 +562,15 @@
     <t>TV_2_Sport_X.jpg</t>
   </si>
   <si>
+    <t>ATP_WTA Tennis.jpg</t>
+  </si>
+  <si>
     <t>ATP: Cerundolo-Alcaraz, Shanghai</t>
   </si>
   <si>
     <t>ATP: Shanghai</t>
   </si>
   <si>
-    <t>ATP_WTA Tennis.jpg</t>
-  </si>
-  <si>
     <t>TV.2.Sport.dk</t>
   </si>
   <si>
@@ -586,6 +619,9 @@
     <t>tv2sport-generic.jpg</t>
   </si>
   <si>
+    <t>Herreligaen.jpg</t>
+  </si>
+  <si>
     <t>Herreligaen: Skjern - Bjerringbro-Silkeborg</t>
   </si>
   <si>
@@ -604,9 +640,6 @@
     <t>NFL: Jacksonville Jaguars-Philadelphia Eagles</t>
   </si>
   <si>
-    <t>NFL.jpg</t>
-  </si>
-  <si>
     <t>NFL: New Orleans Saints-Minnesota Vikings</t>
   </si>
   <si>
@@ -616,6 +649,9 @@
     <t>Serie A: Atalanta-Venezia</t>
   </si>
   <si>
+    <t>Serie A.jpg</t>
+  </si>
+  <si>
     <t>Serie A: Cagliari-Juventus</t>
   </si>
   <si>
@@ -1063,9 +1099,6 @@
     <t>360F1.jpg</t>
   </si>
   <si>
-    <t>3F Superliga.jpg</t>
-  </si>
-  <si>
     <t>A-Liga.jpg</t>
   </si>
   <si>
@@ -1087,9 +1120,6 @@
     <t>Atletik Diamond League.jpg</t>
   </si>
   <si>
-    <t>Betinia Liga.jpg</t>
-  </si>
-  <si>
     <t>Bundesliga Fodbold.jpg</t>
   </si>
   <si>
@@ -1102,18 +1132,12 @@
     <t>Bundesliga Special.jpg</t>
   </si>
   <si>
-    <t>Bundesliga_3.JPG</t>
-  </si>
-  <si>
     <t>CLWomen.jpg</t>
   </si>
   <si>
     <t>Champions Hockey League.jpg</t>
   </si>
   <si>
-    <t>Champions League.jpg</t>
-  </si>
-  <si>
     <t>Cykling Clásica San Sebastián.jpg</t>
   </si>
   <si>
@@ -1156,9 +1180,6 @@
     <t>DP World Tour Danish Golf Championship.jpg</t>
   </si>
   <si>
-    <t>DTM.jpg</t>
-  </si>
-  <si>
     <t>Davis Cup.jpg</t>
   </si>
   <si>
@@ -1168,15 +1189,9 @@
     <t>EFL Championship Highligts.jpg</t>
   </si>
   <si>
-    <t>EFL.jpg</t>
-  </si>
-  <si>
     <t>EHF European League.jpg</t>
   </si>
   <si>
-    <t>EHF Mens Champions League.jpg</t>
-  </si>
-  <si>
     <t>EM i atletik.jpg</t>
   </si>
   <si>
@@ -1240,9 +1255,6 @@
     <t>HBL Håndbold.jpg</t>
   </si>
   <si>
-    <t>Herreligaen.jpg</t>
-  </si>
-  <si>
     <t>Håndbold  Golden League.jpg</t>
   </si>
   <si>
@@ -1273,9 +1285,6 @@
     <t>Ligue 1 The Season Review Show.jpg</t>
   </si>
   <si>
-    <t>Ligue 1_2.jpg</t>
-  </si>
-  <si>
     <t>Ligue1.jpg</t>
   </si>
   <si>
@@ -1312,9 +1321,6 @@
     <t>PDC European Tour.jpg</t>
   </si>
   <si>
-    <t>PL.jpg</t>
-  </si>
-  <si>
     <t>Pokal-highligts.jpg</t>
   </si>
   <si>
@@ -1342,9 +1348,6 @@
     <t>RaceTV_DK.jpg</t>
   </si>
   <si>
-    <t>Serie A.jpg</t>
-  </si>
-  <si>
     <t>Skisport.jpg</t>
   </si>
   <si>
@@ -1388,9 +1391,6 @@
   </si>
   <si>
     <t>Tourstudiet.jpg</t>
-  </si>
-  <si>
-    <t>UEFA Champions League Goal Show.jpg</t>
   </si>
   <si>
     <t>UEFA Champions League.jpg</t>
@@ -1909,16 +1909,16 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>58</v>
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1926,16 +1926,16 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>58</v>
+        <v>131</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1943,16 +1943,16 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1960,16 +1960,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1977,16 +1977,16 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1994,16 +1994,16 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2011,16 +2011,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2028,16 +2028,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2045,2719 +2045,2719 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>213</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>207</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>217</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>219</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>221</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>207</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>230</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="B35" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="C35" t="s">
-        <v>234</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B36" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C36" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C37" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C38" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C42" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C43" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C45" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C46" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C47" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C48" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C49" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C50" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B51" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C51" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C52" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C53" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C54" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="D54" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B55" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C55" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D55" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B56" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C56" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B57" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C57" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D57" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B58" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C58" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C59" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D59" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B60" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C60" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B61" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C61" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B62" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D62" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C65" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B66" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C66" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B67" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B69" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C69" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="G69" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C70" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C71" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B72" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C72" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D72" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B73" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C73" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B74" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C74" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B75" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="C75" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B76" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C76" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C77" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B78" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C78" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B79" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C79" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B80" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C80" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B81" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C81" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B82" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C82" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B83" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C83" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B84" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C84" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B85" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C85" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C86" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B87" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C87" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="D87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B88" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C88" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B89" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C89" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="D89" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B90" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C90" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="D90" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B91" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C91" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B92" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C92" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="D92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B93" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C93" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B94" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C94" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C95" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="D95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B96" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C96" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="D96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B97" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C97" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="D97" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B98" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C98" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="D98" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C99" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="D99" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B100" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C100" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="D100" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B101" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C101" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="D101" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B102" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C102" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D102" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C103" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C104" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="D104" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C105" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="D105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B106" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C106" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="D106" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B107" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C107" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="D107" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G107" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B108" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C108" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="D108" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G108" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B109" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C109" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G109" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B110" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C110" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D110" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G110" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B111" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C111" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="D111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G111" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B112" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C112" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="D112" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B113" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C113" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="D113" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C114" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D114" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G114" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B115" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C115" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G115" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B116" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C116" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="D116" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B117" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C117" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="D117" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G117" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B118" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C118" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D118" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G118" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B119" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C119" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="D119" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G119" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B120" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C120" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="D120" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G120" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B121" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C121" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="D121" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G121" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C122" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="D122" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C123" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="D123" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G123" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B124" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C124" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="D124" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G124" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B125" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C125" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="D125" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G125" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C126" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="D126" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G126" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B127" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C127" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="D127" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G127" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B128" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C128" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="D128" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G128" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B129" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C129" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D129" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G129" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B130" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C130" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="D130" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G130" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B131" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C131" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D131" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G131" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B132" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C132" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="D132" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G132" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B133" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C133" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="D133" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G133" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B134" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C134" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="D134" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G134" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B135" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C135" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="D135" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B136" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C136" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="D136" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B137" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C137" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="D137" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G137" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B138" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C138" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="D138" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G138" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B139" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C139" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="D139" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G139" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B140" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C140" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="D140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G140" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B141" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C141" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="D141" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G141" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C142" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="D142" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G142" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B143" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C143" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="D143" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G143" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B144" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C144" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="D144" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G144" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="C145" t="s">
-        <v>109</v>
+        <v>331</v>
       </c>
       <c r="D145" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G145" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B146" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="C146" t="s">
-        <v>110</v>
+        <v>332</v>
       </c>
       <c r="D146" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G146" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B147" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="C147" t="s">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="D147" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G147" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B148" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="C148" t="s">
-        <v>113</v>
+        <v>334</v>
       </c>
       <c r="D148" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G148" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>219</v>
       </c>
       <c r="C149" t="s">
-        <v>114</v>
+        <v>335</v>
       </c>
       <c r="D149" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G149" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B150" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="C150" t="s">
-        <v>116</v>
+        <v>336</v>
       </c>
       <c r="D150" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G150" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="C151" t="s">
-        <v>127</v>
+        <v>337</v>
       </c>
       <c r="D151" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G151" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="C152" t="s">
-        <v>128</v>
+        <v>338</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G152" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B153" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="C153" t="s">
-        <v>131</v>
+        <v>339</v>
       </c>
       <c r="D153" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G153" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>238</v>
       </c>
       <c r="C154" t="s">
-        <v>132</v>
+        <v>340</v>
       </c>
       <c r="D154" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G154" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B155" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="C155" t="s">
-        <v>136</v>
+        <v>341</v>
       </c>
       <c r="D155" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G155" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B156" t="s">
-        <v>12</v>
+        <v>219</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>342</v>
       </c>
       <c r="D156" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G156" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>219</v>
       </c>
       <c r="C157" t="s">
-        <v>29</v>
+        <v>343</v>
       </c>
       <c r="D157" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G157" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B158" t="s">
-        <v>12</v>
+        <v>219</v>
       </c>
       <c r="C158" t="s">
-        <v>45</v>
+        <v>344</v>
       </c>
       <c r="D158" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G158" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B159" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="C159" t="s">
-        <v>70</v>
+        <v>345</v>
       </c>
       <c r="D159" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G159" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="C160" t="s">
-        <v>71</v>
+        <v>346</v>
       </c>
       <c r="D160" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G160" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B161" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="C161" t="s">
-        <v>73</v>
+        <v>347</v>
       </c>
       <c r="D161" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G161" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B162" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="C162" t="s">
-        <v>117</v>
+        <v>348</v>
       </c>
       <c r="D162" t="s">
-        <v>118</v>
-      </c>
-      <c r="F162" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G162" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B163" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="C163" t="s">
-        <v>119</v>
+        <v>349</v>
       </c>
       <c r="D163" t="s">
-        <v>120</v>
-      </c>
-      <c r="F163" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G163" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B164" t="s">
-        <v>26</v>
+        <v>223</v>
       </c>
       <c r="C164" t="s">
-        <v>121</v>
+        <v>350</v>
       </c>
       <c r="D164" t="s">
-        <v>122</v>
-      </c>
-      <c r="F164" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G164" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B165" t="s">
-        <v>26</v>
+        <v>223</v>
       </c>
       <c r="C165" t="s">
-        <v>123</v>
+        <v>351</v>
       </c>
       <c r="D165" t="s">
-        <v>124</v>
-      </c>
-      <c r="F165" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G165" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B166" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="C166" t="s">
-        <v>125</v>
+        <v>352</v>
       </c>
       <c r="D166" t="s">
-        <v>126</v>
-      </c>
-      <c r="F166" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G166" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B167" t="s">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="C167" t="s">
-        <v>129</v>
+        <v>353</v>
       </c>
       <c r="D167" t="s">
-        <v>130</v>
-      </c>
-      <c r="F167" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G167" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B168" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="C168" t="s">
-        <v>133</v>
+        <v>354</v>
       </c>
       <c r="D168" t="s">
-        <v>134</v>
-      </c>
-      <c r="F168" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G168" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="B169" t="s">
-        <v>26</v>
+        <v>223</v>
       </c>
       <c r="C169" t="s">
-        <v>135</v>
+        <v>355</v>
       </c>
       <c r="D169" t="s">
-        <v>39</v>
-      </c>
-      <c r="F169" t="s">
-        <v>58</v>
+        <v>15</v>
+      </c>
+      <c r="G169" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -4765,502 +4765,520 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>137</v>
+        <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="D170" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="F170" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C171" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="D171" t="s">
-        <v>172</v>
+        <v>17</v>
+      </c>
+      <c r="E171" t="s">
+        <v>18</v>
       </c>
       <c r="F171" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="C172" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="D172" t="s">
-        <v>172</v>
+        <v>17</v>
+      </c>
+      <c r="E172" t="s">
+        <v>18</v>
       </c>
       <c r="F172" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="C173" t="s">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="D173" t="s">
-        <v>172</v>
+        <v>17</v>
+      </c>
+      <c r="E173" t="s">
+        <v>18</v>
       </c>
       <c r="F173" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C174" t="s">
-        <v>175</v>
+        <v>23</v>
       </c>
       <c r="D174" t="s">
-        <v>172</v>
+        <v>17</v>
+      </c>
+      <c r="E174" t="s">
+        <v>18</v>
       </c>
       <c r="F174" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C175" t="s">
-        <v>176</v>
+        <v>24</v>
       </c>
       <c r="D175" t="s">
-        <v>172</v>
+        <v>25</v>
+      </c>
+      <c r="E175" t="s">
+        <v>25</v>
       </c>
       <c r="F175" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
-        <v>177</v>
+        <v>26</v>
       </c>
       <c r="D176" t="s">
-        <v>172</v>
+        <v>27</v>
+      </c>
+      <c r="E176" t="s">
+        <v>28</v>
       </c>
       <c r="F176" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="C177" t="s">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="D177" t="s">
-        <v>172</v>
+        <v>31</v>
+      </c>
+      <c r="E177" t="s">
+        <v>28</v>
       </c>
       <c r="F177" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="C178" t="s">
-        <v>179</v>
+        <v>33</v>
       </c>
       <c r="D178" t="s">
-        <v>172</v>
+        <v>17</v>
+      </c>
+      <c r="E178" t="s">
+        <v>34</v>
       </c>
       <c r="F178" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="C179" t="s">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="D179" t="s">
-        <v>172</v>
+        <v>17</v>
+      </c>
+      <c r="E179" t="s">
+        <v>34</v>
       </c>
       <c r="F179" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="C180" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="D180" t="s">
-        <v>172</v>
+        <v>15</v>
+      </c>
+      <c r="E180" t="s">
+        <v>34</v>
       </c>
       <c r="F180" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="C181" t="s">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="D181" t="s">
-        <v>183</v>
+        <v>17</v>
+      </c>
+      <c r="E181" t="s">
+        <v>39</v>
       </c>
       <c r="F181" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="C182" t="s">
-        <v>184</v>
+        <v>41</v>
       </c>
       <c r="D182" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="E182" t="s">
-        <v>404</v>
+        <v>42</v>
       </c>
       <c r="F182" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C183" t="s">
-        <v>186</v>
+        <v>43</v>
       </c>
       <c r="D183" t="s">
-        <v>185</v>
-      </c>
-      <c r="E183" t="s">
-        <v>404</v>
+        <v>44</v>
       </c>
       <c r="F183" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="C184" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="D184" t="s">
-        <v>185</v>
-      </c>
-      <c r="E184" t="s">
-        <v>404</v>
+        <v>46</v>
       </c>
       <c r="F184" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="C185" t="s">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="D185" t="s">
-        <v>189</v>
+        <v>27</v>
       </c>
       <c r="E185" t="s">
-        <v>404</v>
+        <v>48</v>
       </c>
       <c r="F185" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="C186" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="D186" t="s">
-        <v>192</v>
+        <v>15</v>
+      </c>
+      <c r="E186" t="s">
+        <v>50</v>
       </c>
       <c r="F186" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C187" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
       <c r="D187" t="s">
-        <v>192</v>
+        <v>27</v>
+      </c>
+      <c r="E187" t="s">
+        <v>52</v>
       </c>
       <c r="F187" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="D188" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="F188" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="C189" t="s">
-        <v>195</v>
+        <v>57</v>
       </c>
       <c r="D189" t="s">
-        <v>185</v>
-      </c>
-      <c r="E189" t="s">
-        <v>438</v>
+        <v>44</v>
       </c>
       <c r="F189" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C190" t="s">
-        <v>196</v>
+        <v>58</v>
       </c>
       <c r="D190" t="s">
-        <v>166</v>
-      </c>
-      <c r="E190" t="s">
-        <v>438</v>
+        <v>59</v>
       </c>
       <c r="F190" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B191" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="C191" t="s">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="D191" t="s">
-        <v>166</v>
-      </c>
-      <c r="E191" t="s">
-        <v>438</v>
+        <v>61</v>
       </c>
       <c r="F191" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="C192" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="D192" t="s">
-        <v>166</v>
-      </c>
-      <c r="E192" t="s">
-        <v>438</v>
+        <v>61</v>
       </c>
       <c r="F192" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C193" t="s">
-        <v>199</v>
+        <v>63</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
-      </c>
-      <c r="E193" t="s">
-        <v>438</v>
+        <v>61</v>
       </c>
       <c r="F193" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="C194" t="s">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="D194" t="s">
-        <v>183</v>
+        <v>61</v>
       </c>
       <c r="F194" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B195" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="C195" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="D195" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="F195" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>203</v>
+        <v>29</v>
       </c>
       <c r="C196" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="D196" t="s">
-        <v>202</v>
+        <v>68</v>
       </c>
       <c r="F196" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="B197" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="C197" t="s">
-        <v>205</v>
+        <v>70</v>
       </c>
       <c r="D197" t="s">
-        <v>202</v>
+        <v>68</v>
       </c>
       <c r="F197" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5271,13 +5289,13 @@
         <v>9</v>
       </c>
       <c r="C198" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="D198" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F198" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5285,19 +5303,16 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C199" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
-      </c>
-      <c r="E199" t="s">
-        <v>345</v>
+        <v>74</v>
       </c>
       <c r="F199" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5305,19 +5320,16 @@
         <v>8</v>
       </c>
       <c r="B200" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C200" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
-      </c>
-      <c r="E200" t="s">
-        <v>345</v>
+        <v>76</v>
       </c>
       <c r="F200" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5325,19 +5337,16 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="C201" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
-      </c>
-      <c r="E201" t="s">
-        <v>345</v>
+        <v>83</v>
       </c>
       <c r="F201" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5348,16 +5357,16 @@
         <v>9</v>
       </c>
       <c r="C202" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E202" t="s">
-        <v>345</v>
+        <v>85</v>
       </c>
       <c r="F202" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5368,16 +5377,13 @@
         <v>9</v>
       </c>
       <c r="C203" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="D203" t="s">
-        <v>23</v>
-      </c>
-      <c r="E203" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="F203" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5388,16 +5394,16 @@
         <v>9</v>
       </c>
       <c r="C204" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="D204" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E204" t="s">
-        <v>353</v>
+        <v>93</v>
       </c>
       <c r="F204" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5405,19 +5411,19 @@
         <v>8</v>
       </c>
       <c r="B205" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C205" t="s">
+        <v>94</v>
+      </c>
+      <c r="D205" t="s">
         <v>27</v>
       </c>
-      <c r="D205" t="s">
-        <v>28</v>
-      </c>
       <c r="E205" t="s">
-        <v>353</v>
+        <v>93</v>
       </c>
       <c r="F205" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5425,19 +5431,19 @@
         <v>8</v>
       </c>
       <c r="B206" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C206" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E206" t="s">
-        <v>358</v>
+        <v>93</v>
       </c>
       <c r="F206" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -5445,19 +5451,16 @@
         <v>8</v>
       </c>
       <c r="B207" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="C207" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D207" t="s">
-        <v>16</v>
-      </c>
-      <c r="E207" t="s">
-        <v>358</v>
+        <v>98</v>
       </c>
       <c r="F207" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5465,19 +5468,19 @@
         <v>8</v>
       </c>
       <c r="B208" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C208" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D208" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E208" t="s">
-        <v>358</v>
+        <v>100</v>
       </c>
       <c r="F208" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -5485,19 +5488,16 @@
         <v>8</v>
       </c>
       <c r="B209" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C209" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="D209" t="s">
-        <v>16</v>
-      </c>
-      <c r="E209" t="s">
-        <v>454</v>
+        <v>105</v>
       </c>
       <c r="F209" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -5505,19 +5505,16 @@
         <v>8</v>
       </c>
       <c r="B210" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="C210" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="D210" t="s">
-        <v>37</v>
-      </c>
-      <c r="E210" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="F210" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5525,16 +5522,19 @@
         <v>8</v>
       </c>
       <c r="B211" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="C211" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="D211" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="E211" t="s">
+        <v>111</v>
       </c>
       <c r="F211" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -5542,16 +5542,19 @@
         <v>8</v>
       </c>
       <c r="B212" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C212" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="D212" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="E212" t="s">
+        <v>111</v>
       </c>
       <c r="F212" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -5559,19 +5562,19 @@
         <v>8</v>
       </c>
       <c r="B213" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C213" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="D213" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E213" t="s">
-        <v>376</v>
+        <v>111</v>
       </c>
       <c r="F213" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -5579,19 +5582,19 @@
         <v>8</v>
       </c>
       <c r="B214" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C214" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="D214" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E214" t="s">
-        <v>380</v>
+        <v>111</v>
       </c>
       <c r="F214" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -5599,19 +5602,19 @@
         <v>8</v>
       </c>
       <c r="B215" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C215" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="D215" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E215" t="s">
-        <v>382</v>
+        <v>111</v>
       </c>
       <c r="F215" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -5619,16 +5622,19 @@
         <v>8</v>
       </c>
       <c r="B216" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C216" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="D216" t="s">
-        <v>47</v>
+        <v>17</v>
+      </c>
+      <c r="E216" t="s">
+        <v>111</v>
       </c>
       <c r="F216" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5636,16 +5642,19 @@
         <v>8</v>
       </c>
       <c r="B217" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C217" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="D217" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="E217" t="s">
+        <v>111</v>
       </c>
       <c r="F217" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -5653,16 +5662,19 @@
         <v>8</v>
       </c>
       <c r="B218" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C218" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="D218" t="s">
-        <v>51</v>
+        <v>17</v>
+      </c>
+      <c r="E218" t="s">
+        <v>111</v>
       </c>
       <c r="F218" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -5670,16 +5682,19 @@
         <v>8</v>
       </c>
       <c r="B219" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C219" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="D219" t="s">
-        <v>53</v>
+        <v>17</v>
+      </c>
+      <c r="E219" t="s">
+        <v>111</v>
       </c>
       <c r="F219" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -5687,16 +5702,16 @@
         <v>8</v>
       </c>
       <c r="B220" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C220" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="D220" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="F220" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -5704,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="B221" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C221" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="D221" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="F221" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -5721,16 +5736,16 @@
         <v>8</v>
       </c>
       <c r="B222" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C222" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="D222" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="F222" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -5738,16 +5753,16 @@
         <v>8</v>
       </c>
       <c r="B223" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C223" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="D223" t="s">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="F223" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,16 +5770,16 @@
         <v>8</v>
       </c>
       <c r="B224" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C224" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D224" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="F224" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -5772,16 +5787,16 @@
         <v>8</v>
       </c>
       <c r="B225" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="C225" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="D225" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="F225" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -5789,16 +5804,16 @@
         <v>8</v>
       </c>
       <c r="B226" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C226" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="D226" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F226" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -5806,16 +5821,16 @@
         <v>8</v>
       </c>
       <c r="B227" t="s">
-        <v>9</v>
+        <v>148</v>
       </c>
       <c r="C227" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="D227" t="s">
-        <v>39</v>
+        <v>150</v>
       </c>
       <c r="F227" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -5823,16 +5838,16 @@
         <v>8</v>
       </c>
       <c r="B228" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C228" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="D228" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="F228" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -5840,16 +5855,19 @@
         <v>8</v>
       </c>
       <c r="B229" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C229" t="s">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="D229" t="s">
-        <v>69</v>
+        <v>17</v>
+      </c>
+      <c r="E229" t="s">
+        <v>100</v>
       </c>
       <c r="F229" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -5857,16 +5875,19 @@
         <v>8</v>
       </c>
       <c r="B230" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="D230" t="s">
-        <v>76</v>
+        <v>17</v>
+      </c>
+      <c r="E230" t="s">
+        <v>100</v>
       </c>
       <c r="F230" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -5877,16 +5898,16 @@
         <v>9</v>
       </c>
       <c r="C231" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="D231" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E231" t="s">
-        <v>415</v>
+        <v>100</v>
       </c>
       <c r="F231" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -5897,13 +5918,16 @@
         <v>9</v>
       </c>
       <c r="C232" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="D232" t="s">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="E232" t="s">
+        <v>100</v>
       </c>
       <c r="F232" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -5911,19 +5935,19 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C233" t="s">
+        <v>157</v>
+      </c>
+      <c r="D233" t="s">
+        <v>17</v>
+      </c>
+      <c r="E233" t="s">
         <v>100</v>
       </c>
-      <c r="D233" t="s">
-        <v>16</v>
-      </c>
-      <c r="E233" t="s">
-        <v>428</v>
-      </c>
       <c r="F233" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -5931,19 +5955,19 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C234" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="D234" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E234" t="s">
-        <v>428</v>
+        <v>100</v>
       </c>
       <c r="F234" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -5951,19 +5975,16 @@
         <v>8</v>
       </c>
       <c r="B235" t="s">
-        <v>9</v>
+        <v>148</v>
       </c>
       <c r="C235" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="D235" t="s">
-        <v>16</v>
-      </c>
-      <c r="E235" t="s">
-        <v>428</v>
+        <v>160</v>
       </c>
       <c r="F235" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -5971,754 +5992,736 @@
         <v>8</v>
       </c>
       <c r="B236" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C236" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
-      </c>
-      <c r="E236" t="s">
-        <v>428</v>
+        <v>162</v>
       </c>
       <c r="F236" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B237" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="C237" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E237" t="s">
-        <v>428</v>
+        <v>18</v>
       </c>
       <c r="F237" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B238" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="C238" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="D238" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E238" t="s">
-        <v>428</v>
+        <v>18</v>
       </c>
       <c r="F238" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B239" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="C239" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="D239" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E239" t="s">
-        <v>428</v>
+        <v>18</v>
       </c>
       <c r="F239" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B240" t="s">
+        <v>165</v>
+      </c>
+      <c r="C240" t="s">
+        <v>169</v>
+      </c>
+      <c r="D240" t="s">
         <v>17</v>
       </c>
-      <c r="C240" t="s">
-        <v>107</v>
-      </c>
-      <c r="D240" t="s">
-        <v>16</v>
-      </c>
       <c r="E240" t="s">
-        <v>428</v>
+        <v>18</v>
       </c>
       <c r="F240" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B241" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="C241" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="D241" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E241" t="s">
-        <v>428</v>
+        <v>18</v>
       </c>
       <c r="F241" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B242" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="C242" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D242" t="s">
-        <v>141</v>
+        <v>17</v>
+      </c>
+      <c r="E242" t="s">
+        <v>18</v>
       </c>
       <c r="F242" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B243" t="s">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="C243" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="D243" t="s">
-        <v>16</v>
-      </c>
-      <c r="E243" t="s">
-        <v>361</v>
+        <v>173</v>
       </c>
       <c r="F243" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B244" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="C244" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="D244" t="s">
-        <v>16</v>
-      </c>
-      <c r="E244" t="s">
-        <v>361</v>
+        <v>175</v>
       </c>
       <c r="F244" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B245" t="s">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="C245" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="E245" t="s">
-        <v>361</v>
+        <v>178</v>
       </c>
       <c r="F245" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B246" t="s">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="C246" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="D246" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="E246" t="s">
-        <v>361</v>
+        <v>178</v>
       </c>
       <c r="F246" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B247" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="C247" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="E247" t="s">
-        <v>361</v>
+        <v>178</v>
       </c>
       <c r="F247" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B248" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="C248" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
-      </c>
-      <c r="E248" t="s">
-        <v>361</v>
+        <v>183</v>
       </c>
       <c r="F248" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B249" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="C249" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="D249" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="F249" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B250" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="C250" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="D250" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="F250" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B251" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C251" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D251" t="s">
-        <v>16</v>
-      </c>
-      <c r="E251" t="s">
-        <v>345</v>
+        <v>183</v>
       </c>
       <c r="F251" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B252" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="C252" t="s">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="D252" t="s">
-        <v>14</v>
-      </c>
-      <c r="G252" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="F252" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B253" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="C253" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="D253" t="s">
-        <v>14</v>
-      </c>
-      <c r="G253" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="F253" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B254" t="s">
-        <v>9</v>
+        <v>181</v>
       </c>
       <c r="C254" t="s">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="D254" t="s">
-        <v>25</v>
-      </c>
-      <c r="E254" t="s">
+        <v>183</v>
+      </c>
+      <c r="F254" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>164</v>
+      </c>
+      <c r="B255" t="s">
+        <v>181</v>
+      </c>
+      <c r="C255" t="s">
+        <v>190</v>
+      </c>
+      <c r="D255" t="s">
+        <v>183</v>
+      </c>
+      <c r="F255" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>164</v>
+      </c>
+      <c r="B256" t="s">
+        <v>181</v>
+      </c>
+      <c r="C256" t="s">
+        <v>191</v>
+      </c>
+      <c r="D256" t="s">
+        <v>183</v>
+      </c>
+      <c r="F256" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>164</v>
+      </c>
+      <c r="B257" t="s">
+        <v>181</v>
+      </c>
+      <c r="C257" t="s">
         <v>192</v>
       </c>
-      <c r="F254" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>8</v>
-      </c>
-      <c r="B255" t="s">
-        <v>9</v>
-      </c>
-      <c r="C255" t="s">
-        <v>85</v>
-      </c>
-      <c r="D255" t="s">
-        <v>25</v>
-      </c>
-      <c r="E255" t="s">
-        <v>192</v>
-      </c>
-      <c r="F255" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>8</v>
-      </c>
-      <c r="B256" t="s">
-        <v>9</v>
-      </c>
-      <c r="C256" t="s">
-        <v>86</v>
-      </c>
-      <c r="D256" t="s">
-        <v>25</v>
-      </c>
-      <c r="E256" t="s">
-        <v>192</v>
-      </c>
-      <c r="F256" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>8</v>
-      </c>
-      <c r="B257" t="s">
-        <v>87</v>
-      </c>
-      <c r="C257" t="s">
-        <v>88</v>
-      </c>
       <c r="D257" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="F257" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B258" t="s">
-        <v>33</v>
+        <v>181</v>
       </c>
       <c r="C258" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="D258" t="s">
-        <v>16</v>
-      </c>
-      <c r="E258" t="s">
-        <v>361</v>
+        <v>194</v>
       </c>
       <c r="F258" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B259" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="C259" t="s">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="D259" t="s">
-        <v>14</v>
-      </c>
-      <c r="G259" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="E259" t="s">
+        <v>197</v>
+      </c>
+      <c r="F259" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B260" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="C260" t="s">
+        <v>198</v>
+      </c>
+      <c r="D260" t="s">
+        <v>196</v>
+      </c>
+      <c r="E260" t="s">
+        <v>197</v>
+      </c>
+      <c r="F260" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>164</v>
+      </c>
+      <c r="B261" t="s">
+        <v>181</v>
+      </c>
+      <c r="C261" t="s">
+        <v>199</v>
+      </c>
+      <c r="D261" t="s">
+        <v>196</v>
+      </c>
+      <c r="E261" t="s">
+        <v>197</v>
+      </c>
+      <c r="F261" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>164</v>
+      </c>
+      <c r="B262" t="s">
+        <v>181</v>
+      </c>
+      <c r="C262" t="s">
+        <v>200</v>
+      </c>
+      <c r="D262" t="s">
+        <v>201</v>
+      </c>
+      <c r="E262" t="s">
+        <v>197</v>
+      </c>
+      <c r="F262" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>164</v>
+      </c>
+      <c r="B263" t="s">
+        <v>165</v>
+      </c>
+      <c r="C263" t="s">
+        <v>202</v>
+      </c>
+      <c r="D263" t="s">
+        <v>177</v>
+      </c>
+      <c r="E263" t="s">
+        <v>178</v>
+      </c>
+      <c r="F263" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>164</v>
+      </c>
+      <c r="B264" t="s">
+        <v>181</v>
+      </c>
+      <c r="C264" t="s">
+        <v>203</v>
+      </c>
+      <c r="D264" t="s">
         <v>93</v>
       </c>
-      <c r="D260" t="s">
-        <v>14</v>
-      </c>
-      <c r="G260" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>8</v>
-      </c>
-      <c r="B261" t="s">
-        <v>35</v>
-      </c>
-      <c r="C261" t="s">
-        <v>94</v>
-      </c>
-      <c r="D261" t="s">
-        <v>95</v>
-      </c>
-      <c r="F261" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>8</v>
-      </c>
-      <c r="B262" t="s">
-        <v>19</v>
-      </c>
-      <c r="C262" t="s">
-        <v>96</v>
-      </c>
-      <c r="D262" t="s">
-        <v>14</v>
-      </c>
-      <c r="G262" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>8</v>
-      </c>
-      <c r="B263" t="s">
-        <v>97</v>
-      </c>
-      <c r="C263" t="s">
-        <v>98</v>
-      </c>
-      <c r="D263" t="s">
-        <v>99</v>
-      </c>
-      <c r="F263" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>153</v>
-      </c>
-      <c r="B264" t="s">
-        <v>154</v>
-      </c>
-      <c r="C264" t="s">
-        <v>156</v>
-      </c>
-      <c r="D264" t="s">
-        <v>16</v>
-      </c>
-      <c r="E264" t="s">
-        <v>345</v>
-      </c>
       <c r="F264" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B265" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C265" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="D265" t="s">
-        <v>16</v>
-      </c>
-      <c r="E265" t="s">
-        <v>345</v>
+        <v>93</v>
       </c>
       <c r="F265" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B266" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C266" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="D266" t="s">
-        <v>16</v>
-      </c>
-      <c r="E266" t="s">
-        <v>345</v>
+        <v>93</v>
       </c>
       <c r="F266" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B267" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C267" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="D267" t="s">
-        <v>16</v>
+        <v>196</v>
       </c>
       <c r="E267" t="s">
-        <v>345</v>
+        <v>207</v>
       </c>
       <c r="F267" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B268" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C268" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="D268" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="E268" t="s">
-        <v>345</v>
+        <v>207</v>
       </c>
       <c r="F268" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B269" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C269" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="D269" t="s">
-        <v>162</v>
+        <v>177</v>
+      </c>
+      <c r="E269" t="s">
+        <v>207</v>
       </c>
       <c r="F269" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B270" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C270" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="D270" t="s">
+        <v>177</v>
+      </c>
+      <c r="E270" t="s">
+        <v>207</v>
+      </c>
+      <c r="F270" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
         <v>164</v>
       </c>
-      <c r="F270" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>153</v>
-      </c>
       <c r="B271" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C271" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="D271" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="E271" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="F271" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B272" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C272" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="D272" t="s">
-        <v>166</v>
-      </c>
-      <c r="E272" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="F272" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B273" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C273" t="s">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="D273" t="s">
-        <v>169</v>
-      </c>
-      <c r="E273" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="F273" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B274" t="s">
-        <v>154</v>
+        <v>215</v>
       </c>
       <c r="C274" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="D274" t="s">
-        <v>166</v>
-      </c>
-      <c r="E274" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="F274" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B275" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C275" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="D275" t="s">
-        <v>14</v>
+        <v>214</v>
+      </c>
+      <c r="F275" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -6746,72 +6749,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>345</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>353</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -6821,622 +6824,622 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>358</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>361</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>376</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>380</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>382</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>404</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>415</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>192</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>428</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>438</v>
+        <v>207</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>454</v>
+        <v>39</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
@@ -7496,7 +7499,7 @@
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
@@ -7526,7 +7529,7 @@
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
@@ -7541,12 +7544,12 @@
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.xlsx
+++ b/data/sport_artwork_review.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC2ADB-EF3F-4C95-A976-DE389B9663C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B5F191-48A7-46A8-B676-16A2B0E30C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sport-artwork review" sheetId="1" r:id="rId1"/>
     <sheet name="BilledeListe" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Vejledning" sheetId="3" r:id="rId3"/>
+    <sheet name="Forsvundne (havde valg)" sheetId="3" r:id="rId3"/>
+    <sheet name="Vejledning" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sport-artwork review'!$A$1:$H$1</definedName>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="486">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -55,1396 +56,1378 @@
     <t>A - 3+/TV3 Sport/TV3 Max/Viaplay</t>
   </si>
   <si>
+    <t>TV3+.dk</t>
+  </si>
+  <si>
+    <t>2 Guns</t>
+  </si>
+  <si>
+    <t>(intet billede)</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
     <t>TV3.SPORT.dk</t>
   </si>
   <si>
-    <t>1. Division Studie</t>
+    <t>3F Superliga: FC Midtjylland - F.C. København</t>
+  </si>
+  <si>
+    <t>3F Superliga.jpg</t>
+  </si>
+  <si>
+    <t>TV3+.dk; TV3.MAX.dk</t>
+  </si>
+  <si>
+    <t>3F Superliga: FC Midtjylland-F.C. København</t>
+  </si>
+  <si>
+    <t>3F Superliga: Silkeborg IF - AC Horsens</t>
+  </si>
+  <si>
+    <t>Betinia LIGA Magasinet</t>
+  </si>
+  <si>
+    <t>Betinia LIGA Magasinet.jpg</t>
+  </si>
+  <si>
+    <t>TV3.MAX.dk</t>
+  </si>
+  <si>
+    <t>Bundesliga Fodbold: Freiburg - Schalke 04</t>
+  </si>
+  <si>
+    <t>Bundesliga_3.JPG</t>
+  </si>
+  <si>
+    <t>Bundesliga Highlights I</t>
+  </si>
+  <si>
+    <t>Champions Hockey League: Herning Blue Fox - Fribourg - Gotteron</t>
+  </si>
+  <si>
+    <t>tv3sport-generic.jpg</t>
+  </si>
+  <si>
+    <t>TV3+.dk; TV3.SPORT.dk; Viaplay.Sport.News.dk</t>
+  </si>
+  <si>
+    <t>Champions League Goal Show</t>
+  </si>
+  <si>
+    <t>UEFA Champions League Goal Show.jpg</t>
+  </si>
+  <si>
+    <t>Champions League Weekly</t>
+  </si>
+  <si>
+    <t>Champions League Weekly.jpg</t>
+  </si>
+  <si>
+    <t>Viaplay.Sport.News.dk</t>
+  </si>
+  <si>
+    <t>Danskerklubben</t>
+  </si>
+  <si>
+    <t>Danskerklubben2.jpg</t>
+  </si>
+  <si>
+    <t>TV3.MAX.dk; TV3.SPORT.dk</t>
+  </si>
+  <si>
+    <t>Deutsche Tourenwagen Masters</t>
+  </si>
+  <si>
+    <t>DTM.jpg</t>
+  </si>
+  <si>
+    <t>EHF European League: Batcho BM. Torrelavega - TTH Holstebro</t>
+  </si>
+  <si>
+    <t>EHF Mens Champions League.jpg</t>
+  </si>
+  <si>
+    <t>Elysium</t>
+  </si>
+  <si>
+    <t>FastZone</t>
+  </si>
+  <si>
+    <t>Fastzone.jpg</t>
+  </si>
+  <si>
+    <t>TV3+.dk; TV3.SPORT.dk</t>
+  </si>
+  <si>
+    <t>Formel 1 360°</t>
+  </si>
+  <si>
+    <t>TMDb</t>
+  </si>
+  <si>
+    <t>Formel 1 Studie</t>
+  </si>
+  <si>
+    <t>F1Studio.jpg</t>
+  </si>
+  <si>
+    <t>Formel 1: Singapores Grand Prix</t>
+  </si>
+  <si>
+    <t>Formel 1.jpg</t>
+  </si>
+  <si>
+    <t>Formel 1: Singapores Grand Prix - Kvalifikation</t>
+  </si>
+  <si>
+    <t>Forsvundet sporløst</t>
+  </si>
+  <si>
+    <t>Før Superligaen</t>
+  </si>
+  <si>
+    <t>Hawaii Five-0</t>
+  </si>
+  <si>
+    <t>Højdepunkter fra Dansk Motorsport</t>
+  </si>
+  <si>
+    <t>Højdepunkter fra Dansk Motorsport.jpg</t>
+  </si>
+  <si>
+    <t>Højdepunkter fra EFL Championship</t>
+  </si>
+  <si>
+    <t>Højdepunkter fra Dansk Motorsport1.jpg</t>
+  </si>
+  <si>
+    <t>Ice Road Truckers</t>
+  </si>
+  <si>
+    <t>Last Light</t>
+  </si>
+  <si>
+    <t>Lastbilchauffører klarer alt</t>
+  </si>
+  <si>
+    <t>Let’s Be Frank</t>
+  </si>
+  <si>
+    <t>Let's be Frank2.jpg</t>
+  </si>
+  <si>
+    <t>MotoGP</t>
+  </si>
+  <si>
+    <t>MotoGP.jpg</t>
+  </si>
+  <si>
+    <t>Mountain Men</t>
+  </si>
+  <si>
+    <t>NCIS</t>
+  </si>
+  <si>
+    <t>NCIS: Los Angeles</t>
+  </si>
+  <si>
+    <t>Neighborhood Wars</t>
+  </si>
+  <si>
+    <t>NHL: Buffalo-Florida</t>
+  </si>
+  <si>
+    <t>NFL.jpg</t>
+  </si>
+  <si>
+    <t>NHL: New Jersey-Ottawa</t>
+  </si>
+  <si>
+    <t>Onside</t>
+  </si>
+  <si>
+    <t>Onside.jpg</t>
+  </si>
+  <si>
+    <t>TV3+.dk; Viaplay.Sport.News.dk</t>
+  </si>
+  <si>
+    <t>Optakt til Champions League</t>
+  </si>
+  <si>
+    <t>Champions League.jpg</t>
+  </si>
+  <si>
+    <t>Pacific Blue</t>
+  </si>
+  <si>
+    <t>Paranormal Caught on Camera</t>
+  </si>
+  <si>
+    <t>Pawn Stars</t>
+  </si>
+  <si>
+    <t>PDC European Tour</t>
+  </si>
+  <si>
+    <t>PDC World Series of Darts2.JPG</t>
+  </si>
+  <si>
+    <t>Police 24/7</t>
+  </si>
+  <si>
+    <t>Premier League Stories</t>
+  </si>
+  <si>
+    <t>Fodbold.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Studie</t>
+  </si>
+  <si>
+    <t>Premier League Studie.jpg</t>
+  </si>
+  <si>
+    <t>Premier League: Chelsea - Bournemouth</t>
+  </si>
+  <si>
+    <t>PL.jpg</t>
+  </si>
+  <si>
+    <t>Premier League: Coventry-Newcastle</t>
+  </si>
+  <si>
+    <t>Premier League: Crystal Palace - Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Premier League: Hull - Everton</t>
+  </si>
+  <si>
+    <t>Premier League: Liverpool-Manchester City</t>
+  </si>
+  <si>
+    <t>Premier League: Manchester United - Tottenham</t>
+  </si>
+  <si>
+    <t>Prizefighter: The Life of Jem Belcher</t>
+  </si>
+  <si>
+    <t>Richard Hammond's Workshop</t>
+  </si>
+  <si>
+    <t>Rust Valley Restorers</t>
+  </si>
+  <si>
+    <t>S.W.A.T.</t>
+  </si>
+  <si>
+    <t>Salvage Kings</t>
+  </si>
+  <si>
+    <t>Sendeophold</t>
+  </si>
+  <si>
+    <t>Shipping Wars</t>
+  </si>
+  <si>
+    <t>Skrotjægerne</t>
+  </si>
+  <si>
+    <t>Sky Sports: Ref Watch</t>
+  </si>
+  <si>
+    <t>Sky Sports Ref Watch.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports: The Football Show</t>
+  </si>
+  <si>
+    <t>Sky Sports The Football Show.jpg</t>
+  </si>
+  <si>
+    <t>Sport News</t>
+  </si>
+  <si>
+    <t>Sport News.jpg</t>
+  </si>
+  <si>
+    <t>Sport vs. Money</t>
+  </si>
+  <si>
+    <t>Sport vs. Money: The Premier League</t>
+  </si>
+  <si>
+    <t>TV3.MAX.dk; Viaplay.Sport.News.dk</t>
+  </si>
+  <si>
+    <t>Sportstalk</t>
+  </si>
+  <si>
+    <t>Sportstalk.jpg</t>
+  </si>
+  <si>
+    <t>Stortømmer</t>
+  </si>
+  <si>
+    <t>Street Fighter - Det endelige opgør</t>
+  </si>
+  <si>
+    <t>Superliga Studie</t>
+  </si>
+  <si>
+    <t>Superliga Studiet.jpg</t>
+  </si>
+  <si>
+    <t>SuperligaTilsynet</t>
+  </si>
+  <si>
+    <t>Top Gear</t>
+  </si>
+  <si>
+    <t>TV3.SPORT.dk; Viaplay.Sport.News.dk</t>
+  </si>
+  <si>
+    <t>TV-Udbruddet</t>
+  </si>
+  <si>
+    <t>TV-Udbruddet.jpg</t>
+  </si>
+  <si>
+    <t>Tøffe vs Graver</t>
+  </si>
+  <si>
+    <t>Tøffe vs. Graver.jpg</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Arsenal - Lille</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Aston Villa - Fenerbahce</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Atletico Madrid - Manchester United</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Bodø/Glimt - Dortmund</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Feyenoord - Como</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Galatasaray - FC Barcelona</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: LASK Linz - Liverpool</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Lens - Sporting Lissabon</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Manchester City - Paris Saint - Germain</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Roma - Real Madrid</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Sabah Baku - Slavia Prag</t>
+  </si>
+  <si>
+    <t>UEFA Champions League: Viking Stavanger - Bayern München</t>
+  </si>
+  <si>
+    <t>UEFA Youth League: Manchester City - Paris Saint - Germain</t>
+  </si>
+  <si>
+    <t>UEFA Youth League: Roma - Real Madrid</t>
+  </si>
+  <si>
+    <t>VAR-rummet</t>
+  </si>
+  <si>
+    <t>Var-rummet.jpg</t>
+  </si>
+  <si>
+    <t>Watt the F1!?</t>
+  </si>
+  <si>
+    <t>Watt the F1.jpg</t>
+  </si>
+  <si>
+    <t>B - TV2 Sport/TV2 Sport X/TV2</t>
+  </si>
+  <si>
+    <t>TV.2.Sport.X.dk</t>
+  </si>
+  <si>
+    <t>3F Superliga: AGF-Sønderjyske</t>
+  </si>
+  <si>
+    <t>3F Superliga: Brøndby IF-Lyngby Boldklub</t>
+  </si>
+  <si>
+    <t>3F Superliga: Efter Brøndby IF-Lyngby Boldklub</t>
+  </si>
+  <si>
+    <t>3F Superliga: Før AGF-Sønderjyske</t>
+  </si>
+  <si>
+    <t>3F Superliga: Før Randers FC-Viborg FF</t>
+  </si>
+  <si>
+    <t>3F Superliga: Randers FC-Viborg FF</t>
+  </si>
+  <si>
+    <t>3F Superliga: Totalfodbold</t>
+  </si>
+  <si>
+    <t>Totalfodbold.jpg</t>
+  </si>
+  <si>
+    <t>ATP Tour Highlights</t>
+  </si>
+  <si>
+    <t>ATP Tour Highlights.jpg</t>
+  </si>
+  <si>
+    <t>ATP: Cerundolo-Mensik, Shanghai</t>
+  </si>
+  <si>
+    <t>TV_2_Sport_X.jpg</t>
+  </si>
+  <si>
+    <t>ATP: Hurkacz-Zhou, Shanghai</t>
+  </si>
+  <si>
+    <t>ATP: Shanghai</t>
+  </si>
+  <si>
+    <t>ATP_WTA Tennis.jpg</t>
+  </si>
+  <si>
+    <t>ATP: Shelton-Gea, Shanghai</t>
+  </si>
+  <si>
+    <t>ATP: Zverev-Halys, Shanghai</t>
+  </si>
+  <si>
+    <t>TV.2.Sport.dk</t>
+  </si>
+  <si>
+    <t>Badminton: Antonsen-Lee, semifinale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton.jpg</t>
+  </si>
+  <si>
+    <t>Badminton: Antonsen-Tanaka, finale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton: Blichfeldt-Intanon, finale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton: Blichfeldt-Okuhara, semifinale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton: Chen/Luo-Hsu/Lin, finale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton: Denmark Open</t>
+  </si>
+  <si>
+    <t>Badminton: Finale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton: Jiang/Wei-Gao/Wu, finale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton: Kjær/Kjær-Tai/Yap, semifinale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Badminton: Tai/Yap-Lai/Tsai, finale, Arctic Open</t>
+  </si>
+  <si>
+    <t>Cykling: Paris Tours</t>
+  </si>
+  <si>
+    <t>Cykling-generic.jpg</t>
+  </si>
+  <si>
+    <t>Fodbold: Tirsdagstrænerne</t>
+  </si>
+  <si>
+    <t>Tirsdagstrænerne.jpg</t>
+  </si>
+  <si>
+    <t>Herreligaen: Skanderborg AGF-Fredericia</t>
+  </si>
+  <si>
+    <t>Herreligaen.jpg</t>
+  </si>
+  <si>
+    <t>Herreligaen: Skjern - Bjerringbro-Silkeborg</t>
+  </si>
+  <si>
+    <t>Herreligaen: Skjern-BSH</t>
+  </si>
+  <si>
+    <t>Herreligaen: Studiet</t>
+  </si>
+  <si>
+    <t>NFL: Jacksonville Jaguars-Philadelphia Eagles</t>
+  </si>
+  <si>
+    <t>NFL: New Orleans Saints-Minnesota Vikings</t>
+  </si>
+  <si>
+    <t>NFL: Seattle Seahawks-San Francisco 49ers</t>
+  </si>
+  <si>
+    <t>Serie A: Atalanta-Venezia</t>
+  </si>
+  <si>
+    <t>Serie A.jpg</t>
+  </si>
+  <si>
+    <t>Serie A: Cagliari-Juventus</t>
+  </si>
+  <si>
+    <t>Serie A: Torino-Udinese</t>
+  </si>
+  <si>
+    <t>VM i banecykling</t>
+  </si>
+  <si>
+    <t>VM i gravelcykling</t>
+  </si>
+  <si>
+    <t>WTA: Andreeva-Bartunkova, semifinale, Beijing</t>
+  </si>
+  <si>
+    <t>WTA-generic.jpeg</t>
+  </si>
+  <si>
+    <t>WTA: Wuhan</t>
+  </si>
+  <si>
+    <t>TV.2.Sport.X.dk; TV.2.Sport.dk</t>
+  </si>
+  <si>
+    <t>WTA: Zheng-Andreeva, finale, Beijing</t>
+  </si>
+  <si>
+    <t>C - DR1/DR2</t>
+  </si>
+  <si>
+    <t>DR1.dk</t>
+  </si>
+  <si>
+    <t>80 dage til sommerhus</t>
+  </si>
+  <si>
+    <t>Aftenshowet</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken Australien</t>
+  </si>
+  <si>
+    <t>DR2.dk</t>
+  </si>
+  <si>
+    <t>Alle Guds farver</t>
+  </si>
+  <si>
+    <t>Alt forladt - Scala-bygningen</t>
+  </si>
+  <si>
+    <t>Angkor Vats hemmeligheder</t>
+  </si>
+  <si>
+    <t>Balladen om det beskidte vand</t>
+  </si>
+  <si>
+    <t>Baywatch bag facaden</t>
+  </si>
+  <si>
+    <t>Beck: Den fortabte søn</t>
+  </si>
+  <si>
+    <t>Beck: Et nyt liv</t>
+  </si>
+  <si>
+    <t>Bonderøven 2010</t>
+  </si>
+  <si>
+    <t>Christiania</t>
+  </si>
+  <si>
+    <t>Cooper &amp; Fry: Sort lune</t>
+  </si>
+  <si>
+    <t>Danmark i Den Kolde Krig</t>
+  </si>
+  <si>
+    <t>Dansk teater 300 år: Det politiske teater</t>
+  </si>
+  <si>
+    <t>De ville dø for sagen: Olga &amp; nazismen</t>
+  </si>
+  <si>
+    <t>DR1.dk; DR2.dk</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>Deadline: Fransk gældsbombe truer Europa</t>
+  </si>
+  <si>
+    <t>Deadline: Hænger Danmark stadig sammen?</t>
+  </si>
+  <si>
+    <t>Deadline: Israels ambassadør om den 7. oktober og krigen i Gaza</t>
+  </si>
+  <si>
+    <t>Den klassiske musikquiz</t>
+  </si>
+  <si>
+    <t>Den store bagedyst</t>
+  </si>
+  <si>
+    <t>Drømmen om et liv på landet</t>
+  </si>
+  <si>
+    <t>Dyrenes underverden</t>
+  </si>
+  <si>
+    <t>Dødens velodrom</t>
+  </si>
+  <si>
+    <t>EM bordtennis: Single (m), 1/32-finaler, direkte</t>
+  </si>
+  <si>
+    <t>En barndom fuld af druk</t>
+  </si>
+  <si>
+    <t>Farlig drømmedate</t>
+  </si>
+  <si>
+    <t>Filmperler: De andres liv</t>
+  </si>
+  <si>
+    <t>Fodbold: Canada - Danmark (k), direkte</t>
+  </si>
+  <si>
+    <t>Folk og fæ</t>
+  </si>
+  <si>
+    <t>Frank &amp; Kastaniegaarden - Lækre spær og havelåge med svung</t>
+  </si>
+  <si>
+    <t>Frank Hvam: Make Badminton Great Again</t>
+  </si>
+  <si>
+    <t>Galopbanens hemmeligheder</t>
+  </si>
+  <si>
+    <t>Generation SoMe!</t>
+  </si>
+  <si>
+    <t>Gi' så mor et kys - det er bare sagen</t>
+  </si>
+  <si>
+    <t>Gudstjenesten: Marie Nipper - Troens billeder</t>
+  </si>
+  <si>
+    <t>Hammerslag 2022 - Huse med alder og charme</t>
+  </si>
+  <si>
+    <t>Hammerslag 2022 - Lejlighed i storbyen</t>
+  </si>
+  <si>
+    <t>Hammerslag 2022 - Store feriehuse</t>
+  </si>
+  <si>
+    <t>Historien om den norske kongefamilie</t>
+  </si>
+  <si>
+    <t>Husdrøm fra himlen - med Keith og Marj</t>
+  </si>
+  <si>
+    <t>Huse med hemmeligheder</t>
+  </si>
+  <si>
+    <t>Husker du...</t>
+  </si>
+  <si>
+    <t>Høst</t>
+  </si>
+  <si>
+    <t>Jagten på Danmarkshistorien</t>
+  </si>
+  <si>
+    <t>Jagten på de sidste naziforbrydere</t>
+  </si>
+  <si>
+    <t>Jens i vildmarken</t>
+  </si>
+  <si>
+    <t>Jerusalem - Kampen om den hellige by</t>
+  </si>
+  <si>
+    <t>Jordemoderen</t>
+  </si>
+  <si>
+    <t>Josephine Baker - Stjerne, spion og folkets stemme</t>
+  </si>
+  <si>
+    <t>Ka' du li' ål i karry, Harry?</t>
+  </si>
+  <si>
+    <t>Kabul</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2020 - med dyt og dyppelse</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2020 - med filler og følelser</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2020 - med grill på badeværelset</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2024 - Med hundelagkage og højt til loftet</t>
+  </si>
+  <si>
+    <t>Kinas smukke natur</t>
+  </si>
+  <si>
+    <t>Kommissionen - Folketingets sæsonstart med slagsmål om sindelag, SU og Søren Gades sure exit</t>
+  </si>
+  <si>
+    <t>Kongehuse i krise: Norge</t>
+  </si>
+  <si>
+    <t>Kontinenterne</t>
+  </si>
+  <si>
+    <t>Krigens døgn: Kamprobotter bag fjendens linjer</t>
+  </si>
+  <si>
+    <t>Krigsmaskinen</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby XII: Bristen</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby XII: Den sorte bog</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby XII: Listetyven</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby XII: Mord ved 13. hul</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby XII: Små glæder</t>
+  </si>
+  <si>
+    <t>Kriminalkommissær Barnaby XII: Spioner</t>
+  </si>
+  <si>
+    <t>Kriminelt: Betal eller dø</t>
+  </si>
+  <si>
+    <t>Kriseøvelse: Hybridangreb på Danmark</t>
+  </si>
+  <si>
+    <t>Kunstnerkolonien på Sydfyn</t>
+  </si>
+  <si>
+    <t>Ludere, lommetyve og lirekassemænd</t>
+  </si>
+  <si>
+    <t>Mens vi venter på at dø - Graver vi et hul</t>
+  </si>
+  <si>
+    <t>Mesterstrikkerne</t>
+  </si>
+  <si>
+    <t>Mig og 70'erne</t>
+  </si>
+  <si>
+    <t>Militærkuppet i Chile</t>
+  </si>
+  <si>
+    <t>Min kunstige kæreste</t>
+  </si>
+  <si>
+    <t>Morgenandagten</t>
+  </si>
+  <si>
+    <t>Mors dreng</t>
+  </si>
+  <si>
+    <t>Norges naturskønne nationalparker</t>
+  </si>
+  <si>
+    <t>Nul stjerner - på camping i Sydtyskland</t>
+  </si>
+  <si>
+    <t>Nul stjerner - Scooterferie i Grækenland</t>
+  </si>
+  <si>
+    <t>Nul stjerner - Tømmerflådeferie i Holland</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>Once Upon a Time... in Hollywood</t>
+  </si>
+  <si>
+    <t>Optimistens guide til planeten</t>
+  </si>
+  <si>
+    <t>P3 Essensen - Sundhedstrends: Hvad skal man egentlig tro på?</t>
+  </si>
+  <si>
+    <t>P3 Essensen: AI overtager måske dit job hurtigere end du tror</t>
+  </si>
+  <si>
+    <t>På rejse med Griff - Sydstaterne</t>
+  </si>
+  <si>
+    <t>På æblerov med Frank Erichsen</t>
+  </si>
+  <si>
+    <t>Radioavisen</t>
+  </si>
+  <si>
+    <t>Riefenstahl - Instruktør for nazisterne</t>
+  </si>
+  <si>
+    <t>Sandheden om fængselseksperimentet</t>
+  </si>
+  <si>
+    <t>Seneste nyt fra TVA</t>
+  </si>
+  <si>
+    <t>Shalako</t>
+  </si>
+  <si>
+    <t>Signe Molde på udebane: Hash er harmløst</t>
+  </si>
+  <si>
+    <t>Smagen af Italien</t>
+  </si>
+  <si>
+    <t>Sporløs UK</t>
+  </si>
+  <si>
+    <t>Sporløs UK - Sådan gik det</t>
+  </si>
+  <si>
+    <t>Sportsmagasinet</t>
+  </si>
+  <si>
+    <t>Stjerner og striber: Præster på prærien presser Trump</t>
+  </si>
+  <si>
+    <t>Stjernerne fra lokal-tv</t>
+  </si>
+  <si>
+    <t>Store danskere - Hans Scherfig</t>
+  </si>
+  <si>
+    <t>Super-showet</t>
+  </si>
+  <si>
+    <t>Team Bachstad på hjemmebane</t>
+  </si>
+  <si>
+    <t>The Capture</t>
+  </si>
+  <si>
+    <t>The Dark</t>
+  </si>
+  <si>
+    <t>Troldspejlet: Pokémon for voksne</t>
+  </si>
+  <si>
+    <t>TVA</t>
+  </si>
+  <si>
+    <t>Tænkepauser: Krig</t>
+  </si>
+  <si>
+    <t>Udsendelsesophør</t>
+  </si>
+  <si>
+    <t>Under sydens sol</t>
+  </si>
+  <si>
+    <t>Verdens mest eftersøgte våbenhandler</t>
+  </si>
+  <si>
+    <t>Verdenssituationen med Clement</t>
+  </si>
+  <si>
+    <t>Verner Panton - En dansk verdensstjerne</t>
+  </si>
+  <si>
+    <t>Vikaren</t>
+  </si>
+  <si>
+    <t>Vil AI tage mit job?</t>
+  </si>
+  <si>
+    <t>Vilde familier - helt kort</t>
+  </si>
+  <si>
+    <t>Vilde vidunderlige Danmark - Gråsælen</t>
+  </si>
+  <si>
+    <t>Vinterkrigens piloter og dobbeltspioner</t>
+  </si>
+  <si>
+    <t>Vores sange med DR Pigekoret: Dansevise</t>
+  </si>
+  <si>
+    <t>Vores Vejr</t>
+  </si>
+  <si>
+    <t>Værtshushistorier: Cosy Bar</t>
+  </si>
+  <si>
+    <t>Woman of the Hour</t>
+  </si>
+  <si>
+    <t>Ørkenrigets mægtigste mand</t>
+  </si>
+  <si>
+    <t>360F1.jpg</t>
+  </si>
+  <si>
+    <t>A-Liga.jpg</t>
+  </si>
+  <si>
+    <t>ATP_WTA Tennis2.jpg</t>
+  </si>
+  <si>
+    <t>Aften Paris Nice.jpg</t>
+  </si>
+  <si>
+    <t>Aften Roubaix.jpg</t>
+  </si>
+  <si>
+    <t>AftenVuelta.jpg</t>
+  </si>
+  <si>
+    <t>Aftentour.jpg</t>
+  </si>
+  <si>
+    <t>Atletik Diamond League.jpg</t>
+  </si>
+  <si>
+    <t>Betinia Liga.jpg</t>
   </si>
   <si>
     <t>BetiniaStudio.jpg</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>TV3+.dk</t>
-  </si>
-  <si>
-    <t>2 Guns</t>
-  </si>
-  <si>
-    <t>(intet billede)</t>
-  </si>
-  <si>
-    <t>3F Superliga: FC Midtjylland - F.C. København</t>
-  </si>
-  <si>
-    <t>Fodbold.jpg</t>
-  </si>
-  <si>
-    <t>3F Superliga.jpg</t>
-  </si>
-  <si>
-    <t>TV3+.dk; TV3.MAX.dk</t>
-  </si>
-  <si>
-    <t>3F Superliga: FC Midtjylland-F.C. København</t>
-  </si>
-  <si>
-    <t>TV3.MAX.dk</t>
+    <t>Bundesliga Fodbold.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga Review of the Midseason.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga Saturday Highlights.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga Special.jpg</t>
+  </si>
+  <si>
+    <t>CLWomen.jpg</t>
+  </si>
+  <si>
+    <t>Champions Hockey League.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Clásica San Sebastián.jpg</t>
+  </si>
+  <si>
+    <t>Cykling La Vuelta Femenina.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Paris Nice.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Polen Rundt.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Postnord Danmark Rundt.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour Auvergne Rhone-Alpes.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de France Femmes.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de France.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de France2.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Tour de Romandie.jpg</t>
+  </si>
+  <si>
+    <t>Cykling Volta.jpg</t>
+  </si>
+  <si>
+    <t>Cykling.jpg</t>
+  </si>
+  <si>
+    <t>DBU Pokalen.jpg</t>
+  </si>
+  <si>
+    <t>DP World Tour Danish Golf Championship.jpg</t>
+  </si>
+  <si>
+    <t>Davis Cup.jpg</t>
+  </si>
+  <si>
+    <t>Discover a Club.jpg</t>
+  </si>
+  <si>
+    <t>EFL Championship Highligts.jpg</t>
+  </si>
+  <si>
+    <t>EFL.jpg</t>
+  </si>
+  <si>
+    <t>EHF European League.jpg</t>
+  </si>
+  <si>
+    <t>EM i atletik.jpg</t>
+  </si>
+  <si>
+    <t>Endurance Car Racing.jpg</t>
+  </si>
+  <si>
+    <t>Euro Cup Håndbold.jpg</t>
+  </si>
+  <si>
+    <t>F1.jpg</t>
+  </si>
+  <si>
+    <t>F1Q.JPG</t>
+  </si>
+  <si>
+    <t>F1T.JPG</t>
+  </si>
+  <si>
+    <t>F2.jpg</t>
+  </si>
+  <si>
+    <t>F2_Chasing the Dream.jpg</t>
+  </si>
+  <si>
+    <t>F3.jpg</t>
+  </si>
+  <si>
+    <t>FIA World Endurance Championship.jpg</t>
+  </si>
+  <si>
+    <t>FIFA VM 2026.jpg</t>
+  </si>
+  <si>
+    <t>Fodbold Carabao Cup.jpg</t>
+  </si>
+  <si>
+    <t>Fodbold Friuli Venezia Giulia Cup - Kampe.jpg</t>
+  </si>
+  <si>
+    <t>Fodbold Serie A.jpg</t>
+  </si>
+  <si>
+    <t>Formel E VM.jpg</t>
+  </si>
+  <si>
+    <t>Før Superligaen.jpg</t>
+  </si>
+  <si>
+    <t>Golf LPGA Tour.jpg</t>
+  </si>
+  <si>
+    <t>Golf PGA Champions Tour.jpg</t>
+  </si>
+  <si>
+    <t>Golf PGA Tour.jpg</t>
+  </si>
+  <si>
+    <t>Golf Scandinavian Challenge.jpg</t>
+  </si>
+  <si>
+    <t>Gp Confidential.jpg</t>
+  </si>
+  <si>
+    <t>HBL Håndbold.jpg</t>
+  </si>
+  <si>
+    <t>Håndbold  Golden League.jpg</t>
+  </si>
+  <si>
+    <t>Håndbold Herre Pokal.jpg</t>
+  </si>
+  <si>
+    <t>Håndbold Herreligaen.jpg</t>
+  </si>
+  <si>
+    <t>Håndbold Kvindeligaen.jpg</t>
+  </si>
+  <si>
+    <t>IndyCar1.jpg</t>
+  </si>
+  <si>
+    <t>Kvindeligaen.jpg</t>
+  </si>
+  <si>
+    <t>Landstrænerne.jpg</t>
+  </si>
+  <si>
+    <t>Le Mans.jpg</t>
+  </si>
+  <si>
+    <t>League Cup.jpg</t>
+  </si>
+  <si>
+    <t>Lets Be Frank.jpg</t>
+  </si>
+  <si>
+    <t>Ligue 1 The Season Review Show.jpg</t>
+  </si>
+  <si>
+    <t>Ligue 1_2.jpg</t>
+  </si>
+  <si>
+    <t>Ligue1.jpg</t>
+  </si>
+  <si>
+    <t>MotoGp Season Review.jpg</t>
+  </si>
+  <si>
+    <t>Motocross.jpg</t>
+  </si>
+  <si>
+    <t>Motorsport-generic.jpg</t>
+  </si>
+  <si>
+    <t>Målfesten.jpg</t>
+  </si>
+  <si>
+    <t>NFL Gameday.jpg</t>
+  </si>
+  <si>
+    <t>NFL2.jpg</t>
+  </si>
+  <si>
+    <t>NHL.jpg</t>
+  </si>
+  <si>
+    <t>Nations League1.jpg</t>
+  </si>
+  <si>
+    <t>Nations LeagueDK.jpg</t>
+  </si>
+  <si>
+    <t>PDC Darts.jpg</t>
+  </si>
+  <si>
+    <t>PDC European Tour.jpg</t>
+  </si>
+  <si>
+    <t>Pokal-highligts.jpg</t>
+  </si>
+  <si>
+    <t>Pokalkampe.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Goals of the Season.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Netbusters.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Preview.jpg</t>
+  </si>
+  <si>
+    <t>Premier League Review.jpg</t>
+  </si>
+  <si>
+    <t>Premier League-studiet.jpg</t>
+  </si>
+  <si>
+    <t>Premier League.jpg</t>
+  </si>
+  <si>
+    <t>RaceTV_DK.jpg</t>
+  </si>
+  <si>
+    <t>Skisport.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports Deadline Day.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports Fan Club.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports Soccer Saturday.jpg</t>
+  </si>
+  <si>
+    <t>Snooker.jpg</t>
+  </si>
+  <si>
+    <t>Speedway FIM Speedway Grand Prix.jpg</t>
+  </si>
+  <si>
+    <t>Sporten.jpg</t>
+  </si>
+  <si>
+    <t>Spot på Betinia Liga.jpg</t>
+  </si>
+  <si>
+    <t>Superligaens Topchefer.jpg</t>
+  </si>
+  <si>
+    <t>Superligaens Topchefer2.jpg</t>
+  </si>
+  <si>
+    <t>Superligatilsynet.jpg</t>
+  </si>
+  <si>
+    <t>Tennis Billie-Jean-King-Cup.jpg</t>
+  </si>
+  <si>
+    <t>Tennis-generic3.jpg</t>
+  </si>
+  <si>
+    <t>Tour Studiet.jpg</t>
+  </si>
+  <si>
+    <t>Tour de France Femmes Studiet.jpg</t>
+  </si>
+  <si>
+    <t>Tourstudiet.jpg</t>
+  </si>
+  <si>
+    <t>UEFA Champions League.jpg</t>
+  </si>
+  <si>
+    <t>UEFA Conference League Qualification Studio.jpg</t>
+  </si>
+  <si>
+    <t>UEFA Europa og Conference League.jpg</t>
+  </si>
+  <si>
+    <t>UEFA Super Cup.jpg</t>
+  </si>
+  <si>
+    <t>UEFA Youth League.jpg</t>
+  </si>
+  <si>
+    <t>US Open.jpg</t>
+  </si>
+  <si>
+    <t>Ultimate Championship.jpg</t>
+  </si>
+  <si>
+    <t>VM i MTB.jpg</t>
+  </si>
+  <si>
+    <t>VM i dressur.jpg</t>
+  </si>
+  <si>
+    <t>VM i dressur2.jpg</t>
+  </si>
+  <si>
+    <t>VM i landevejscykling.jpg</t>
+  </si>
+  <si>
+    <t>Venskabskamp Testkamp.jpg</t>
+  </si>
+  <si>
+    <t>Viaplay_Sport_News-generic.jpg</t>
+  </si>
+  <si>
+    <t>Vuelta a España -  Studiet.jpg</t>
+  </si>
+  <si>
+    <t>Vuelta a España.jpeg</t>
+  </si>
+  <si>
+    <t>WTA-generic.jpg</t>
+  </si>
+  <si>
+    <t>Womens CL.jpg</t>
+  </si>
+  <si>
+    <t>cykling4.jpg</t>
+  </si>
+  <si>
+    <t>tv2sport-generic.jpg</t>
+  </si>
+  <si>
+    <t>Tidligere valgt billede</t>
   </si>
   <si>
     <t>3F Superliga: FC Nordsjælland-OB</t>
   </si>
   <si>
-    <t>3F Superliga: Silkeborg IF - AC Horsens</t>
-  </si>
-  <si>
-    <t>Betinia LIGA Magasinet</t>
-  </si>
-  <si>
-    <t>Betinia LIGA Magasinet.jpg</t>
-  </si>
-  <si>
     <t>Betinia LIGA: Esbjerg fB - AaB</t>
   </si>
   <si>
-    <t>tv3sport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Betinia Liga.jpg</t>
-  </si>
-  <si>
-    <t>Viaplay.Sport.News.dk</t>
-  </si>
-  <si>
     <t>Betinia LIGA: Hobro IK - Kolding IF</t>
   </si>
   <si>
-    <t>https://i-viaplay-com.akamaized.net/viaplay-prod/155/944/Sport_News1920x1080_SportNews_ok.jpg</t>
-  </si>
-  <si>
-    <t>Black Adam</t>
-  </si>
-  <si>
     <t>Bundesliga Fodbold: Dortmund-Werder Bremen</t>
   </si>
   <si>
-    <t>Bundesliga_3.JPG</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Freiburg - Schalke 04</t>
-  </si>
-  <si>
-    <t>Bundesliga Highlights I</t>
-  </si>
-  <si>
-    <t>TV3+.dk; Viaplay.Sport.News.dk</t>
-  </si>
-  <si>
-    <t>Champions League Goal Show</t>
-  </si>
-  <si>
-    <t>UEFA Champions League Goal Show.jpg</t>
-  </si>
-  <si>
-    <t>TV3.MAX.dk; TV3.SPORT.dk</t>
-  </si>
-  <si>
-    <t>Champions League Weekly</t>
-  </si>
-  <si>
-    <t>Champions League Weekly.jpg</t>
-  </si>
-  <si>
-    <t>Chasing the Dream</t>
-  </si>
-  <si>
-    <t>TMDb</t>
-  </si>
-  <si>
-    <t>Danskerklubben</t>
-  </si>
-  <si>
-    <t>Danskerklubben2.jpg</t>
-  </si>
-  <si>
-    <t>Deutsche Tourenwagen Masters</t>
-  </si>
-  <si>
-    <t>DTM.jpg</t>
-  </si>
-  <si>
     <t>EFL Championship: Swansea - Norwich</t>
   </si>
   <si>
-    <t>EFL.jpg</t>
-  </si>
-  <si>
-    <t>EHF European League: Batcho BM. Torrelavega - TTH Holstebro</t>
-  </si>
-  <si>
-    <t>EHF Mens Champions League.jpg</t>
-  </si>
-  <si>
-    <t>Elysium</t>
-  </si>
-  <si>
-    <t>F1 Qualification Studio</t>
-  </si>
-  <si>
-    <t>F1Q.JPG</t>
-  </si>
-  <si>
-    <t>TV3+.dk; TV3.SPORT.dk</t>
-  </si>
-  <si>
-    <t>Formel 1 360°</t>
-  </si>
-  <si>
-    <t>Formel 1 Studie</t>
-  </si>
-  <si>
-    <t>F1Studio.jpg</t>
-  </si>
-  <si>
-    <t>Formel 1: Singapores Grand Prix</t>
-  </si>
-  <si>
-    <t>Formel 1.jpg</t>
-  </si>
-  <si>
-    <t>Formel 1: Singapores Grand Prix - Kvalifikation</t>
-  </si>
-  <si>
-    <t>Formel 1: Singapores Grand Prix - Sprint kvalifikation</t>
-  </si>
-  <si>
-    <t>Formel 1: Singapores Grand Prix - Sprint Race</t>
-  </si>
-  <si>
-    <t>Forsvundet sporløst</t>
-  </si>
-  <si>
-    <t>Før Superligaen</t>
-  </si>
-  <si>
-    <t>Før Superligaen Brøndby IF</t>
-  </si>
-  <si>
-    <t>Før Superligaen.jpg</t>
-  </si>
-  <si>
-    <t>Før Superligaen F.C. København</t>
-  </si>
-  <si>
-    <t>Før Superligaen FC Midtjylland</t>
-  </si>
-  <si>
-    <t>GP Confidential</t>
-  </si>
-  <si>
-    <t>Hawaii Five-0</t>
-  </si>
-  <si>
-    <t>Højdepunkter fra Dansk Motorsport</t>
-  </si>
-  <si>
-    <t>Højdepunkter fra Dansk Motorsport.jpg</t>
-  </si>
-  <si>
-    <t>Højdepunkter fra EFL Championship</t>
-  </si>
-  <si>
-    <t>Højdepunkter fra Dansk Motorsport1.jpg</t>
-  </si>
-  <si>
-    <t>Ice Road Truckers</t>
-  </si>
-  <si>
-    <t>Jumanji: The Next Level</t>
-  </si>
-  <si>
-    <t>Last Light</t>
-  </si>
-  <si>
-    <t>Lastbilchauffører klarer alt</t>
-  </si>
-  <si>
-    <t>TV3.MAX.dk; Viaplay.Sport.News.dk</t>
-  </si>
-  <si>
-    <t>Let’s Be Frank</t>
-  </si>
-  <si>
-    <t>Let's be Frank2.jpg</t>
-  </si>
-  <si>
     <t>Ligue 1: Paris Saint - Germain - Le Mans</t>
   </si>
   <si>
-    <t>Ligue 1_2.jpg</t>
-  </si>
-  <si>
-    <t>MotoGP</t>
-  </si>
-  <si>
-    <t>MotoGP.jpg</t>
-  </si>
-  <si>
-    <t>Mountain Men</t>
-  </si>
-  <si>
-    <t>NCIS</t>
-  </si>
-  <si>
-    <t>NCIS: Los Angeles</t>
-  </si>
-  <si>
-    <t>Neighborhood Wars</t>
-  </si>
-  <si>
-    <t>NHL: Buffalo-Florida</t>
-  </si>
-  <si>
-    <t>NFL.jpg</t>
-  </si>
-  <si>
     <t>NHL: Florida Panthers - Minnesota Wild</t>
   </si>
   <si>
-    <t>NHL: New Jersey-Ottawa</t>
-  </si>
-  <si>
-    <t>TV3+.dk; TV3.SPORT.dk; Viaplay.Sport.News.dk</t>
-  </si>
-  <si>
-    <t>Onside</t>
-  </si>
-  <si>
-    <t>Onside.jpg</t>
-  </si>
-  <si>
-    <t>Optakt til Champions League</t>
-  </si>
-  <si>
-    <t>Champions League.jpg</t>
-  </si>
-  <si>
-    <t>Pacific Blue</t>
-  </si>
-  <si>
-    <t>Paranormal Caught on Camera</t>
-  </si>
-  <si>
-    <t>Pawn Stars</t>
-  </si>
-  <si>
-    <t>PDC European Tour</t>
-  </si>
-  <si>
-    <t>PDC World Series of Darts2.JPG</t>
-  </si>
-  <si>
-    <t>Police 24/7</t>
-  </si>
-  <si>
-    <t>TV3+.dk; TV3.MAX.dk; TV3.SPORT.dk</t>
-  </si>
-  <si>
-    <t>Premier League Studie</t>
-  </si>
-  <si>
-    <t>Premier League Studie.jpg</t>
-  </si>
-  <si>
     <t>Premier League: Aston Villa - Brentford</t>
   </si>
   <si>
-    <t>PL.jpg</t>
-  </si>
-  <si>
-    <t>Premier League: Chelsea - Bournemouth</t>
-  </si>
-  <si>
-    <t>Premier League: Coventry-Newcastle</t>
-  </si>
-  <si>
-    <t>Premier League: Crystal Palace - Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Premier League: Hull - Everton</t>
-  </si>
-  <si>
     <t>Premier League: Ipswich - Fulham</t>
   </si>
   <si>
-    <t>Premier League: Liverpool-Manchester City</t>
-  </si>
-  <si>
-    <t>Premier League: Manchester United - Tottenham</t>
-  </si>
-  <si>
     <t>Premier League: Sunderland - Brighton</t>
   </si>
   <si>
-    <t>Prizefighter: The Life of Jem Belcher</t>
-  </si>
-  <si>
-    <t>Richard Hammond's Workshop</t>
-  </si>
-  <si>
-    <t>Rust Valley Restorers</t>
-  </si>
-  <si>
-    <t>S.W.A.T.</t>
-  </si>
-  <si>
-    <t>Salvage Kings</t>
-  </si>
-  <si>
-    <t>Sendeophold</t>
-  </si>
-  <si>
-    <t>Shipping Wars</t>
-  </si>
-  <si>
-    <t>Skrotjægerne</t>
-  </si>
-  <si>
-    <t>Sky Sports Fan Club</t>
-  </si>
-  <si>
-    <t>Sky Sports Fan Club.jpg</t>
-  </si>
-  <si>
-    <t>Sky Sports: Ref Watch</t>
-  </si>
-  <si>
-    <t>Sky Sports Ref Watch.jpg</t>
-  </si>
-  <si>
-    <t>Sky Sports: Soccer Saturday</t>
-  </si>
-  <si>
-    <t>Sky Sports Soccer Saturday.jpg</t>
-  </si>
-  <si>
-    <t>Sky Sports: The Football Show</t>
-  </si>
-  <si>
-    <t>Sky Sports The Football Show.jpg</t>
-  </si>
-  <si>
-    <t>Sport News</t>
-  </si>
-  <si>
-    <t>Sport News.jpg</t>
-  </si>
-  <si>
-    <t>Sport vs. Money</t>
-  </si>
-  <si>
-    <t>Sport vs. Money: The Premier League</t>
-  </si>
-  <si>
-    <t>Sportstalk</t>
-  </si>
-  <si>
-    <t>Sportstalk.jpg</t>
-  </si>
-  <si>
-    <t>Stortømmer</t>
-  </si>
-  <si>
-    <t>Street Fighter - Det endelige opgør</t>
-  </si>
-  <si>
-    <t>Superliga Studie</t>
-  </si>
-  <si>
-    <t>Superliga Studiet.jpg</t>
-  </si>
-  <si>
-    <t>SuperligaTilsynet</t>
-  </si>
-  <si>
-    <t>Top Gear</t>
-  </si>
-  <si>
-    <t>TV3.SPORT.dk; Viaplay.Sport.News.dk</t>
-  </si>
-  <si>
-    <t>TV-Udbruddet</t>
-  </si>
-  <si>
-    <t>TV-Udbruddet.jpg</t>
-  </si>
-  <si>
-    <t>Tøffe vs Graver</t>
-  </si>
-  <si>
-    <t>Tøffe vs. Graver.jpg</t>
-  </si>
-  <si>
-    <t>UEFA Champions League: Arsenal - Lille</t>
-  </si>
-  <si>
-    <t>UEFA Champions League: Atletico Madrid - Manchester United</t>
-  </si>
-  <si>
-    <t>UEFA Champions League: Galatasaray - FC Barcelona</t>
-  </si>
-  <si>
-    <t>UEFA Champions League: Lens - Sporting Lissabon</t>
-  </si>
-  <si>
-    <t>UEFA Champions League: Sabah Baku - Slavia Prag</t>
-  </si>
-  <si>
-    <t>UEFA Champions League: Viking Stavanger - Bayern München</t>
-  </si>
-  <si>
-    <t>VAR-rummet</t>
-  </si>
-  <si>
-    <t>Var-rummet.jpg</t>
-  </si>
-  <si>
-    <t>Watt the F1!?</t>
-  </si>
-  <si>
-    <t>Watt the F1.jpg</t>
-  </si>
-  <si>
-    <t>We Got This</t>
-  </si>
-  <si>
-    <t>B - TV2 Sport/TV2 Sport X/TV2</t>
-  </si>
-  <si>
-    <t>TV.2.Sport.X.dk</t>
-  </si>
-  <si>
-    <t>3F Superliga: AGF-Sønderjyske</t>
-  </si>
-  <si>
-    <t>3F Superliga: Brøndby IF-Lyngby Boldklub</t>
-  </si>
-  <si>
-    <t>3F Superliga: Efter Brøndby IF-Lyngby Boldklub</t>
-  </si>
-  <si>
-    <t>3F Superliga: Før AGF-Sønderjyske</t>
-  </si>
-  <si>
-    <t>3F Superliga: Før Randers FC-Viborg FF</t>
-  </si>
-  <si>
-    <t>3F Superliga: Randers FC-Viborg FF</t>
-  </si>
-  <si>
-    <t>3F Superliga: Totalfodbold</t>
-  </si>
-  <si>
-    <t>Totalfodbold.jpg</t>
-  </si>
-  <si>
-    <t>ATP Tour Highlights</t>
-  </si>
-  <si>
-    <t>ATP Tour Highlights.jpg</t>
-  </si>
-  <si>
     <t>ATP: Carabelli - Auger-Aliassime, Shanghai</t>
   </si>
   <si>
-    <t>TV_2_Sport_X.jpg</t>
-  </si>
-  <si>
-    <t>ATP_WTA Tennis.jpg</t>
-  </si>
-  <si>
     <t>ATP: Cerundolo-Alcaraz, Shanghai</t>
   </si>
   <si>
-    <t>ATP: Shanghai</t>
-  </si>
-  <si>
-    <t>TV.2.Sport.dk</t>
-  </si>
-  <si>
-    <t>Badminton: Antonsen-Hu, kvartfinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton.jpg</t>
-  </si>
-  <si>
-    <t>Badminton: Antonsen-Lee, semifinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton: Blichfeldt-Han, kvartfinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton: Blichfeldt-Okuhara, semifinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton: Christophersen-Intanon, semifinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton: Denmark Open</t>
-  </si>
-  <si>
-    <t>Badminton: Finale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton: Kjær/Kjær-Garaga/Roy, kvartfinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton: Kjær/Kjær-Tai/Yap, semifinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Badminton: Semifinale, Arctic Open</t>
-  </si>
-  <si>
-    <t>Cykling: Paris Tours</t>
-  </si>
-  <si>
-    <t>Cykling-generic.jpg</t>
-  </si>
-  <si>
-    <t>Herreligaen: Skanderborg AGF-Fredericia</t>
-  </si>
-  <si>
-    <t>tv2sport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Herreligaen.jpg</t>
-  </si>
-  <si>
-    <t>Herreligaen: Skjern - Bjerringbro-Silkeborg</t>
-  </si>
-  <si>
-    <t>Herreligaen: Skjern-BSH</t>
-  </si>
-  <si>
-    <t>Herreligaen: Studiet</t>
-  </si>
-  <si>
-    <t>Håndbold Herreligaen.jpg</t>
-  </si>
-  <si>
     <t>Holger Rune er tilbage på banen</t>
   </si>
   <si>
-    <t>NFL: Jacksonville Jaguars-Philadelphia Eagles</t>
-  </si>
-  <si>
-    <t>NFL: New Orleans Saints-Minnesota Vikings</t>
-  </si>
-  <si>
-    <t>NFL: Seattle Seahawks-San Francisco 49ers</t>
-  </si>
-  <si>
-    <t>Serie A: Atalanta-Venezia</t>
-  </si>
-  <si>
-    <t>Serie A.jpg</t>
-  </si>
-  <si>
-    <t>Serie A: Cagliari-Juventus</t>
-  </si>
-  <si>
     <t>Serie A: Inter-Parma</t>
   </si>
   <si>
     <t>Serie A: Napoli-Frosinone</t>
-  </si>
-  <si>
-    <t>Serie A: Torino-Udinese</t>
-  </si>
-  <si>
-    <t>VM i gravelcykling</t>
-  </si>
-  <si>
-    <t>WTA: Andreeva-Bartunkova, semifinale, Beijing</t>
-  </si>
-  <si>
-    <t>WTA-generic.jpeg</t>
-  </si>
-  <si>
-    <t>TV.2.Sport.X.dk; TV.2.Sport.dk</t>
-  </si>
-  <si>
-    <t>WTA: Finale, Beijing</t>
-  </si>
-  <si>
-    <t>WTA: Zheng-Mertens, semifinale, Beijing</t>
-  </si>
-  <si>
-    <t>C - DR1/DR2</t>
-  </si>
-  <si>
-    <t>DR1.dk</t>
-  </si>
-  <si>
-    <t>80 dage til sommerhus</t>
-  </si>
-  <si>
-    <t>Aftenshowet</t>
-  </si>
-  <si>
-    <t>Alene i vildmarken Australien</t>
-  </si>
-  <si>
-    <t>DR2.dk</t>
-  </si>
-  <si>
-    <t>Alle Guds farver</t>
-  </si>
-  <si>
-    <t>Alt forladt - Scala-bygningen</t>
-  </si>
-  <si>
-    <t>Angkor Vats hemmeligheder</t>
-  </si>
-  <si>
-    <t>Anne og Anders i Kina</t>
-  </si>
-  <si>
-    <t>Aros Skattens Hemmelighed - Flugten</t>
-  </si>
-  <si>
-    <t>Aros Skattens Hemmelighed - Underjordisk kirke</t>
-  </si>
-  <si>
-    <t>Balladen om det beskidte vand</t>
-  </si>
-  <si>
-    <t>Baywatch bag facaden</t>
-  </si>
-  <si>
-    <t>Beck: Den fortabte søn</t>
-  </si>
-  <si>
-    <t>Bonderøven 2010</t>
-  </si>
-  <si>
-    <t>Christiania</t>
-  </si>
-  <si>
-    <t>Cooper &amp; Fry: Det skrigende dødningehoved</t>
-  </si>
-  <si>
-    <t>Cooper &amp; Fry: Sort lune</t>
-  </si>
-  <si>
-    <t>Dansk teater 300 år: Det politiske teater</t>
-  </si>
-  <si>
-    <t>DR1.dk; DR2.dk</t>
-  </si>
-  <si>
-    <t>Deadline</t>
-  </si>
-  <si>
-    <t>Deadline: Fransk gældsbombe truer Europa</t>
-  </si>
-  <si>
-    <t>Deadline: Hænger Danmark stadig sammen?</t>
-  </si>
-  <si>
-    <t>Deadline: Israels ambassadør om den 7. oktober og krigen i Gaza</t>
-  </si>
-  <si>
-    <t>Den klassiske musikquiz</t>
-  </si>
-  <si>
-    <t>Den store bagedyst</t>
-  </si>
-  <si>
-    <t>Der kan man se</t>
-  </si>
-  <si>
-    <t>Destination</t>
-  </si>
-  <si>
-    <t>Drømmen om et liv på landet</t>
-  </si>
-  <si>
-    <t>Dyrenes underverden</t>
-  </si>
-  <si>
-    <t>En barndom fuld af druk</t>
-  </si>
-  <si>
-    <t>Farlig drømmedate</t>
-  </si>
-  <si>
-    <t>Filmperler: De andres liv</t>
-  </si>
-  <si>
-    <t>Fodbold: Canada - Danmark (k), direkte</t>
-  </si>
-  <si>
-    <t>Folk og fæ</t>
-  </si>
-  <si>
-    <t>Frank &amp; Kastaniegaarden - Lækre spær og havelåge med svung</t>
-  </si>
-  <si>
-    <t>Frank Hvam: Make Badminton Great Again</t>
-  </si>
-  <si>
-    <t>Før søndagen: Fald min engel</t>
-  </si>
-  <si>
-    <t>Galopbanens hemmeligheder</t>
-  </si>
-  <si>
-    <t>Generation SoMe!</t>
-  </si>
-  <si>
-    <t>Gi' så mor et kys - det er bare sagen</t>
-  </si>
-  <si>
-    <t>Gift ved første blik</t>
-  </si>
-  <si>
-    <t>Gudstjenesten: Marie Nipper - Troens billeder</t>
-  </si>
-  <si>
-    <t>Hammerslag 2022 - Huse med alder og charme</t>
-  </si>
-  <si>
-    <t>Hammerslag 2022 - Lejlighed i storbyen</t>
-  </si>
-  <si>
-    <t>Husdrøm fra himlen - med Keith og Marj</t>
-  </si>
-  <si>
-    <t>Huse med hemmeligheder</t>
-  </si>
-  <si>
-    <t>Huset på Christianshavn</t>
-  </si>
-  <si>
-    <t>Husker du...</t>
-  </si>
-  <si>
-    <t>Hvornår var det nu det var</t>
-  </si>
-  <si>
-    <t>Høst</t>
-  </si>
-  <si>
-    <t>Jagten på Danmarkshistorien</t>
-  </si>
-  <si>
-    <t>Jagten på de sidste naziforbrydere</t>
-  </si>
-  <si>
-    <t>Jens i vildmarken</t>
-  </si>
-  <si>
-    <t>Jerusalem - Kampen om den hellige by</t>
-  </si>
-  <si>
-    <t>Jonas Kaufmann &amp; DR Symfoniorkestret</t>
-  </si>
-  <si>
-    <t>Jordemoderen</t>
-  </si>
-  <si>
-    <t>Josephine Baker - Stjerne, spion og folkets stemme</t>
-  </si>
-  <si>
-    <t>Ka' du li' ål i karry, Harry?</t>
-  </si>
-  <si>
-    <t>Kabul</t>
-  </si>
-  <si>
-    <t>Kalak</t>
-  </si>
-  <si>
-    <t>Kender Du Typen? 2020 - med dyt og dyppelse</t>
-  </si>
-  <si>
-    <t>Kender Du Typen? 2020 - med grill på badeværelset</t>
-  </si>
-  <si>
-    <t>Kinas smukke natur</t>
-  </si>
-  <si>
-    <t>Kirsebærhaven 89</t>
-  </si>
-  <si>
-    <t>Kommissionen - Folketingets sæsonstart med slagsmål om sindelag, SU og Søren Gades sure exit</t>
-  </si>
-  <si>
-    <t>Kongehuse i krise: Norge</t>
-  </si>
-  <si>
-    <t>Kontinenterne</t>
-  </si>
-  <si>
-    <t>Krigsmaskinen</t>
-  </si>
-  <si>
-    <t>Kriminalkommissær Barnaby XI: Samtale med de døde</t>
-  </si>
-  <si>
-    <t>Kriminalkommissær Barnaby XII: Bristen</t>
-  </si>
-  <si>
-    <t>Kriminalkommissær Barnaby XII: Den sorte bog</t>
-  </si>
-  <si>
-    <t>Kriminalkommissær Barnaby XII: Mord ved 13. hul</t>
-  </si>
-  <si>
-    <t>Kriminalkommissær Barnaby XII: Små glæder</t>
-  </si>
-  <si>
-    <t>Kriseøvelse: Hybridangreb på Danmark</t>
-  </si>
-  <si>
-    <t>Kunstnerkolonien på Sydfyn</t>
-  </si>
-  <si>
-    <t>Love Lies Bleeding</t>
-  </si>
-  <si>
-    <t>Ludere, lommetyve og lirekassemænd</t>
-  </si>
-  <si>
-    <t>Mesterstrikkerne</t>
-  </si>
-  <si>
-    <t>Mig og 70'erne</t>
-  </si>
-  <si>
-    <t>Militærkuppet i Chile</t>
-  </si>
-  <si>
-    <t>Min kunstige kæreste</t>
-  </si>
-  <si>
-    <t>Min søsters børn og guldgraverne</t>
-  </si>
-  <si>
-    <t>Morgenandagten</t>
-  </si>
-  <si>
-    <t>Mors dreng</t>
-  </si>
-  <si>
-    <t>Nak &amp; Æd - Fjæsing og hveps</t>
-  </si>
-  <si>
-    <t>Norges naturskønne nationalparker</t>
-  </si>
-  <si>
-    <t>Nul stjerner - på camping i Sydtyskland</t>
-  </si>
-  <si>
-    <t>Nul stjerner - Tømmerflådeferie i Holland</t>
-  </si>
-  <si>
-    <t>OBS</t>
-  </si>
-  <si>
-    <t>Once Upon a Time... in Hollywood</t>
-  </si>
-  <si>
-    <t>Optimistens guide til planeten</t>
-  </si>
-  <si>
-    <t>P3 Essensen: AI overtager måske dit job hurtigere end du tror</t>
-  </si>
-  <si>
-    <t>På rejse med Griff - Sydstaterne</t>
-  </si>
-  <si>
-    <t>På skuldrene af H. C. Ørsted - Hvad var der før Big Bang?</t>
-  </si>
-  <si>
-    <t>På æblerov med Frank Erichsen</t>
-  </si>
-  <si>
-    <t>Radioavisen</t>
-  </si>
-  <si>
-    <t>Riefenstahl - Instruktør for nazisterne</t>
-  </si>
-  <si>
-    <t>Råzone</t>
-  </si>
-  <si>
-    <t>Sandheden om fængselseksperimentet</t>
-  </si>
-  <si>
-    <t>Seneste nyt fra TVA</t>
-  </si>
-  <si>
-    <t>Shalako</t>
-  </si>
-  <si>
-    <t>Shetland</t>
-  </si>
-  <si>
-    <t>Signe Molde på udebane: Hash er harmløst</t>
-  </si>
-  <si>
-    <t>Smagen af Italien</t>
-  </si>
-  <si>
-    <t>Sporløs UK</t>
-  </si>
-  <si>
-    <t>Sporløs UK - Sådan gik det</t>
-  </si>
-  <si>
-    <t>Sportsmagasinet</t>
-  </si>
-  <si>
-    <t>Stjerner og striber: Præster på prærien presser Trump</t>
-  </si>
-  <si>
-    <t>Stjernerne fra lokal-tv</t>
-  </si>
-  <si>
-    <t>Store danskere - Hans Scherfig</t>
-  </si>
-  <si>
-    <t>Super-showet</t>
-  </si>
-  <si>
-    <t>Supermagternes kamp: USA vs. Kina</t>
-  </si>
-  <si>
-    <t>Søren Vester bygger sommerhus</t>
-  </si>
-  <si>
-    <t>Team Bachstad på hjemmebane</t>
-  </si>
-  <si>
-    <t>Tegnsprogsmagasinet Udsyn</t>
-  </si>
-  <si>
-    <t>The Capture</t>
-  </si>
-  <si>
-    <t>The Dark</t>
-  </si>
-  <si>
-    <t>Troldspejlet: Bæver med budskab</t>
-  </si>
-  <si>
-    <t>Troldspejlet: Ikoniske filmbiler</t>
-  </si>
-  <si>
-    <t>Troldspejlet: Pokémon for voksne</t>
-  </si>
-  <si>
-    <t>TVA</t>
-  </si>
-  <si>
-    <t>Udsendelsesophør</t>
-  </si>
-  <si>
-    <t>Under sydens sol</t>
-  </si>
-  <si>
-    <t>Vera: Brudte løfter</t>
-  </si>
-  <si>
-    <t>Vera: Sort engel</t>
-  </si>
-  <si>
-    <t>Verdenssituationen med Clement</t>
-  </si>
-  <si>
-    <t>Verner Panton - En dansk verdensstjerne</t>
-  </si>
-  <si>
-    <t>Vil AI tage mit job?</t>
-  </si>
-  <si>
-    <t>Vilde familier - helt kort</t>
-  </si>
-  <si>
-    <t>Vilde vidunderlige Danmark - Gråsælen</t>
-  </si>
-  <si>
-    <t>Vinterkrigens piloter og dobbeltspioner</t>
-  </si>
-  <si>
-    <t>Vores sange med DR Pigekoret: Dansevise</t>
-  </si>
-  <si>
-    <t>Vores Vejr</t>
-  </si>
-  <si>
-    <t>Værtshushistorier: Cosy Bar</t>
-  </si>
-  <si>
-    <t>Woman of the Hour</t>
-  </si>
-  <si>
-    <t>Ørkenrigets mægtigste mand</t>
-  </si>
-  <si>
-    <t>360F1.jpg</t>
-  </si>
-  <si>
-    <t>A-Liga.jpg</t>
-  </si>
-  <si>
-    <t>ATP_WTA Tennis2.jpg</t>
-  </si>
-  <si>
-    <t>Aften Paris Nice.jpg</t>
-  </si>
-  <si>
-    <t>Aften Roubaix.jpg</t>
-  </si>
-  <si>
-    <t>AftenVuelta.jpg</t>
-  </si>
-  <si>
-    <t>Aftentour.jpg</t>
-  </si>
-  <si>
-    <t>Atletik Diamond League.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga Review of the Midseason.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga Saturday Highlights.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga Special.jpg</t>
-  </si>
-  <si>
-    <t>CLWomen.jpg</t>
-  </si>
-  <si>
-    <t>Champions Hockey League.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Clásica San Sebastián.jpg</t>
-  </si>
-  <si>
-    <t>Cykling La Vuelta Femenina.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Paris Nice.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Polen Rundt.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Postnord Danmark Rundt.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour Auvergne Rhone-Alpes.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de France Femmes.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de France.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de France2.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Tour de Romandie.jpg</t>
-  </si>
-  <si>
-    <t>Cykling Volta.jpg</t>
-  </si>
-  <si>
-    <t>Cykling.jpg</t>
-  </si>
-  <si>
-    <t>DBU Pokalen.jpg</t>
-  </si>
-  <si>
-    <t>DP World Tour Danish Golf Championship.jpg</t>
-  </si>
-  <si>
-    <t>Davis Cup.jpg</t>
-  </si>
-  <si>
-    <t>Discover a Club.jpg</t>
-  </si>
-  <si>
-    <t>EFL Championship Highligts.jpg</t>
-  </si>
-  <si>
-    <t>EHF European League.jpg</t>
-  </si>
-  <si>
-    <t>EM i atletik.jpg</t>
-  </si>
-  <si>
-    <t>Endurance Car Racing.jpg</t>
-  </si>
-  <si>
-    <t>Euro Cup Håndbold.jpg</t>
-  </si>
-  <si>
-    <t>F1.jpg</t>
-  </si>
-  <si>
-    <t>F1T.JPG</t>
-  </si>
-  <si>
-    <t>F2.jpg</t>
-  </si>
-  <si>
-    <t>F2_Chasing the Dream.jpg</t>
-  </si>
-  <si>
-    <t>F3.jpg</t>
-  </si>
-  <si>
-    <t>FIA World Endurance Championship.jpg</t>
-  </si>
-  <si>
-    <t>FIFA VM 2026.jpg</t>
-  </si>
-  <si>
-    <t>Fastzone.jpg</t>
-  </si>
-  <si>
-    <t>Fodbold Carabao Cup.jpg</t>
-  </si>
-  <si>
-    <t>Fodbold Friuli Venezia Giulia Cup - Kampe.jpg</t>
-  </si>
-  <si>
-    <t>Fodbold Serie A.jpg</t>
-  </si>
-  <si>
-    <t>Formel E VM.jpg</t>
-  </si>
-  <si>
-    <t>Golf LPGA Tour.jpg</t>
-  </si>
-  <si>
-    <t>Golf PGA Champions Tour.jpg</t>
-  </si>
-  <si>
-    <t>Golf PGA Tour.jpg</t>
-  </si>
-  <si>
-    <t>Golf Scandinavian Challenge.jpg</t>
-  </si>
-  <si>
-    <t>Gp Confidential.jpg</t>
-  </si>
-  <si>
-    <t>HBL Håndbold.jpg</t>
-  </si>
-  <si>
-    <t>Håndbold  Golden League.jpg</t>
-  </si>
-  <si>
-    <t>Håndbold Herre Pokal.jpg</t>
-  </si>
-  <si>
-    <t>Håndbold Kvindeligaen.jpg</t>
-  </si>
-  <si>
-    <t>IndyCar1.jpg</t>
-  </si>
-  <si>
-    <t>Kvindeligaen.jpg</t>
-  </si>
-  <si>
-    <t>Landstrænerne.jpg</t>
-  </si>
-  <si>
-    <t>Le Mans.jpg</t>
-  </si>
-  <si>
-    <t>League Cup.jpg</t>
-  </si>
-  <si>
-    <t>Lets Be Frank.jpg</t>
-  </si>
-  <si>
-    <t>Ligue 1 The Season Review Show.jpg</t>
-  </si>
-  <si>
-    <t>Ligue1.jpg</t>
-  </si>
-  <si>
-    <t>MotoGp Season Review.jpg</t>
-  </si>
-  <si>
-    <t>Motocross.jpg</t>
-  </si>
-  <si>
-    <t>Motorsport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Målfesten.jpg</t>
-  </si>
-  <si>
-    <t>NFL Gameday.jpg</t>
-  </si>
-  <si>
-    <t>NFL2.jpg</t>
-  </si>
-  <si>
-    <t>NHL.jpg</t>
-  </si>
-  <si>
-    <t>Nations League1.jpg</t>
-  </si>
-  <si>
-    <t>Nations LeagueDK.jpg</t>
-  </si>
-  <si>
-    <t>PDC Darts.jpg</t>
-  </si>
-  <si>
-    <t>PDC European Tour.jpg</t>
-  </si>
-  <si>
-    <t>Pokal-highligts.jpg</t>
-  </si>
-  <si>
-    <t>Pokalkampe.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Goals of the Season.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Netbusters.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Preview.jpg</t>
-  </si>
-  <si>
-    <t>Premier League Review.jpg</t>
-  </si>
-  <si>
-    <t>Premier League-studiet.jpg</t>
-  </si>
-  <si>
-    <t>Premier League.jpg</t>
-  </si>
-  <si>
-    <t>RaceTV_DK.jpg</t>
-  </si>
-  <si>
-    <t>Skisport.jpg</t>
-  </si>
-  <si>
-    <t>Sky Sports Deadline Day.jpg</t>
-  </si>
-  <si>
-    <t>Snooker.jpg</t>
-  </si>
-  <si>
-    <t>Speedway FIM Speedway Grand Prix.jpg</t>
-  </si>
-  <si>
-    <t>Sporten.jpg</t>
-  </si>
-  <si>
-    <t>Spot på Betinia Liga.jpg</t>
-  </si>
-  <si>
-    <t>Superligaens Topchefer.jpg</t>
-  </si>
-  <si>
-    <t>Superligaens Topchefer2.jpg</t>
-  </si>
-  <si>
-    <t>Superligatilsynet.jpg</t>
-  </si>
-  <si>
-    <t>Tennis Billie-Jean-King-Cup.jpg</t>
-  </si>
-  <si>
-    <t>Tennis-generic3.jpg</t>
-  </si>
-  <si>
-    <t>Tirsdagstrænerne.jpg</t>
-  </si>
-  <si>
-    <t>Tour Studiet.jpg</t>
-  </si>
-  <si>
-    <t>Tour de France Femmes Studiet.jpg</t>
-  </si>
-  <si>
-    <t>Tourstudiet.jpg</t>
-  </si>
-  <si>
-    <t>UEFA Champions League.jpg</t>
-  </si>
-  <si>
-    <t>UEFA Conference League Qualification Studio.jpg</t>
-  </si>
-  <si>
-    <t>UEFA Europa og Conference League.jpg</t>
-  </si>
-  <si>
-    <t>UEFA Super Cup.jpg</t>
-  </si>
-  <si>
-    <t>UEFA Youth League.jpg</t>
-  </si>
-  <si>
-    <t>US Open.jpg</t>
-  </si>
-  <si>
-    <t>Ultimate Championship.jpg</t>
-  </si>
-  <si>
-    <t>VM i MTB.jpg</t>
-  </si>
-  <si>
-    <t>VM i dressur.jpg</t>
-  </si>
-  <si>
-    <t>VM i dressur2.jpg</t>
-  </si>
-  <si>
-    <t>VM i landevejscykling.jpg</t>
-  </si>
-  <si>
-    <t>Venskabskamp Testkamp.jpg</t>
-  </si>
-  <si>
-    <t>Viaplay_Sport_News-generic.jpg</t>
-  </si>
-  <si>
-    <t>Vuelta a España -  Studiet.jpg</t>
-  </si>
-  <si>
-    <t>Vuelta a España.jpeg</t>
-  </si>
-  <si>
-    <t>WTA-generic.jpg</t>
-  </si>
-  <si>
-    <t>Womens CL.jpg</t>
-  </si>
-  <si>
-    <t>cykling4.jpg</t>
   </si>
   <si>
     <t>Sådan bruger du denne fil</t>
@@ -1866,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H275"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1909,13 +1892,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1926,15 +1909,15 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1943,13 +1926,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -1960,13 +1943,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -1977,13 +1960,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -1994,13 +1977,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -2011,13 +1994,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -2031,10 +2014,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -2045,13 +2028,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -2062,13 +2045,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -2079,13 +2062,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -2099,10 +2082,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -2113,13 +2096,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -2130,13 +2113,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -2150,10 +2133,10 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -2164,13 +2147,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -2181,13 +2164,13 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -2201,10 +2184,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -2218,10 +2201,10 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -2232,13 +2215,13 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -2252,10 +2235,10 @@
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G22" t="s">
         <v>12</v>
@@ -2266,13 +2249,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
         <v>12</v>
@@ -2283,13 +2266,13 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G24" t="s">
         <v>12</v>
@@ -2303,10 +2286,10 @@
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -2320,10 +2303,10 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
@@ -2334,13 +2317,13 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
@@ -2354,10 +2337,10 @@
         <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -2368,13 +2351,13 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
@@ -2385,13 +2368,13 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
         <v>12</v>
@@ -2399,16 +2382,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
         <v>12</v>
@@ -2416,16 +2399,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>197</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
         <v>12</v>
@@ -2433,16 +2416,16 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -2450,16 +2433,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
         <v>12</v>
@@ -2467,16 +2450,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G35" t="s">
         <v>12</v>
@@ -2484,16 +2467,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C36" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
@@ -2501,16 +2484,16 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -2518,16 +2501,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G38" t="s">
         <v>12</v>
@@ -2535,16 +2518,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -2552,16 +2535,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G40" t="s">
         <v>12</v>
@@ -2569,16 +2552,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C41" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -2586,16 +2569,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -2603,16 +2586,16 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C43" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -2620,16 +2603,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B44" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
@@ -2637,16 +2620,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C45" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G45" t="s">
         <v>12</v>
@@ -2654,16 +2637,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
@@ -2671,16 +2654,16 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B47" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C47" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
         <v>12</v>
@@ -2688,16 +2671,16 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B48" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -2705,16 +2688,16 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B49" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C49" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
         <v>12</v>
@@ -2722,16 +2705,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>196</v>
+      </c>
+      <c r="B50" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" t="s">
         <v>218</v>
       </c>
-      <c r="B50" t="s">
-        <v>219</v>
-      </c>
-      <c r="C50" t="s">
-        <v>235</v>
-      </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G50" t="s">
         <v>12</v>
@@ -2739,16 +2722,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B51" t="s">
+        <v>201</v>
+      </c>
+      <c r="C51" t="s">
         <v>219</v>
       </c>
-      <c r="C51" t="s">
-        <v>236</v>
-      </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G51" t="s">
         <v>12</v>
@@ -2756,16 +2739,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B52" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C52" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G52" t="s">
         <v>12</v>
@@ -2773,16 +2756,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B53" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C53" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G53" t="s">
         <v>12</v>
@@ -2790,16 +2773,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B54" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G54" t="s">
         <v>12</v>
@@ -2807,16 +2790,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B55" t="s">
+        <v>197</v>
+      </c>
+      <c r="C55" t="s">
         <v>223</v>
       </c>
-      <c r="C55" t="s">
-        <v>241</v>
-      </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
@@ -2824,16 +2807,16 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C56" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G56" t="s">
         <v>12</v>
@@ -2841,16 +2824,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B57" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C57" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G57" t="s">
         <v>12</v>
@@ -2858,16 +2841,16 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C58" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G58" t="s">
         <v>12</v>
@@ -2875,16 +2858,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B59" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C59" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D59" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G59" t="s">
         <v>12</v>
@@ -2892,16 +2875,16 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C60" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G60" t="s">
         <v>12</v>
@@ -2909,16 +2892,16 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C61" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="G61" t="s">
         <v>12</v>
@@ -2926,16 +2909,16 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B62" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G62" t="s">
         <v>12</v>
@@ -2943,16 +2926,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B63" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C63" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G63" t="s">
         <v>12</v>
@@ -2960,16 +2943,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B64" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C64" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="G64" t="s">
         <v>12</v>
@@ -2977,16 +2960,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B65" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C65" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="D65" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G65" t="s">
         <v>12</v>
@@ -2994,16 +2977,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B66" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D66" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G66" t="s">
         <v>12</v>
@@ -3011,16 +2994,16 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B67" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C67" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G67" t="s">
         <v>12</v>
@@ -3028,16 +3011,16 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C68" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G68" t="s">
         <v>12</v>
@@ -3045,16 +3028,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B69" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C69" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="D69" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="G69" t="s">
         <v>12</v>
@@ -3062,16 +3045,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B70" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C70" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G70" t="s">
         <v>12</v>
@@ -3079,16 +3062,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B71" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C71" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G71" t="s">
         <v>12</v>
@@ -3096,16 +3079,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C72" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G72" t="s">
         <v>12</v>
@@ -3113,16 +3096,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G73" t="s">
         <v>12</v>
@@ -3130,16 +3113,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C74" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G74" t="s">
         <v>12</v>
@@ -3147,16 +3130,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B75" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G75" t="s">
         <v>12</v>
@@ -3164,16 +3147,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B76" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G76" t="s">
         <v>12</v>
@@ -3181,16 +3164,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B77" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C77" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G77" t="s">
         <v>12</v>
@@ -3198,16 +3181,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B78" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C78" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G78" t="s">
         <v>12</v>
@@ -3215,16 +3198,16 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B79" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G79" t="s">
         <v>12</v>
@@ -3232,16 +3215,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B80" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C80" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G80" t="s">
         <v>12</v>
@@ -3249,16 +3232,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B81" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C81" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G81" t="s">
         <v>12</v>
@@ -3266,16 +3249,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B82" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C82" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G82" t="s">
         <v>12</v>
@@ -3283,16 +3266,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B83" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C83" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G83" t="s">
         <v>12</v>
@@ -3300,16 +3283,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B84" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C84" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G84" t="s">
         <v>12</v>
@@ -3317,16 +3300,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B85" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C85" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G85" t="s">
         <v>12</v>
@@ -3334,16 +3317,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B86" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C86" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G86" t="s">
         <v>12</v>
@@ -3351,16 +3334,16 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B87" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C87" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G87" t="s">
         <v>12</v>
@@ -3368,16 +3351,16 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B88" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C88" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G88" t="s">
         <v>12</v>
@@ -3385,16 +3368,16 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B89" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C89" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G89" t="s">
         <v>12</v>
@@ -3402,16 +3385,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B90" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C90" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G90" t="s">
         <v>12</v>
@@ -3419,16 +3402,16 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C91" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G91" t="s">
         <v>12</v>
@@ -3436,16 +3419,16 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C92" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="D92" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G92" t="s">
         <v>12</v>
@@ -3453,16 +3436,16 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C93" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G93" t="s">
         <v>12</v>
@@ -3470,16 +3453,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C94" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="D94" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G94" t="s">
         <v>12</v>
@@ -3487,16 +3470,16 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B95" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C95" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G95" t="s">
         <v>12</v>
@@ -3504,16 +3487,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B96" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C96" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G96" t="s">
         <v>12</v>
@@ -3521,16 +3504,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C97" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="D97" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G97" t="s">
         <v>12</v>
@@ -3538,16 +3521,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B98" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C98" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G98" t="s">
         <v>12</v>
@@ -3555,16 +3538,16 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B99" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C99" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="D99" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G99" t="s">
         <v>12</v>
@@ -3572,16 +3555,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C100" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G100" t="s">
         <v>12</v>
@@ -3589,16 +3572,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B101" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C101" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G101" t="s">
         <v>12</v>
@@ -3606,16 +3589,16 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C102" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G102" t="s">
         <v>12</v>
@@ -3623,16 +3606,16 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B103" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C103" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G103" t="s">
         <v>12</v>
@@ -3640,16 +3623,16 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B104" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C104" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G104" t="s">
         <v>12</v>
@@ -3657,16 +3640,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B105" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C105" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G105" t="s">
         <v>12</v>
@@ -3674,16 +3657,16 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B106" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C106" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G106" t="s">
         <v>12</v>
@@ -3691,16 +3674,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B107" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C107" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G107" t="s">
         <v>12</v>
@@ -3708,16 +3691,16 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B108" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C108" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G108" t="s">
         <v>12</v>
@@ -3725,16 +3708,16 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B109" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C109" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G109" t="s">
         <v>12</v>
@@ -3742,16 +3725,16 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B110" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C110" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G110" t="s">
         <v>12</v>
@@ -3759,16 +3742,16 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C111" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="D111" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G111" t="s">
         <v>12</v>
@@ -3776,16 +3759,16 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B112" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C112" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D112" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G112" t="s">
         <v>12</v>
@@ -3793,16 +3776,16 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B113" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C113" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G113" t="s">
         <v>12</v>
@@ -3810,16 +3793,16 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B114" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C114" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D114" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G114" t="s">
         <v>12</v>
@@ -3827,16 +3810,16 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C115" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="D115" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G115" t="s">
         <v>12</v>
@@ -3844,16 +3827,16 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B116" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C116" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G116" t="s">
         <v>12</v>
@@ -3861,16 +3844,16 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B117" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C117" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D117" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G117" t="s">
         <v>12</v>
@@ -3878,16 +3861,16 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B118" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C118" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="D118" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G118" t="s">
         <v>12</v>
@@ -3895,16 +3878,16 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B119" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C119" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="D119" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G119" t="s">
         <v>12</v>
@@ -3912,16 +3895,16 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B120" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C120" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="D120" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G120" t="s">
         <v>12</v>
@@ -3929,16 +3912,16 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B121" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C121" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="D121" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G121" t="s">
         <v>12</v>
@@ -3946,16 +3929,16 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B122" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C122" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="D122" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G122" t="s">
         <v>12</v>
@@ -3963,16 +3946,16 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B123" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C123" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="D123" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G123" t="s">
         <v>12</v>
@@ -3980,16 +3963,16 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B124" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C124" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G124" t="s">
         <v>12</v>
@@ -3997,16 +3980,16 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B125" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C125" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="D125" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G125" t="s">
         <v>12</v>
@@ -4014,16 +3997,16 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B126" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C126" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="D126" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G126" t="s">
         <v>12</v>
@@ -4031,16 +4014,16 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B127" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C127" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G127" t="s">
         <v>12</v>
@@ -4048,16 +4031,16 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B128" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C128" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="D128" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G128" t="s">
         <v>12</v>
@@ -4065,16 +4048,16 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B129" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C129" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="D129" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G129" t="s">
         <v>12</v>
@@ -4082,16 +4065,16 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B130" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C130" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G130" t="s">
         <v>12</v>
@@ -4099,16 +4082,16 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B131" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C131" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G131" t="s">
         <v>12</v>
@@ -4116,16 +4099,16 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B132" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C132" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G132" t="s">
         <v>12</v>
@@ -4133,16 +4116,16 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B133" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="C133" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="D133" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G133" t="s">
         <v>12</v>
@@ -4150,16 +4133,16 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B134" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C134" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="D134" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G134" t="s">
         <v>12</v>
@@ -4167,16 +4150,16 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B135" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C135" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D135" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G135" t="s">
         <v>12</v>
@@ -4184,16 +4167,16 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B136" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C136" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="D136" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G136" t="s">
         <v>12</v>
@@ -4201,16 +4184,16 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B137" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C137" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="D137" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G137" t="s">
         <v>12</v>
@@ -4218,16 +4201,16 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B138" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C138" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G138" t="s">
         <v>12</v>
@@ -4235,16 +4218,16 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B139" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C139" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D139" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G139" t="s">
         <v>12</v>
@@ -4252,16 +4235,16 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B140" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C140" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="D140" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G140" t="s">
         <v>12</v>
@@ -4269,16 +4252,16 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B141" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C141" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="D141" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G141" t="s">
         <v>12</v>
@@ -4286,16 +4269,16 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B142" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C142" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="D142" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G142" t="s">
         <v>12</v>
@@ -4303,16 +4286,16 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B143" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C143" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="D143" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G143" t="s">
         <v>12</v>
@@ -4320,16 +4303,16 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B144" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C144" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="D144" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G144" t="s">
         <v>12</v>
@@ -4337,16 +4320,16 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B145" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C145" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="D145" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G145" t="s">
         <v>12</v>
@@ -4354,16 +4337,16 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B146" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C146" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D146" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G146" t="s">
         <v>12</v>
@@ -4371,16 +4354,16 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B147" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C147" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="D147" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G147" t="s">
         <v>12</v>
@@ -4388,16 +4371,16 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B148" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C148" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G148" t="s">
         <v>12</v>
@@ -4405,16 +4388,16 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B149" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C149" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G149" t="s">
         <v>12</v>
@@ -4422,16 +4405,16 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B150" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C150" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="D150" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G150" t="s">
         <v>12</v>
@@ -4439,16 +4422,16 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B151" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C151" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G151" t="s">
         <v>12</v>
@@ -4456,16 +4439,16 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B152" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C152" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G152" t="s">
         <v>12</v>
@@ -4473,16 +4456,16 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B153" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C153" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="D153" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G153" t="s">
         <v>12</v>
@@ -4490,16 +4473,16 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B154" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C154" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="D154" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G154" t="s">
         <v>12</v>
@@ -4507,16 +4490,16 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B155" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C155" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="D155" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G155" t="s">
         <v>12</v>
@@ -4524,16 +4507,16 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B156" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C156" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G156" t="s">
         <v>12</v>
@@ -4541,16 +4524,16 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B157" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="C157" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="D157" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G157" t="s">
         <v>12</v>
@@ -4558,209 +4541,239 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>219</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>344</v>
+        <v>14</v>
       </c>
       <c r="D158" t="s">
         <v>15</v>
       </c>
-      <c r="G158" t="s">
+      <c r="E158" t="s">
+        <v>15</v>
+      </c>
+      <c r="F158" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>219</v>
+        <v>16</v>
       </c>
       <c r="C159" t="s">
-        <v>345</v>
+        <v>17</v>
       </c>
       <c r="D159" t="s">
         <v>15</v>
       </c>
-      <c r="G159" t="s">
+      <c r="E159" t="s">
+        <v>15</v>
+      </c>
+      <c r="F159" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>18</v>
       </c>
       <c r="D160" t="s">
         <v>15</v>
       </c>
-      <c r="G160" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E160" t="s">
+        <v>15</v>
+      </c>
+      <c r="F160" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>347</v>
+        <v>19</v>
       </c>
       <c r="D161" t="s">
-        <v>15</v>
-      </c>
-      <c r="G161" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="E161" t="s">
+        <v>20</v>
+      </c>
+      <c r="F161" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="C162" t="s">
-        <v>348</v>
+        <v>22</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
-      </c>
-      <c r="G162" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E162" t="s">
+        <v>23</v>
+      </c>
+      <c r="F162" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="C163" t="s">
-        <v>349</v>
+        <v>24</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
-      </c>
-      <c r="G163" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E163" t="s">
+        <v>23</v>
+      </c>
+      <c r="F163" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>223</v>
+        <v>27</v>
       </c>
       <c r="C164" t="s">
-        <v>350</v>
+        <v>28</v>
       </c>
       <c r="D164" t="s">
-        <v>15</v>
-      </c>
-      <c r="G164" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="E164" t="s">
+        <v>29</v>
+      </c>
+      <c r="F164" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="C165" t="s">
-        <v>351</v>
+        <v>30</v>
       </c>
       <c r="D165" t="s">
-        <v>15</v>
-      </c>
-      <c r="G165" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="E165" t="s">
+        <v>31</v>
+      </c>
+      <c r="F165" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>219</v>
+        <v>32</v>
       </c>
       <c r="C166" t="s">
-        <v>352</v>
+        <v>33</v>
       </c>
       <c r="D166" t="s">
-        <v>15</v>
-      </c>
-      <c r="G166" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="F166" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
       <c r="C167" t="s">
-        <v>353</v>
+        <v>36</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
-      </c>
-      <c r="G167" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="E167" t="s">
+        <v>37</v>
+      </c>
+      <c r="F167" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
-        <v>354</v>
+        <v>38</v>
       </c>
       <c r="D168" t="s">
-        <v>15</v>
-      </c>
-      <c r="G168" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="E168" t="s">
+        <v>39</v>
+      </c>
+      <c r="F168" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>223</v>
+        <v>43</v>
       </c>
       <c r="C169" t="s">
-        <v>355</v>
+        <v>44</v>
       </c>
       <c r="D169" t="s">
-        <v>15</v>
-      </c>
-      <c r="G169" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="F169" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -4768,130 +4781,112 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D170" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F170" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C171" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D171" t="s">
-        <v>17</v>
-      </c>
-      <c r="E171" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F171" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C172" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D172" t="s">
-        <v>17</v>
-      </c>
-      <c r="E172" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F172" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>8</v>
       </c>
       <c r="B173" t="s">
+        <v>32</v>
+      </c>
+      <c r="C173" t="s">
+        <v>52</v>
+      </c>
+      <c r="D173" t="s">
+        <v>45</v>
+      </c>
+      <c r="F173" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s">
+        <v>35</v>
+      </c>
+      <c r="C174" t="s">
+        <v>54</v>
+      </c>
+      <c r="D174" t="s">
+        <v>55</v>
+      </c>
+      <c r="F174" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
         <v>21</v>
       </c>
-      <c r="C173" t="s">
-        <v>22</v>
-      </c>
-      <c r="D173" t="s">
-        <v>17</v>
-      </c>
-      <c r="E173" t="s">
-        <v>18</v>
-      </c>
-      <c r="F173" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>8</v>
-      </c>
-      <c r="B174" t="s">
-        <v>9</v>
-      </c>
-      <c r="C174" t="s">
-        <v>23</v>
-      </c>
-      <c r="D174" t="s">
-        <v>17</v>
-      </c>
-      <c r="E174" t="s">
-        <v>18</v>
-      </c>
-      <c r="F174" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>8</v>
-      </c>
-      <c r="B175" t="s">
-        <v>9</v>
-      </c>
       <c r="C175" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D175" t="s">
-        <v>25</v>
-      </c>
-      <c r="E175" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F175" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C176" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D176" t="s">
-        <v>27</v>
-      </c>
-      <c r="E176" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F176" t="s">
         <v>12</v>
@@ -4902,16 +4897,13 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C177" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D177" t="s">
-        <v>31</v>
-      </c>
-      <c r="E177" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="F177" t="s">
         <v>12</v>
@@ -4922,16 +4914,16 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D178" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="E178" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F178" t="s">
         <v>12</v>
@@ -4942,16 +4934,16 @@
         <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D179" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="E179" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F179" t="s">
         <v>12</v>
@@ -4962,16 +4954,13 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C180" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
-      </c>
-      <c r="E180" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="F180" t="s">
         <v>12</v>
@@ -4982,16 +4971,16 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="C181" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D181" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E181" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="F181" t="s">
         <v>12</v>
@@ -5002,16 +4991,13 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C182" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D182" t="s">
-        <v>42</v>
-      </c>
-      <c r="E182" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="F182" t="s">
         <v>12</v>
@@ -5022,13 +5008,13 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C183" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="D183" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="F183" t="s">
         <v>12</v>
@@ -5039,13 +5025,16 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D184" t="s">
-        <v>46</v>
+        <v>88</v>
+      </c>
+      <c r="E184" t="s">
+        <v>88</v>
       </c>
       <c r="F184" t="s">
         <v>12</v>
@@ -5056,16 +5045,16 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D185" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="E185" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F185" t="s">
         <v>12</v>
@@ -5079,13 +5068,13 @@
         <v>21</v>
       </c>
       <c r="C186" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D186" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="E186" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F186" t="s">
         <v>12</v>
@@ -5096,16 +5085,16 @@
         <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C187" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D187" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="E187" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="F187" t="s">
         <v>12</v>
@@ -5116,13 +5105,16 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C188" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="D188" t="s">
-        <v>55</v>
+        <v>88</v>
+      </c>
+      <c r="E188" t="s">
+        <v>88</v>
       </c>
       <c r="F188" t="s">
         <v>12</v>
@@ -5133,13 +5125,16 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C189" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D189" t="s">
-        <v>44</v>
+        <v>88</v>
+      </c>
+      <c r="E189" t="s">
+        <v>88</v>
       </c>
       <c r="F189" t="s">
         <v>12</v>
@@ -5150,13 +5145,13 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C190" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="D190" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="F190" t="s">
         <v>12</v>
@@ -5167,13 +5162,13 @@
         <v>8</v>
       </c>
       <c r="B191" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C191" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="D191" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="F191" t="s">
         <v>12</v>
@@ -5184,13 +5179,13 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="C192" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="D192" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="F192" t="s">
         <v>12</v>
@@ -5201,13 +5196,13 @@
         <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C193" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="D193" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="F193" t="s">
         <v>12</v>
@@ -5218,13 +5213,13 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="C194" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="D194" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F194" t="s">
         <v>12</v>
@@ -5235,13 +5230,13 @@
         <v>8</v>
       </c>
       <c r="B195" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="C195" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="D195" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="F195" t="s">
         <v>12</v>
@@ -5252,13 +5247,13 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C196" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="D196" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="F196" t="s">
         <v>12</v>
@@ -5269,13 +5264,16 @@
         <v>8</v>
       </c>
       <c r="B197" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C197" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D197" t="s">
-        <v>68</v>
+        <v>76</v>
+      </c>
+      <c r="E197" t="s">
+        <v>76</v>
       </c>
       <c r="F197" t="s">
         <v>12</v>
@@ -5286,13 +5284,16 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C198" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="D198" t="s">
-        <v>44</v>
+        <v>76</v>
+      </c>
+      <c r="E198" t="s">
+        <v>76</v>
       </c>
       <c r="F198" t="s">
         <v>12</v>
@@ -5303,13 +5304,16 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="D199" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="E199" t="s">
+        <v>76</v>
       </c>
       <c r="F199" t="s">
         <v>12</v>
@@ -5320,14 +5324,17 @@
         <v>8</v>
       </c>
       <c r="B200" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C200" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D200" t="s">
         <v>76</v>
       </c>
+      <c r="E200" t="s">
+        <v>76</v>
+      </c>
       <c r="F200" t="s">
         <v>12</v>
       </c>
@@ -5337,13 +5344,16 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="C201" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D201" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="E201" t="s">
+        <v>76</v>
       </c>
       <c r="F201" t="s">
         <v>12</v>
@@ -5354,16 +5364,16 @@
         <v>8</v>
       </c>
       <c r="B202" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C202" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D202" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="E202" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F202" t="s">
         <v>12</v>
@@ -5374,13 +5384,13 @@
         <v>8</v>
       </c>
       <c r="B203" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="C203" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="D203" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="F203" t="s">
         <v>12</v>
@@ -5391,16 +5401,13 @@
         <v>8</v>
       </c>
       <c r="B204" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C204" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="D204" t="s">
-        <v>27</v>
-      </c>
-      <c r="E204" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="F204" t="s">
         <v>12</v>
@@ -5408,19 +5415,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B205" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="C205" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="D205" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E205" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="F205" t="s">
         <v>12</v>
@@ -5428,19 +5435,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B206" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="C206" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="D206" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E206" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="F206" t="s">
         <v>12</v>
@@ -5448,16 +5455,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B207" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="C207" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="D207" t="s">
-        <v>98</v>
+        <v>15</v>
+      </c>
+      <c r="E207" t="s">
+        <v>15</v>
       </c>
       <c r="F207" t="s">
         <v>12</v>
@@ -5465,19 +5475,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B208" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C208" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="D208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E208" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F208" t="s">
         <v>12</v>
@@ -5485,16 +5495,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B209" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="C209" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="D209" t="s">
-        <v>105</v>
+        <v>15</v>
+      </c>
+      <c r="E209" t="s">
+        <v>15</v>
       </c>
       <c r="F209" t="s">
         <v>12</v>
@@ -5502,16 +5515,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B210" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="C210" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D210" t="s">
-        <v>109</v>
+        <v>15</v>
+      </c>
+      <c r="E210" t="s">
+        <v>15</v>
       </c>
       <c r="F210" t="s">
         <v>12</v>
@@ -5519,19 +5535,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B211" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="C211" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D211" t="s">
-        <v>17</v>
-      </c>
-      <c r="E211" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="F211" t="s">
         <v>12</v>
@@ -5539,19 +5552,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B212" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="C212" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="D212" t="s">
-        <v>17</v>
-      </c>
-      <c r="E212" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="F212" t="s">
         <v>12</v>
@@ -5559,19 +5569,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B213" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="C213" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="D213" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="E213" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="F213" t="s">
         <v>12</v>
@@ -5579,19 +5589,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B214" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="C214" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="D214" t="s">
-        <v>17</v>
-      </c>
-      <c r="E214" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="F214" t="s">
         <v>12</v>
@@ -5599,19 +5606,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B215" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="C215" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="D215" t="s">
-        <v>17</v>
-      </c>
-      <c r="E215" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="F215" t="s">
         <v>12</v>
@@ -5619,19 +5623,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B216" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="C216" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="D216" t="s">
-        <v>17</v>
-      </c>
-      <c r="E216" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="F216" t="s">
         <v>12</v>
@@ -5639,19 +5640,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B217" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="C217" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="D217" t="s">
-        <v>17</v>
-      </c>
-      <c r="E217" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="F217" t="s">
         <v>12</v>
@@ -5659,19 +5657,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B218" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="C218" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="D218" t="s">
-        <v>17</v>
-      </c>
-      <c r="E218" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="F218" t="s">
         <v>12</v>
@@ -5679,19 +5674,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B219" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="C219" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="D219" t="s">
-        <v>17</v>
-      </c>
-      <c r="E219" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="F219" t="s">
         <v>12</v>
@@ -5699,16 +5691,19 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B220" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="C220" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="D220" t="s">
-        <v>129</v>
+        <v>178</v>
+      </c>
+      <c r="E220" t="s">
+        <v>178</v>
       </c>
       <c r="F220" t="s">
         <v>12</v>
@@ -5716,16 +5711,19 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B221" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="C221" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="D221" t="s">
-        <v>133</v>
+        <v>178</v>
+      </c>
+      <c r="E221" t="s">
+        <v>178</v>
       </c>
       <c r="F221" t="s">
         <v>12</v>
@@ -5733,16 +5731,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B222" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="C222" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="D222" t="s">
-        <v>135</v>
+        <v>178</v>
+      </c>
+      <c r="E222" t="s">
+        <v>178</v>
       </c>
       <c r="F222" t="s">
         <v>12</v>
@@ -5750,16 +5751,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B223" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="C223" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="D223" t="s">
-        <v>137</v>
+        <v>178</v>
+      </c>
+      <c r="E223" t="s">
+        <v>178</v>
       </c>
       <c r="F223" t="s">
         <v>12</v>
@@ -5767,16 +5771,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B224" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="C224" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="D224" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="F224" t="s">
         <v>12</v>
@@ -5784,16 +5788,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B225" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="C225" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="D225" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="F225" t="s">
         <v>12</v>
@@ -5801,16 +5805,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B226" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="C226" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="D226" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="F226" t="s">
         <v>12</v>
@@ -5818,16 +5822,19 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B227" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C227" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="D227" t="s">
-        <v>150</v>
+        <v>186</v>
+      </c>
+      <c r="E227" t="s">
+        <v>186</v>
       </c>
       <c r="F227" t="s">
         <v>12</v>
@@ -5835,16 +5842,19 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B228" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C228" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="D228" t="s">
-        <v>152</v>
+        <v>186</v>
+      </c>
+      <c r="E228" t="s">
+        <v>186</v>
       </c>
       <c r="F228" t="s">
         <v>12</v>
@@ -5852,19 +5862,19 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B229" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="C229" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="D229" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="E229" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="F229" t="s">
         <v>12</v>
@@ -5872,19 +5882,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B230" t="s">
-        <v>13</v>
+        <v>161</v>
       </c>
       <c r="C230" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="D230" t="s">
-        <v>17</v>
-      </c>
-      <c r="E230" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="F230" t="s">
         <v>12</v>
@@ -5892,19 +5899,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="B231" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="C231" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="D231" t="s">
-        <v>17</v>
-      </c>
-      <c r="E231" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="F231" t="s">
         <v>12</v>
@@ -5915,16 +5919,16 @@
         <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C232" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E232" t="s">
-        <v>100</v>
+        <v>341</v>
       </c>
       <c r="F232" t="s">
         <v>12</v>
@@ -5935,16 +5939,13 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C233" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="D233" t="s">
-        <v>17</v>
-      </c>
-      <c r="E233" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="F233" t="s">
         <v>12</v>
@@ -5955,16 +5956,13 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C234" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="D234" t="s">
-        <v>17</v>
-      </c>
-      <c r="E234" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="F234" t="s">
         <v>12</v>
@@ -5975,13 +5973,16 @@
         <v>8</v>
       </c>
       <c r="B235" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="C235" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="D235" t="s">
-        <v>160</v>
+        <v>84</v>
+      </c>
+      <c r="E235" t="s">
+        <v>76</v>
       </c>
       <c r="F235" t="s">
         <v>12</v>
@@ -5992,13 +5993,16 @@
         <v>8</v>
       </c>
       <c r="B236" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C236" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="D236" t="s">
-        <v>162</v>
+        <v>84</v>
+      </c>
+      <c r="E236" t="s">
+        <v>76</v>
       </c>
       <c r="F236" t="s">
         <v>12</v>
@@ -6006,19 +6010,19 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="B237" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="C237" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="D237" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E237" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F237" t="s">
         <v>12</v>
@@ -6026,19 +6030,19 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="B238" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C238" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="D238" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E238" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F238" t="s">
         <v>12</v>
@@ -6046,19 +6050,19 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="B239" t="s">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="C239" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="D239" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E239" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F239" t="s">
         <v>12</v>
@@ -6066,19 +6070,19 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="B240" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C240" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="D240" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="E240" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F240" t="s">
         <v>12</v>
@@ -6086,19 +6090,19 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="B241" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C241" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="D241" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E241" t="s">
-        <v>18</v>
+        <v>436</v>
       </c>
       <c r="F241" t="s">
         <v>12</v>
@@ -6106,19 +6110,19 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="B242" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C242" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="D242" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E242" t="s">
-        <v>18</v>
+        <v>436</v>
       </c>
       <c r="F242" t="s">
         <v>12</v>
@@ -6126,16 +6130,19 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B243" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C243" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D243" t="s">
-        <v>173</v>
+        <v>155</v>
+      </c>
+      <c r="E243" t="s">
+        <v>158</v>
       </c>
       <c r="F243" t="s">
         <v>12</v>
@@ -6143,16 +6150,19 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B244" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C244" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D244" t="s">
-        <v>175</v>
+        <v>155</v>
+      </c>
+      <c r="E244" t="s">
+        <v>158</v>
       </c>
       <c r="F244" t="s">
         <v>12</v>
@@ -6160,19 +6170,19 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B245" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C245" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D245" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="E245" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="F245" t="s">
         <v>12</v>
@@ -6180,19 +6190,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B246" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C246" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="D246" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="E246" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="F246" t="s">
         <v>12</v>
@@ -6200,19 +6210,19 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>142</v>
+      </c>
+      <c r="B247" t="s">
+        <v>161</v>
+      </c>
+      <c r="C247" t="s">
         <v>164</v>
       </c>
-      <c r="B247" t="s">
-        <v>165</v>
-      </c>
-      <c r="C247" t="s">
-        <v>180</v>
-      </c>
       <c r="D247" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E247" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F247" t="s">
         <v>12</v>
@@ -6220,16 +6230,19 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B248" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C248" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D248" t="s">
-        <v>183</v>
+        <v>163</v>
+      </c>
+      <c r="E248" t="s">
+        <v>163</v>
       </c>
       <c r="F248" t="s">
         <v>12</v>
@@ -6237,16 +6250,19 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B249" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C249" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="D249" t="s">
-        <v>183</v>
+        <v>163</v>
+      </c>
+      <c r="E249" t="s">
+        <v>163</v>
       </c>
       <c r="F249" t="s">
         <v>12</v>
@@ -6254,16 +6270,19 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B250" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C250" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="D250" t="s">
-        <v>183</v>
+        <v>163</v>
+      </c>
+      <c r="E250" t="s">
+        <v>163</v>
       </c>
       <c r="F250" t="s">
         <v>12</v>
@@ -6271,16 +6290,19 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B251" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C251" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D251" t="s">
-        <v>183</v>
+        <v>163</v>
+      </c>
+      <c r="E251" t="s">
+        <v>163</v>
       </c>
       <c r="F251" t="s">
         <v>12</v>
@@ -6288,16 +6310,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B252" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="C252" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D252" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F252" t="s">
         <v>12</v>
@@ -6305,16 +6327,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B253" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="C253" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D253" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F253" t="s">
         <v>12</v>
@@ -6322,16 +6344,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B254" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="C254" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D254" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F254" t="s">
         <v>12</v>
@@ -6339,402 +6361,32 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B255" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C255" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D255" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F255" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>164</v>
-      </c>
-      <c r="B256" t="s">
-        <v>181</v>
-      </c>
-      <c r="C256" t="s">
-        <v>191</v>
-      </c>
-      <c r="D256" t="s">
-        <v>183</v>
-      </c>
-      <c r="F256" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>164</v>
-      </c>
-      <c r="B257" t="s">
-        <v>181</v>
-      </c>
-      <c r="C257" t="s">
-        <v>192</v>
-      </c>
-      <c r="D257" t="s">
-        <v>183</v>
-      </c>
-      <c r="F257" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>164</v>
-      </c>
-      <c r="B258" t="s">
-        <v>181</v>
-      </c>
-      <c r="C258" t="s">
-        <v>193</v>
-      </c>
-      <c r="D258" t="s">
-        <v>194</v>
-      </c>
-      <c r="F258" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>164</v>
-      </c>
-      <c r="B259" t="s">
-        <v>181</v>
-      </c>
-      <c r="C259" t="s">
-        <v>195</v>
-      </c>
-      <c r="D259" t="s">
-        <v>196</v>
-      </c>
-      <c r="E259" t="s">
-        <v>197</v>
-      </c>
-      <c r="F259" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>164</v>
-      </c>
-      <c r="B260" t="s">
-        <v>181</v>
-      </c>
-      <c r="C260" t="s">
-        <v>198</v>
-      </c>
-      <c r="D260" t="s">
-        <v>196</v>
-      </c>
-      <c r="E260" t="s">
-        <v>197</v>
-      </c>
-      <c r="F260" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>164</v>
-      </c>
-      <c r="B261" t="s">
-        <v>181</v>
-      </c>
-      <c r="C261" t="s">
-        <v>199</v>
-      </c>
-      <c r="D261" t="s">
-        <v>196</v>
-      </c>
-      <c r="E261" t="s">
-        <v>197</v>
-      </c>
-      <c r="F261" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>164</v>
-      </c>
-      <c r="B262" t="s">
-        <v>181</v>
-      </c>
-      <c r="C262" t="s">
-        <v>200</v>
-      </c>
-      <c r="D262" t="s">
-        <v>201</v>
-      </c>
-      <c r="E262" t="s">
-        <v>197</v>
-      </c>
-      <c r="F262" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>164</v>
-      </c>
-      <c r="B263" t="s">
-        <v>165</v>
-      </c>
-      <c r="C263" t="s">
-        <v>202</v>
-      </c>
-      <c r="D263" t="s">
-        <v>177</v>
-      </c>
-      <c r="E263" t="s">
-        <v>178</v>
-      </c>
-      <c r="F263" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>164</v>
-      </c>
-      <c r="B264" t="s">
-        <v>181</v>
-      </c>
-      <c r="C264" t="s">
-        <v>203</v>
-      </c>
-      <c r="D264" t="s">
-        <v>93</v>
-      </c>
-      <c r="F264" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>164</v>
-      </c>
-      <c r="B265" t="s">
-        <v>181</v>
-      </c>
-      <c r="C265" t="s">
-        <v>204</v>
-      </c>
-      <c r="D265" t="s">
-        <v>93</v>
-      </c>
-      <c r="F265" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>164</v>
-      </c>
-      <c r="B266" t="s">
-        <v>181</v>
-      </c>
-      <c r="C266" t="s">
-        <v>205</v>
-      </c>
-      <c r="D266" t="s">
-        <v>93</v>
-      </c>
-      <c r="F266" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>164</v>
-      </c>
-      <c r="B267" t="s">
-        <v>181</v>
-      </c>
-      <c r="C267" t="s">
-        <v>206</v>
-      </c>
-      <c r="D267" t="s">
-        <v>196</v>
-      </c>
-      <c r="E267" t="s">
-        <v>207</v>
-      </c>
-      <c r="F267" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>164</v>
-      </c>
-      <c r="B268" t="s">
-        <v>165</v>
-      </c>
-      <c r="C268" t="s">
-        <v>208</v>
-      </c>
-      <c r="D268" t="s">
-        <v>177</v>
-      </c>
-      <c r="E268" t="s">
-        <v>207</v>
-      </c>
-      <c r="F268" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>164</v>
-      </c>
-      <c r="B269" t="s">
-        <v>165</v>
-      </c>
-      <c r="C269" t="s">
-        <v>209</v>
-      </c>
-      <c r="D269" t="s">
-        <v>177</v>
-      </c>
-      <c r="E269" t="s">
-        <v>207</v>
-      </c>
-      <c r="F269" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>164</v>
-      </c>
-      <c r="B270" t="s">
-        <v>165</v>
-      </c>
-      <c r="C270" t="s">
-        <v>210</v>
-      </c>
-      <c r="D270" t="s">
-        <v>177</v>
-      </c>
-      <c r="E270" t="s">
-        <v>207</v>
-      </c>
-      <c r="F270" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>164</v>
-      </c>
-      <c r="B271" t="s">
-        <v>181</v>
-      </c>
-      <c r="C271" t="s">
-        <v>211</v>
-      </c>
-      <c r="D271" t="s">
-        <v>196</v>
-      </c>
-      <c r="E271" t="s">
-        <v>207</v>
-      </c>
-      <c r="F271" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>164</v>
-      </c>
-      <c r="B272" t="s">
-        <v>181</v>
-      </c>
-      <c r="C272" t="s">
-        <v>212</v>
-      </c>
-      <c r="D272" t="s">
-        <v>194</v>
-      </c>
-      <c r="F272" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>164</v>
-      </c>
-      <c r="B273" t="s">
-        <v>165</v>
-      </c>
-      <c r="C273" t="s">
-        <v>213</v>
-      </c>
-      <c r="D273" t="s">
-        <v>214</v>
-      </c>
-      <c r="F273" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>164</v>
-      </c>
-      <c r="B274" t="s">
-        <v>215</v>
-      </c>
-      <c r="C274" t="s">
-        <v>216</v>
-      </c>
-      <c r="D274" t="s">
-        <v>214</v>
-      </c>
-      <c r="F274" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>164</v>
-      </c>
-      <c r="B275" t="s">
-        <v>165</v>
-      </c>
-      <c r="C275" t="s">
-        <v>217</v>
-      </c>
-      <c r="D275" t="s">
-        <v>214</v>
-      </c>
-      <c r="F275" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H275">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H255">
       <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E275" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E255" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>BilledeValgListe</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:G275" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:G255" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6749,807 +6401,807 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>360</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>361</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>363</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>369</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>387</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>398</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>400</v>
+        <v>373</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>201</v>
+        <v>385</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>85</v>
+        <v>394</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>129</v>
+        <v>418</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>133</v>
+        <v>419</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>451</v>
+        <v>176</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>196</v>
+        <v>450</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -7559,6 +7211,201 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>456</v>
+      </c>
+      <c r="C6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>457</v>
+      </c>
+      <c r="C7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>458</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>459</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>460</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>461</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" t="s">
+        <v>462</v>
+      </c>
+      <c r="C12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>464</v>
+      </c>
+      <c r="C14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" t="s">
+        <v>465</v>
+      </c>
+      <c r="C15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>466</v>
+      </c>
+      <c r="C16" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7568,7 +7415,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7576,50 +7423,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B5" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B6" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B7" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B8" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7627,42 +7474,42 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B10" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B11" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B12" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B13" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B14" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
